--- a/jira_export_2026-09-09.xlsx
+++ b/jira_export_2026-09-09.xlsx
@@ -720,7 +720,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>10,955 €</t>
+          <t>15,986 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -734,7 +734,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>15.1%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -760,14 +760,14 @@
     <row r="11" ht="26" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>3,356 €</t>
+          <t>4,036 €</t>
         </is>
       </c>
       <c r="B11" s="7" t="n"/>
       <c r="C11" s="7" t="n"/>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>7,598 €</t>
+          <t>11,950 €</t>
         </is>
       </c>
       <c r="E11" s="7" t="n"/>
@@ -815,7 +815,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>134 h</t>
+          <t>148 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -829,7 +829,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>40.2%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -933,7 +933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P109"/>
+  <dimension ref="A1:P115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -1054,32 +1054,32 @@
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-35435</t>
+          <t>PDMDEP-35518</t>
         </is>
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>[CD 92] - Modélisation suite audit sur site</t>
+          <t>[COMMUNE DE PRIVAS] - Migration Placier sans nouveau matériel</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D5" s="11" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DES HAUTS-DE-SEINE</t>
+          <t>COMMUNE DE PRIVAS</t>
         </is>
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>Modélisation suite audit sur site</t>
+          <t>Migration Placier sans nouveau matériel</t>
         </is>
       </c>
       <c r="F5" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G5" s="11" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="H5" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I5" s="11" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="J5" s="11" t="n">
@@ -1105,14 +1105,10 @@
       </c>
       <c r="L5" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35439</t>
-        </is>
-      </c>
-      <c r="M5" s="11" t="inlineStr">
-        <is>
-          <t>00180506</t>
-        </is>
-      </c>
+          <t>PDMDEP-35532</t>
+        </is>
+      </c>
+      <c r="M5" s="11" t="inlineStr"/>
       <c r="N5" s="12" t="n">
         <v>0</v>
       </c>
@@ -1126,32 +1122,32 @@
     <row r="6">
       <c r="A6" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-35401</t>
+          <t>PDMDEP-35435</t>
         </is>
       </c>
       <c r="B6" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de Saint Cast le Guildo ] - Migration GEODP 2 </t>
+          <t>[CD 92] - Modélisation suite audit sur site</t>
         </is>
       </c>
       <c r="C6" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D6" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Commune de Saint Cast le Guildo </t>
+          <t>DEPARTEMENT DES HAUTS-DE-SEINE</t>
         </is>
       </c>
       <c r="E6" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GEODP 2 </t>
+          <t>Modélisation suite audit sur site</t>
         </is>
       </c>
       <c r="F6" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G6" s="14" t="inlineStr">
@@ -1161,28 +1157,28 @@
       </c>
       <c r="H6" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I6" s="14" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
       <c r="J6" s="14" t="n">
         <v>0</v>
       </c>
       <c r="K6" s="14" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="L6" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35410</t>
+          <t>PDMDEP-35439</t>
         </is>
       </c>
       <c r="M6" s="14" t="inlineStr">
         <is>
-          <t>00173074</t>
+          <t>00180506</t>
         </is>
       </c>
       <c r="N6" s="15" t="n">
@@ -1198,12 +1194,12 @@
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-35313</t>
+          <t>PDMDEP-35401</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE GAREOULT] - Migration Geodp Placier</t>
+          <t xml:space="preserve">[Commune de Saint Cast le Guildo ] - Migration GEODP 2 </t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
@@ -1213,12 +1209,12 @@
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE GAREOULT</t>
+          <t xml:space="preserve">Commune de Saint Cast le Guildo </t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>Migration Geodp Placier</t>
+          <t xml:space="preserve">Migration GEODP 2 </t>
         </is>
       </c>
       <c r="F7" s="11" t="inlineStr">
@@ -1238,23 +1234,23 @@
       </c>
       <c r="I7" s="11" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="J7" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" s="11" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="L7" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35319</t>
+          <t>PDMDEP-35410</t>
         </is>
       </c>
       <c r="M7" s="11" t="inlineStr">
         <is>
-          <t>00179389</t>
+          <t>00173074</t>
         </is>
       </c>
       <c r="N7" s="12" t="n">
@@ -1270,32 +1266,32 @@
     <row r="8">
       <c r="A8" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-35184</t>
+          <t>PDMDEP-35313</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE GAILLARD] - Prestation forfait - Reprise de charte graphique</t>
+          <t>[COMMUNE DE GAREOULT] - Migration Geodp Placier</t>
         </is>
       </c>
       <c r="C8" s="14" t="inlineStr">
         <is>
-          <t>Marine MASINGARBE</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D8" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE GAILLARD</t>
+          <t>COMMUNE DE GAREOULT</t>
         </is>
       </c>
       <c r="E8" s="14" t="inlineStr">
         <is>
-          <t>Prestation forfait - Reprise de charte graphique</t>
+          <t>Migration Geodp Placier</t>
         </is>
       </c>
       <c r="F8" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G8" s="14" t="inlineStr">
@@ -1305,69 +1301,69 @@
       </c>
       <c r="H8" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I8" s="14" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="J8" s="14" t="n">
         <v>1</v>
       </c>
       <c r="K8" s="14" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="L8" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35188</t>
+          <t>PDMDEP-35319</t>
         </is>
       </c>
       <c r="M8" s="14" t="inlineStr">
         <is>
-          <t>00178947</t>
+          <t>00179389</t>
         </is>
       </c>
       <c r="N8" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O8" s="15" t="n">
-        <v>902.72</v>
+        <v>0</v>
       </c>
       <c r="P8" s="15" t="n">
-        <v>451.36</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-35148</t>
+          <t>PDMDEP-35184</t>
         </is>
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>[MAIRIE DES PORTES EN RE] - UPSELL PAX</t>
+          <t>[COMMUNE DE GAILLARD] - Prestation forfait - Reprise de charte graphique</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Marine MASINGARBE</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>Mairie de Les Portes En Ré</t>
+          <t>COMMUNE DE GAILLARD</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>UPSELL PAX</t>
+          <t>Prestation forfait - Reprise de charte graphique</t>
         </is>
       </c>
       <c r="F9" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G9" s="11" t="inlineStr">
@@ -1382,69 +1378,69 @@
       </c>
       <c r="I9" s="11" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
       <c r="J9" s="11" t="n">
         <v>1</v>
       </c>
       <c r="K9" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L9" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35156</t>
+          <t>PDMDEP-35188</t>
         </is>
       </c>
       <c r="M9" s="11" t="inlineStr">
         <is>
-          <t>00178841</t>
+          <t>00178947</t>
         </is>
       </c>
       <c r="N9" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O9" s="12" t="n">
-        <v>225</v>
+        <v>902.72</v>
       </c>
       <c r="P9" s="12" t="n">
-        <v>0</v>
+        <v>451.36</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-35037</t>
+          <t>PDMDEP-35148</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[VILLE DE VILLEFRANCHE SUR SAONE ] - mise a jour carto comprise dans leur abonnement annuel </t>
+          <t>[MAIRIE DES PORTES EN RE] - UPSELL PAX</t>
         </is>
       </c>
       <c r="C10" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D10" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">VILLE DE VILLEFRANCHE SUR SAONE </t>
+          <t>Mairie de Les Portes En Ré</t>
         </is>
       </c>
       <c r="E10" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">mise a jour carto comprise dans leur abonnement annuel </t>
+          <t>UPSELL PAX</t>
         </is>
       </c>
       <c r="F10" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G10" s="14" t="inlineStr">
         <is>
-          <t>Prestation offerte</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H10" s="14" t="inlineStr">
@@ -1454,22 +1450,30 @@
       </c>
       <c r="I10" s="14" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
       <c r="J10" s="14" t="n">
         <v>1</v>
       </c>
       <c r="K10" s="14" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="L10" s="14" t="inlineStr"/>
-      <c r="M10" s="14" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L10" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-35156</t>
+        </is>
+      </c>
+      <c r="M10" s="14" t="inlineStr">
+        <is>
+          <t>00178841</t>
+        </is>
+      </c>
       <c r="N10" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O10" s="15" t="n">
-        <v>0</v>
+        <v>225</v>
       </c>
       <c r="P10" s="15" t="n">
         <v>0</v>
@@ -1478,12 +1482,12 @@
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-35029</t>
+          <t>PDMDEP-35037</t>
         </is>
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>[VILLE DE LEVALLOIS PERRET] - Hébergement Litt Exp test et prod</t>
+          <t xml:space="preserve">[VILLE DE VILLEFRANCHE SUR SAONE ] - mise a jour carto comprise dans leur abonnement annuel </t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
@@ -1493,12 +1497,12 @@
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE LEVALLOIS PERRET</t>
+          <t xml:space="preserve">VILLE DE VILLEFRANCHE SUR SAONE </t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hébergement Litt Exp </t>
+          <t xml:space="preserve">mise a jour carto comprise dans leur abonnement annuel </t>
         </is>
       </c>
       <c r="F11" s="11" t="inlineStr">
@@ -1508,7 +1512,7 @@
       </c>
       <c r="G11" s="11" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Prestation offerte</t>
         </is>
       </c>
       <c r="H11" s="11" t="inlineStr">
@@ -1525,7 +1529,7 @@
         <v>1</v>
       </c>
       <c r="K11" s="11" t="n">
-        <v>4</v>
+        <v>1.75</v>
       </c>
       <c r="L11" s="11" t="inlineStr"/>
       <c r="M11" s="11" t="inlineStr"/>
@@ -1542,27 +1546,27 @@
     <row r="12">
       <c r="A12" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34975</t>
+          <t>PDMDEP-35029</t>
         </is>
       </c>
       <c r="B12" s="14" t="inlineStr">
         <is>
-          <t>[VILLE DE SURESNES] - Migration Littéralis vers nouveau serveur+ montée de version Test et Prod</t>
+          <t>[VILLE DE LEVALLOIS PERRET] - Hébergement Litt Exp test et prod</t>
         </is>
       </c>
       <c r="C12" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D12" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE SURESNES</t>
+          <t>VILLE DE LEVALLOIS PERRET</t>
         </is>
       </c>
       <c r="E12" s="14" t="inlineStr">
         <is>
-          <t>Migration Littéralis vers nouveau serveur+ montée de version Test et Prod</t>
+          <t xml:space="preserve">Hébergement Litt Exp </t>
         </is>
       </c>
       <c r="F12" s="14" t="inlineStr">
@@ -1572,7 +1576,7 @@
       </c>
       <c r="G12" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H12" s="14" t="inlineStr">
@@ -1582,29 +1586,21 @@
       </c>
       <c r="I12" s="14" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
       <c r="J12" s="14" t="n">
         <v>1</v>
       </c>
       <c r="K12" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-34979</t>
-        </is>
-      </c>
-      <c r="M12" s="14" t="inlineStr">
-        <is>
-          <t>00178226</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="L12" s="14" t="inlineStr"/>
+      <c r="M12" s="14" t="inlineStr"/>
       <c r="N12" s="15" t="n">
-        <v>1100</v>
-      </c>
-      <c r="O12" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P12" s="15" t="n">
@@ -1614,32 +1610,32 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34819</t>
+          <t>PDMDEP-34975</t>
         </is>
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>[Ville de Bourges] - Migration GEODP Placier et ODP</t>
+          <t>[VILLE DE SURESNES] - Migration Littéralis vers nouveau serveur+ montée de version Test et Prod</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>Ville de Bourges</t>
+          <t>VILLE DE SURESNES</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier et ODP</t>
+          <t>Migration Littéralis vers nouveau serveur+ montée de version Test et Prod</t>
         </is>
       </c>
       <c r="F13" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G13" s="11" t="inlineStr">
@@ -1649,35 +1645,35 @@
       </c>
       <c r="H13" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I13" s="11" t="inlineStr">
         <is>
-          <t>29/07/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
       <c r="J13" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K13" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L13" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34825</t>
+          <t>PDMDEP-34979</t>
         </is>
       </c>
       <c r="M13" s="11" t="inlineStr">
         <is>
-          <t>00177218</t>
+          <t>00178226</t>
         </is>
       </c>
       <c r="N13" s="12" t="n">
-        <v>2419</v>
+        <v>1100</v>
       </c>
       <c r="O13" s="16" t="n">
-        <v>120.95</v>
+        <v>0</v>
       </c>
       <c r="P13" s="12" t="n">
         <v>0</v>
@@ -1686,27 +1682,27 @@
     <row r="14">
       <c r="A14" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34782</t>
+          <t>PDMDEP-34819</t>
         </is>
       </c>
       <c r="B14" s="14" t="inlineStr">
         <is>
-          <t>[MAIRIE DE SAINT-ISMIER] - Acquisition GEODP Placier</t>
+          <t>[Ville de Bourges] - Migration GEODP Placier et ODP</t>
         </is>
       </c>
       <c r="C14" s="14" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D14" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE SAINT-ISMIER</t>
+          <t>Ville de Bourges</t>
         </is>
       </c>
       <c r="E14" s="14" t="inlineStr">
         <is>
-          <t>GEODP PLACIER</t>
+          <t>Migration GEODP Placier et ODP</t>
         </is>
       </c>
       <c r="F14" s="14" t="inlineStr">
@@ -1721,7 +1717,7 @@
       </c>
       <c r="H14" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I14" s="14" t="inlineStr">
@@ -1733,52 +1729,52 @@
         <v>2</v>
       </c>
       <c r="K14" s="14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L14" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34791</t>
+          <t>PDMDEP-34825</t>
         </is>
       </c>
       <c r="M14" s="14" t="inlineStr">
         <is>
-          <t>00177122</t>
+          <t>00177218</t>
         </is>
       </c>
       <c r="N14" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" s="15" t="n">
-        <v>643.95</v>
+        <v>2419</v>
+      </c>
+      <c r="O14" s="16" t="n">
+        <v>120.95</v>
       </c>
       <c r="P14" s="15" t="n">
-        <v>321.98</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34761</t>
+          <t>PDMDEP-34782</t>
         </is>
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DU PUY EN VELAY] - Migration GeODP Placier + migration ODP</t>
+          <t>[MAIRIE DE SAINT-ISMIER] - Acquisition GEODP Placier</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DU PUY EN VELAY</t>
+          <t>MAIRIE DE SAINT-ISMIER</t>
         </is>
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier + migration ODP</t>
+          <t>GEODP PLACIER</t>
         </is>
       </c>
       <c r="F15" s="11" t="inlineStr">
@@ -1793,69 +1789,69 @@
       </c>
       <c r="H15" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I15" s="11" t="inlineStr">
         <is>
-          <t>28/07/2026</t>
+          <t>29/07/2026</t>
         </is>
       </c>
       <c r="J15" s="11" t="n">
         <v>2</v>
       </c>
       <c r="K15" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L15" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34768</t>
+          <t>PDMDEP-34791</t>
         </is>
       </c>
       <c r="M15" s="11" t="inlineStr">
         <is>
-          <t>00177029</t>
+          <t>00177122</t>
         </is>
       </c>
       <c r="N15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O15" s="12" t="n">
-        <v>726.05</v>
+        <v>643.95</v>
       </c>
       <c r="P15" s="12" t="n">
-        <v>0</v>
+        <v>321.98</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34718</t>
+          <t>PDMDEP-34761</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>[VILLE DE VILLEURBANNE] - Crédits d'heure (14h)</t>
+          <t>[COMMUNE DU PUY EN VELAY] - Migration GeODP Placier + migration ODP</t>
         </is>
       </c>
       <c r="C16" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D16" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE VILLEURBANNE</t>
+          <t>COMMUNE DU PUY EN VELAY</t>
         </is>
       </c>
       <c r="E16" s="14" t="inlineStr">
         <is>
-          <t>Crédits d'heure (14h)</t>
+          <t>Migration GeODP Placier + migration ODP</t>
         </is>
       </c>
       <c r="F16" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G16" s="14" t="inlineStr">
@@ -1865,49 +1861,49 @@
       </c>
       <c r="H16" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I16" s="14" t="inlineStr">
         <is>
-          <t>24/07/2026</t>
+          <t>28/07/2026</t>
         </is>
       </c>
       <c r="J16" s="14" t="n">
         <v>2</v>
       </c>
       <c r="K16" s="14" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="L16" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34722</t>
+          <t>PDMDEP-34768</t>
         </is>
       </c>
       <c r="M16" s="14" t="inlineStr">
         <is>
-          <t>00176875</t>
+          <t>00177029</t>
         </is>
       </c>
       <c r="N16" s="15" t="n">
-        <v>1260</v>
-      </c>
-      <c r="O16" s="16" t="n">
-        <v>728</v>
+        <v>0</v>
+      </c>
+      <c r="O16" s="15" t="n">
+        <v>726.05</v>
       </c>
       <c r="P16" s="15" t="n">
-        <v>264.73</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34495</t>
+          <t>PDMDEP-34718</t>
         </is>
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE CLICHY] - PRESTATION DE MODELISATION + integration RODP </t>
+          <t>[VILLE DE VILLEURBANNE] - Crédits d'heure (14h)</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
@@ -1917,12 +1913,12 @@
       </c>
       <c r="D17" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CLICHY</t>
+          <t>VILLE DE VILLEURBANNE</t>
         </is>
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">PRESTATION DE MODELISATION + integration RODP </t>
+          <t>Crédits d'heure (14h)</t>
         </is>
       </c>
       <c r="F17" s="11" t="inlineStr">
@@ -1942,64 +1938,64 @@
       </c>
       <c r="I17" s="11" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>24/07/2026</t>
         </is>
       </c>
       <c r="J17" s="11" t="n">
         <v>2</v>
       </c>
       <c r="K17" s="11" t="n">
-        <v>2.25</v>
+        <v>2.92</v>
       </c>
       <c r="L17" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34499</t>
+          <t>PDMDEP-34722</t>
         </is>
       </c>
       <c r="M17" s="11" t="inlineStr">
         <is>
-          <t>00172678</t>
+          <t>00176875</t>
         </is>
       </c>
       <c r="N17" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" s="12" t="n">
-        <v>43</v>
+        <v>1260</v>
+      </c>
+      <c r="O17" s="16" t="n">
+        <v>728</v>
       </c>
       <c r="P17" s="12" t="n">
-        <v>19.11</v>
+        <v>249.6</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34475</t>
+          <t>PDMDEP-34495</t>
         </is>
       </c>
       <c r="B18" s="14" t="inlineStr">
         <is>
-          <t>[Mairie de Pontcharra] - Migration simple placier</t>
+          <t xml:space="preserve">[COMMUNE DE CLICHY] - PRESTATION DE MODELISATION + integration RODP </t>
         </is>
       </c>
       <c r="C18" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D18" s="14" t="inlineStr">
         <is>
-          <t>Mairie de Pontcharra</t>
+          <t>COMMUNE DE CLICHY</t>
         </is>
       </c>
       <c r="E18" s="14" t="inlineStr">
         <is>
-          <t>Migration simple placier</t>
+          <t xml:space="preserve">PRESTATION DE MODELISATION + integration RODP </t>
         </is>
       </c>
       <c r="F18" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G18" s="14" t="inlineStr">
@@ -2009,49 +2005,49 @@
       </c>
       <c r="H18" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I18" s="14" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
       <c r="J18" s="14" t="n">
         <v>2</v>
       </c>
       <c r="K18" s="14" t="n">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="L18" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34481</t>
+          <t>PDMDEP-34499</t>
         </is>
       </c>
       <c r="M18" s="14" t="inlineStr">
         <is>
-          <t>00172611</t>
+          <t>00172678</t>
         </is>
       </c>
       <c r="N18" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O18" s="15" t="n">
-        <v>105</v>
+        <v>43</v>
       </c>
       <c r="P18" s="15" t="n">
-        <v>70</v>
+        <v>12.29</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34411</t>
+          <t>PDMDEP-34475</t>
         </is>
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>[MAIRIE DE MAIZIERES LES METZ] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>[Mairie de Pontcharra] - Migration simple placier</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
@@ -2061,12 +2057,12 @@
       </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE MAIZIERES LES METZ</t>
+          <t>Mairie de Pontcharra</t>
         </is>
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>Migration simple placier</t>
         </is>
       </c>
       <c r="F19" s="11" t="inlineStr">
@@ -2086,44 +2082,44 @@
       </c>
       <c r="I19" s="11" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
       <c r="J19" s="11" t="n">
         <v>2</v>
       </c>
       <c r="K19" s="11" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="L19" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34420</t>
+          <t>PDMDEP-34481</t>
         </is>
       </c>
       <c r="M19" s="11" t="inlineStr">
         <is>
-          <t>00172317</t>
+          <t>00172611</t>
         </is>
       </c>
       <c r="N19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O19" s="12" t="n">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="P19" s="12" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34319</t>
+          <t>PDMDEP-34411</t>
         </is>
       </c>
       <c r="B20" s="14" t="inlineStr">
         <is>
-          <t>[Commune de Mouscron (BE)] - Migration GEODP Placier</t>
+          <t>[MAIRIE DE MAIZIERES LES METZ] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="C20" s="14" t="inlineStr">
@@ -2133,12 +2129,12 @@
       </c>
       <c r="D20" s="14" t="inlineStr">
         <is>
-          <t>Commune de Mouscron (BE)</t>
+          <t>MAIRIE DE MAIZIERES LES METZ</t>
         </is>
       </c>
       <c r="E20" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier</t>
+          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="F20" s="14" t="inlineStr">
@@ -2158,29 +2154,29 @@
       </c>
       <c r="I20" s="14" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
       <c r="J20" s="14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K20" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34326</t>
+          <t>PDMDEP-34420</t>
         </is>
       </c>
       <c r="M20" s="14" t="inlineStr">
         <is>
-          <t>00171691</t>
+          <t>00172317</t>
         </is>
       </c>
       <c r="N20" s="15" t="n">
-        <v>769.5</v>
-      </c>
-      <c r="O20" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P20" s="15" t="n">
@@ -2190,27 +2186,27 @@
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34287</t>
+          <t>PDMDEP-34319</t>
         </is>
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE LUNEL] - Migration GeODP </t>
+          <t>[Commune de Mouscron (BE)] - Migration GEODP Placier</t>
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D21" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE LUNEL</t>
+          <t>Commune de Mouscron (BE)</t>
         </is>
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GeODP </t>
+          <t>Migration GEODP Placier</t>
         </is>
       </c>
       <c r="F21" s="11" t="inlineStr">
@@ -2220,7 +2216,7 @@
       </c>
       <c r="G21" s="11" t="inlineStr">
         <is>
-          <t>Prestation offerte</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H21" s="11" t="inlineStr">
@@ -2230,21 +2226,29 @@
       </c>
       <c r="I21" s="11" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="J21" s="11" t="n">
         <v>3</v>
       </c>
       <c r="K21" s="11" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L21" s="11" t="inlineStr"/>
-      <c r="M21" s="11" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L21" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-34326</t>
+        </is>
+      </c>
+      <c r="M21" s="11" t="inlineStr">
+        <is>
+          <t>00171691</t>
+        </is>
+      </c>
       <c r="N21" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" s="12" t="n">
+        <v>769.5</v>
+      </c>
+      <c r="O21" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P21" s="12" t="n">
@@ -2254,27 +2258,27 @@
     <row r="22">
       <c r="A22" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34249</t>
+          <t>PDMDEP-34287</t>
         </is>
       </c>
       <c r="B22" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE VIENNE] - Migration Placier et ODP </t>
+          <t xml:space="preserve">[COMMUNE DE LUNEL] - Migration GeODP </t>
         </is>
       </c>
       <c r="C22" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D22" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE VIENNE</t>
+          <t>COMMUNE DE LUNEL</t>
         </is>
       </c>
       <c r="E22" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration Placier et ODP </t>
+          <t xml:space="preserve">Migration GeODP </t>
         </is>
       </c>
       <c r="F22" s="14" t="inlineStr">
@@ -2284,7 +2288,7 @@
       </c>
       <c r="G22" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Prestation offerte</t>
         </is>
       </c>
       <c r="H22" s="14" t="inlineStr">
@@ -2301,22 +2305,14 @@
         <v>3</v>
       </c>
       <c r="K22" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-34258</t>
-        </is>
-      </c>
-      <c r="M22" s="14" t="inlineStr">
-        <is>
-          <t>00171361</t>
-        </is>
-      </c>
+        <v>2.5</v>
+      </c>
+      <c r="L22" s="14" t="inlineStr"/>
+      <c r="M22" s="14" t="inlineStr"/>
       <c r="N22" s="15" t="n">
-        <v>2127.2</v>
-      </c>
-      <c r="O22" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P22" s="15" t="n">
@@ -2326,32 +2322,32 @@
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34229</t>
+          <t>PDMDEP-34249</t>
         </is>
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>[DIJON METROPOLE] - GRC + Connecteur</t>
+          <t xml:space="preserve">[COMMUNE DE VIENNE] - Migration Placier et ODP </t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>DIJON METROPOLE</t>
+          <t>COMMUNE DE VIENNE</t>
         </is>
       </c>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t>GRC + Connecteur</t>
+          <t xml:space="preserve">Migration Placier et ODP </t>
         </is>
       </c>
       <c r="F23" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G23" s="11" t="inlineStr">
@@ -2361,69 +2357,69 @@
       </c>
       <c r="H23" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I23" s="11" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="J23" s="11" t="n">
         <v>3</v>
       </c>
       <c r="K23" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L23" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34235</t>
+          <t>PDMDEP-34258</t>
         </is>
       </c>
       <c r="M23" s="11" t="inlineStr">
         <is>
-          <t>00171333</t>
+          <t>00171361</t>
         </is>
       </c>
       <c r="N23" s="12" t="n">
-        <v>4536</v>
+        <v>2127.2</v>
       </c>
       <c r="O23" s="16" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="P23" s="12" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34208</t>
+          <t>PDMDEP-34229</t>
         </is>
       </c>
       <c r="B24" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE CHATEAUGIRON] - Migration GEODP Placier 2</t>
+          <t>[DIJON METROPOLE] - GRC + Connecteur</t>
         </is>
       </c>
       <c r="C24" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D24" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHATEAUGIRON</t>
+          <t>DIJON METROPOLE</t>
         </is>
       </c>
       <c r="E24" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier 2</t>
+          <t>GRC + Connecteur</t>
         </is>
       </c>
       <c r="F24" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G24" s="14" t="inlineStr">
@@ -2433,49 +2429,49 @@
       </c>
       <c r="H24" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I24" s="14" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="J24" s="14" t="n">
         <v>3</v>
       </c>
       <c r="K24" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34216</t>
+          <t>PDMDEP-34235</t>
         </is>
       </c>
       <c r="M24" s="14" t="inlineStr">
         <is>
-          <t>00171155</t>
+          <t>00171333</t>
         </is>
       </c>
       <c r="N24" s="15" t="n">
-        <v>525</v>
+        <v>4536</v>
       </c>
       <c r="O24" s="16" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="P24" s="15" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34192</t>
+          <t>PDMDEP-34208</t>
         </is>
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>[Commune de Macon ] - GEODP Placier</t>
+          <t>[COMMUNE DE CHATEAUGIRON] - Migration GEODP Placier 2</t>
         </is>
       </c>
       <c r="C25" s="11" t="inlineStr">
@@ -2485,12 +2481,12 @@
       </c>
       <c r="D25" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Commune de Macon </t>
+          <t>COMMUNE DE CHATEAUGIRON</t>
         </is>
       </c>
       <c r="E25" s="11" t="inlineStr">
         <is>
-          <t>GEODP Placier</t>
+          <t>Migration GEODP Placier 2</t>
         </is>
       </c>
       <c r="F25" s="11" t="inlineStr">
@@ -2505,7 +2501,7 @@
       </c>
       <c r="H25" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I25" s="11" t="inlineStr">
@@ -2517,52 +2513,52 @@
         <v>3</v>
       </c>
       <c r="K25" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L25" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34201</t>
+          <t>PDMDEP-34216</t>
         </is>
       </c>
       <c r="M25" s="11" t="inlineStr">
         <is>
-          <t>00171162</t>
+          <t>00171155</t>
         </is>
       </c>
       <c r="N25" s="12" t="n">
-        <v>1662</v>
+        <v>525</v>
       </c>
       <c r="O25" s="16" t="n">
-        <v>277</v>
+        <v>0</v>
       </c>
       <c r="P25" s="12" t="n">
-        <v>277</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34169</t>
+          <t>PDMDEP-34192</t>
         </is>
       </c>
       <c r="B26" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE] - Migration GEODP 1 vers GEODP 2</t>
+          <t>[Commune de Macon ] - GEODP Placier</t>
         </is>
       </c>
       <c r="C26" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D26" s="14" t="inlineStr">
         <is>
-          <t>COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE</t>
+          <t xml:space="preserve">Commune de Macon </t>
         </is>
       </c>
       <c r="E26" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2</t>
+          <t>GEODP Placier</t>
         </is>
       </c>
       <c r="F26" s="14" t="inlineStr">
@@ -2577,49 +2573,49 @@
       </c>
       <c r="H26" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I26" s="14" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="J26" s="14" t="n">
         <v>3</v>
       </c>
       <c r="K26" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34227</t>
+          <t>PDMDEP-34201</t>
         </is>
       </c>
       <c r="M26" s="14" t="inlineStr">
         <is>
-          <t>2026-0210095</t>
+          <t>00171162</t>
         </is>
       </c>
       <c r="N26" s="15" t="n">
-        <v>9623.1</v>
+        <v>1662</v>
       </c>
       <c r="O26" s="16" t="n">
-        <v>320.77</v>
+        <v>277</v>
       </c>
       <c r="P26" s="15" t="n">
-        <v>0</v>
+        <v>277</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34108</t>
+          <t>PDMDEP-34169</t>
         </is>
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DU PUY EN VELAY] - Migration GeODP Placier + migration ODP</t>
+          <t>[COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE] - Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="C27" s="11" t="inlineStr">
@@ -2629,12 +2625,12 @@
       </c>
       <c r="D27" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DU PUY EN VELAY</t>
+          <t>COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE</t>
         </is>
       </c>
       <c r="E27" s="11" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier + migration ODP</t>
+          <t>Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="F27" s="11" t="inlineStr">
@@ -2654,7 +2650,7 @@
       </c>
       <c r="I27" s="11" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="J27" s="11" t="n">
@@ -2665,19 +2661,19 @@
       </c>
       <c r="L27" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34117</t>
+          <t>PDMDEP-34227</t>
         </is>
       </c>
       <c r="M27" s="11" t="inlineStr">
         <is>
-          <t>00170907</t>
+          <t>2026-0210095</t>
         </is>
       </c>
       <c r="N27" s="12" t="n">
-        <v>707</v>
+        <v>9623.1</v>
       </c>
       <c r="O27" s="16" t="n">
-        <v>0</v>
+        <v>3849.24</v>
       </c>
       <c r="P27" s="12" t="n">
         <v>0</v>
@@ -2686,32 +2682,32 @@
     <row r="28">
       <c r="A28" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34064</t>
+          <t>PDMDEP-34126</t>
         </is>
       </c>
       <c r="B28" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[VILLE DE VANNES] - ORMC pour GEODP PLACIER </t>
+          <t>[SETE] - AME LiEx</t>
         </is>
       </c>
       <c r="C28" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D28" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE VANNES</t>
+          <t>COMMUNE DE SETE</t>
         </is>
       </c>
       <c r="E28" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">ORMC pour GEODP PLACIER </t>
+          <t>AME LiEx</t>
         </is>
       </c>
       <c r="F28" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G28" s="14" t="inlineStr">
@@ -2726,29 +2722,29 @@
       </c>
       <c r="I28" s="14" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="J28" s="14" t="n">
         <v>3</v>
       </c>
       <c r="K28" s="14" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L28" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34070</t>
+          <t>PDMDEP-34130</t>
         </is>
       </c>
       <c r="M28" s="14" t="inlineStr">
         <is>
-          <t>00170468</t>
+          <t>00170928</t>
         </is>
       </c>
       <c r="N28" s="15" t="n">
-        <v>300</v>
-      </c>
-      <c r="O28" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P28" s="15" t="n">
@@ -2758,27 +2754,27 @@
     <row r="29">
       <c r="A29" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33985</t>
+          <t>PDMDEP-34108</t>
         </is>
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE QUIMPERLE] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>[COMMUNE DU PUY EN VELAY] - Migration GeODP Placier + migration ODP</t>
         </is>
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D29" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE QUIMPERLE</t>
+          <t>COMMUNE DU PUY EN VELAY</t>
         </is>
       </c>
       <c r="E29" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>Migration GeODP Placier + migration ODP</t>
         </is>
       </c>
       <c r="F29" s="11" t="inlineStr">
@@ -2798,7 +2794,7 @@
       </c>
       <c r="I29" s="11" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="J29" s="11" t="n">
@@ -2809,16 +2805,16 @@
       </c>
       <c r="L29" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33991</t>
+          <t>PDMDEP-34117</t>
         </is>
       </c>
       <c r="M29" s="11" t="inlineStr">
         <is>
-          <t>00170408</t>
+          <t>00170907</t>
         </is>
       </c>
       <c r="N29" s="12" t="n">
-        <v>510</v>
+        <v>707</v>
       </c>
       <c r="O29" s="16" t="n">
         <v>0</v>
@@ -2830,32 +2826,32 @@
     <row r="30">
       <c r="A30" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33949</t>
+          <t>PDMDEP-34064</t>
         </is>
       </c>
       <c r="B30" s="14" t="inlineStr">
         <is>
-          <t>[Commune de Colmar] - Modélisation Littéralis Expert et Démarrage Prod</t>
+          <t xml:space="preserve">[VILLE DE VANNES] - ORMC pour GEODP PLACIER </t>
         </is>
       </c>
       <c r="C30" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D30" s="14" t="inlineStr">
         <is>
-          <t>Commune de Colmar</t>
+          <t>VILLE DE VANNES</t>
         </is>
       </c>
       <c r="E30" s="14" t="inlineStr">
         <is>
-          <t>Modélisation Littéralis Expert</t>
+          <t xml:space="preserve">ORMC pour GEODP PLACIER </t>
         </is>
       </c>
       <c r="F30" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G30" s="14" t="inlineStr">
@@ -2870,64 +2866,64 @@
       </c>
       <c r="I30" s="14" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="J30" s="14" t="n">
         <v>3</v>
       </c>
       <c r="K30" s="14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L30" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33955</t>
+          <t>PDMDEP-34070</t>
         </is>
       </c>
       <c r="M30" s="14" t="inlineStr">
         <is>
-          <t>00170302</t>
+          <t>00170468</t>
         </is>
       </c>
       <c r="N30" s="15" t="n">
-        <v>242.9</v>
-      </c>
-      <c r="O30" s="15" t="n">
-        <v>248.58</v>
+        <v>300</v>
+      </c>
+      <c r="O30" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P30" s="15" t="n">
-        <v>124.29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33940</t>
+          <t>PDMDEP-33985</t>
         </is>
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de Thionville] - AME </t>
+          <t>[COMMUNE DE QUIMPERLE] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="C31" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D31" s="11" t="inlineStr">
         <is>
-          <t>Commune de Thionville</t>
+          <t>COMMUNE DE QUIMPERLE</t>
         </is>
       </c>
       <c r="E31" s="11" t="inlineStr">
         <is>
-          <t>AME Littéralis Expert</t>
+          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="F31" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G31" s="11" t="inlineStr">
@@ -2937,12 +2933,12 @@
       </c>
       <c r="H31" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I31" s="11" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="J31" s="11" t="n">
@@ -2953,16 +2949,16 @@
       </c>
       <c r="L31" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33944</t>
+          <t>PDMDEP-33991</t>
         </is>
       </c>
       <c r="M31" s="11" t="inlineStr">
         <is>
-          <t>00170299</t>
+          <t>00170408</t>
         </is>
       </c>
       <c r="N31" s="12" t="n">
-        <v>220</v>
+        <v>510</v>
       </c>
       <c r="O31" s="16" t="n">
         <v>0</v>
@@ -2974,27 +2970,27 @@
     <row r="32">
       <c r="A32" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33813</t>
+          <t>PDMDEP-33949</t>
         </is>
       </c>
       <c r="B32" s="14" t="inlineStr">
         <is>
-          <t>[METROPOLE TOULON-PROVENCE-MEDITERRANEE] - Modélisation Seyne S/ Mer</t>
+          <t>[Commune de Colmar] - Modélisation Littéralis Expert et Démarrage Prod</t>
         </is>
       </c>
       <c r="C32" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D32" s="14" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
+          <t>Commune de Colmar</t>
         </is>
       </c>
       <c r="E32" s="14" t="inlineStr">
         <is>
-          <t>Modélisation Seyne S/ Mer</t>
+          <t>Modélisation Littéralis Expert</t>
         </is>
       </c>
       <c r="F32" s="14" t="inlineStr">
@@ -3014,44 +3010,44 @@
       </c>
       <c r="I32" s="14" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="J32" s="14" t="n">
         <v>3</v>
       </c>
       <c r="K32" s="14" t="n">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="L32" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33817</t>
+          <t>PDMDEP-33955</t>
         </is>
       </c>
       <c r="M32" s="14" t="inlineStr">
         <is>
-          <t>00169865</t>
+          <t>00170302</t>
         </is>
       </c>
       <c r="N32" s="15" t="n">
-        <v>0</v>
+        <v>242.9</v>
       </c>
       <c r="O32" s="15" t="n">
-        <v>65.73</v>
+        <v>248.58</v>
       </c>
       <c r="P32" s="15" t="n">
-        <v>52.58</v>
+        <v>124.29</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33804</t>
+          <t>PDMDEP-33940</t>
         </is>
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>[CD 73)] - Purge arrêtés temporaires</t>
+          <t xml:space="preserve">[Commune de Thionville] - AME </t>
         </is>
       </c>
       <c r="C33" s="11" t="inlineStr">
@@ -3061,12 +3057,12 @@
       </c>
       <c r="D33" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE LA SAVOIE (CD 73)</t>
+          <t>Commune de Thionville</t>
         </is>
       </c>
       <c r="E33" s="11" t="inlineStr">
         <is>
-          <t>Purge arrêtés temporaires</t>
+          <t>AME Littéralis Expert</t>
         </is>
       </c>
       <c r="F33" s="11" t="inlineStr">
@@ -3086,7 +3082,7 @@
       </c>
       <c r="I33" s="11" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="J33" s="11" t="n">
@@ -3097,16 +3093,16 @@
       </c>
       <c r="L33" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33808</t>
+          <t>PDMDEP-33944</t>
         </is>
       </c>
       <c r="M33" s="11" t="inlineStr">
         <is>
-          <t>00169856</t>
+          <t>00170299</t>
         </is>
       </c>
       <c r="N33" s="12" t="n">
-        <v>1890</v>
+        <v>220</v>
       </c>
       <c r="O33" s="16" t="n">
         <v>0</v>
@@ -3118,27 +3114,27 @@
     <row r="34">
       <c r="A34" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33790</t>
+          <t>PDMDEP-33813</t>
         </is>
       </c>
       <c r="B34" s="14" t="inlineStr">
         <is>
-          <t>[CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91)] - Commande modélisation supplémentaire - 6,5j</t>
+          <t>[METROPOLE TOULON-PROVENCE-MEDITERRANEE] - Modélisation Seyne S/ Mer</t>
         </is>
       </c>
       <c r="C34" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D34" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
         </is>
       </c>
       <c r="E34" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Commande modélisation supplémentaire </t>
+          <t>Modélisation Seyne S/ Mer</t>
         </is>
       </c>
       <c r="F34" s="14" t="inlineStr">
@@ -3158,59 +3154,59 @@
       </c>
       <c r="I34" s="14" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="J34" s="14" t="n">
         <v>3</v>
       </c>
       <c r="K34" s="14" t="n">
-        <v>2.75</v>
+        <v>1.25</v>
       </c>
       <c r="L34" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33794</t>
+          <t>PDMDEP-33817</t>
         </is>
       </c>
       <c r="M34" s="14" t="inlineStr">
         <is>
-          <t>00169697</t>
+          <t>00169865</t>
         </is>
       </c>
       <c r="N34" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O34" s="15" t="n">
-        <v>266.2</v>
+        <v>65.73</v>
       </c>
       <c r="P34" s="15" t="n">
-        <v>96.8</v>
+        <v>52.58</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33739</t>
+          <t>PDMDEP-33804</t>
         </is>
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DU POIRE SUR VIE (MAIRIE)] - UPSELL Pastell + Portail DA DPA</t>
+          <t>[CD 73)] - Purge arrêtés temporaires</t>
         </is>
       </c>
       <c r="C35" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D35" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DU POIRE SUR VIE (MAIRIE)</t>
+          <t>CONSEIL DEPARTEMENTAL DE LA SAVOIE (CD 73)</t>
         </is>
       </c>
       <c r="E35" s="11" t="inlineStr">
         <is>
-          <t>UPSELL PASTELL + DA DPA</t>
+          <t>Purge arrêtés temporaires</t>
         </is>
       </c>
       <c r="F35" s="11" t="inlineStr">
@@ -3230,27 +3226,27 @@
       </c>
       <c r="I35" s="11" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="J35" s="11" t="n">
         <v>3</v>
       </c>
       <c r="K35" s="11" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="L35" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33745</t>
+          <t>PDMDEP-33808</t>
         </is>
       </c>
       <c r="M35" s="11" t="inlineStr">
         <is>
-          <t>00169509</t>
+          <t>00169856</t>
         </is>
       </c>
       <c r="N35" s="12" t="n">
-        <v>920</v>
+        <v>1890</v>
       </c>
       <c r="O35" s="16" t="n">
         <v>0</v>
@@ -3262,27 +3258,27 @@
     <row r="36">
       <c r="A36" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33699</t>
+          <t>PDMDEP-33790</t>
         </is>
       </c>
       <c r="B36" s="14" t="inlineStr">
         <is>
-          <t>[CD 35)] - Montée de version Littéralis - 1 journée d'assistance fonctionnelle à distance</t>
+          <t>[CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91)] - Commande modélisation supplémentaire - 6,5j</t>
         </is>
       </c>
       <c r="C36" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D36" s="14" t="inlineStr">
         <is>
-          <t>DEPARTEMENT D'ILLE ET VILAINE (CD 35)</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
         </is>
       </c>
       <c r="E36" s="14" t="inlineStr">
         <is>
-          <t>Montée de version Littéralis - 1 journée d'assistance fonctionnelle à distance</t>
+          <t xml:space="preserve">Commande modélisation supplémentaire </t>
         </is>
       </c>
       <c r="F36" s="14" t="inlineStr">
@@ -3302,64 +3298,64 @@
       </c>
       <c r="I36" s="14" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="J36" s="14" t="n">
         <v>3</v>
       </c>
       <c r="K36" s="14" t="n">
-        <v>0.75</v>
+        <v>3.75</v>
       </c>
       <c r="L36" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33703</t>
+          <t>PDMDEP-33794</t>
         </is>
       </c>
       <c r="M36" s="14" t="inlineStr">
         <is>
-          <t>00169363</t>
+          <t>00169697</t>
         </is>
       </c>
       <c r="N36" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O36" s="15" t="n">
-        <v>540</v>
+        <v>266.2</v>
       </c>
       <c r="P36" s="15" t="n">
-        <v>720</v>
+        <v>70.98999999999999</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33610</t>
+          <t>PDMDEP-33739</t>
         </is>
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE MORLAIX] - Migration GEODP Placier hors matériel </t>
+          <t>[COMMUNE DU POIRE SUR VIE (MAIRIE)] - UPSELL Pastell + Portail DA DPA</t>
         </is>
       </c>
       <c r="C37" s="11" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D37" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE MORLAIX</t>
+          <t>COMMUNE DU POIRE SUR VIE (MAIRIE)</t>
         </is>
       </c>
       <c r="E37" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">MIGRATION GEODP PLACIER hors matériel </t>
+          <t>UPSELL PASTELL + DA DPA</t>
         </is>
       </c>
       <c r="F37" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G37" s="11" t="inlineStr">
@@ -3369,35 +3365,35 @@
       </c>
       <c r="H37" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I37" s="11" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="J37" s="11" t="n">
         <v>3</v>
       </c>
       <c r="K37" s="11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="L37" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33616</t>
+          <t>PDMDEP-33745</t>
         </is>
       </c>
       <c r="M37" s="11" t="inlineStr">
         <is>
-          <t>00169015</t>
+          <t>00169509</t>
         </is>
       </c>
       <c r="N37" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O37" s="12" t="n">
-        <v>505</v>
+        <v>920</v>
+      </c>
+      <c r="O37" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P37" s="12" t="n">
         <v>0</v>
@@ -3406,32 +3402,32 @@
     <row r="38">
       <c r="A38" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33597</t>
+          <t>PDMDEP-33729</t>
         </is>
       </c>
       <c r="B38" s="14" t="inlineStr">
         <is>
-          <t>[Commune de Trets] - Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
+          <t xml:space="preserve">[VILLE DE NEUILLY SUR SEINE - Direction des systèmes d'information] - MONTEE DE VERSION LITT EXP  test et prod </t>
         </is>
       </c>
       <c r="C38" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D38" s="14" t="inlineStr">
         <is>
-          <t>Commune de Trets</t>
+          <t>VILLE DE NEUILLY SUR SEINE - Direction des systèmes d'information</t>
         </is>
       </c>
       <c r="E38" s="14" t="inlineStr">
         <is>
-          <t>Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
+          <t xml:space="preserve">MONTEE DE VERSION LITT EXP  test et prod </t>
         </is>
       </c>
       <c r="F38" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G38" s="14" t="inlineStr">
@@ -3446,64 +3442,64 @@
       </c>
       <c r="I38" s="14" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="J38" s="14" t="n">
         <v>3</v>
       </c>
       <c r="K38" s="14" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="L38" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33605</t>
+          <t>PDMDEP-33733</t>
         </is>
       </c>
       <c r="M38" s="14" t="inlineStr">
         <is>
-          <t>00168993</t>
+          <t>00169480</t>
         </is>
       </c>
       <c r="N38" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O38" s="15" t="n">
-        <v>0</v>
+        <v>679.5</v>
       </c>
       <c r="P38" s="15" t="n">
-        <v>0</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33500</t>
+          <t>PDMDEP-33699</t>
         </is>
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Mairie de Carcès ] - GEODP PLACIER avec PAIEMENT CB </t>
+          <t>[CD 35)] - Montée de version Littéralis - 1 journée d'assistance fonctionnelle à distance</t>
         </is>
       </c>
       <c r="C39" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D39" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mairie de Carcès </t>
+          <t>DEPARTEMENT D'ILLE ET VILAINE (CD 35)</t>
         </is>
       </c>
       <c r="E39" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">GEODP PLACIER avec PAIEMENT CB </t>
+          <t>Montée de version Littéralis - 1 journée d'assistance fonctionnelle à distance</t>
         </is>
       </c>
       <c r="F39" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G39" s="11" t="inlineStr">
@@ -3513,69 +3509,69 @@
       </c>
       <c r="H39" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I39" s="11" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="J39" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K39" s="11" t="n">
-        <v>1.5</v>
+        <v>0.75</v>
       </c>
       <c r="L39" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33509</t>
+          <t>PDMDEP-33703</t>
         </is>
       </c>
       <c r="M39" s="11" t="inlineStr">
         <is>
-          <t>00168117</t>
+          <t>00169363</t>
         </is>
       </c>
       <c r="N39" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O39" s="12" t="n">
-        <v>691.9</v>
+        <v>540</v>
       </c>
       <c r="P39" s="12" t="n">
-        <v>461.27</v>
+        <v>720</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33471</t>
+          <t>PDMDEP-33610</t>
         </is>
       </c>
       <c r="B40" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE D AUCH] - FDS Facture LiS</t>
+          <t xml:space="preserve">[COMMUNE DE MORLAIX] - Migration GEODP Placier hors matériel </t>
         </is>
       </c>
       <c r="C40" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D40" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE D AUCH</t>
+          <t>COMMUNE DE MORLAIX</t>
         </is>
       </c>
       <c r="E40" s="14" t="inlineStr">
         <is>
-          <t>FDS Facture LiS</t>
+          <t xml:space="preserve">MIGRATION GEODP PLACIER hors matériel </t>
         </is>
       </c>
       <c r="F40" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G40" s="14" t="inlineStr">
@@ -3585,35 +3581,35 @@
       </c>
       <c r="H40" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I40" s="14" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="J40" s="14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K40" s="14" t="n">
         <v>0</v>
       </c>
       <c r="L40" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33475</t>
+          <t>PDMDEP-33616</t>
         </is>
       </c>
       <c r="M40" s="14" t="inlineStr">
         <is>
-          <t>00168025</t>
+          <t>00169015</t>
         </is>
       </c>
       <c r="N40" s="15" t="n">
-        <v>171.4</v>
-      </c>
-      <c r="O40" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O40" s="15" t="n">
+        <v>505</v>
       </c>
       <c r="P40" s="15" t="n">
         <v>0</v>
@@ -3622,27 +3618,27 @@
     <row r="41">
       <c r="A41" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33431</t>
+          <t>PDMDEP-33597</t>
         </is>
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE VERSAILLES] - Migration multi-modules (hors taxi) </t>
+          <t>[Commune de Trets] - Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
         </is>
       </c>
       <c r="C41" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D41" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">COMMUNE DE VERSAILLES </t>
+          <t>Commune de Trets</t>
         </is>
       </c>
       <c r="E41" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration multi-modules (hors taxi) </t>
+          <t>Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
         </is>
       </c>
       <c r="F41" s="11" t="inlineStr">
@@ -3657,35 +3653,35 @@
       </c>
       <c r="H41" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I41" s="11" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="J41" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K41" s="11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L41" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33440</t>
+          <t>PDMDEP-33605</t>
         </is>
       </c>
       <c r="M41" s="11" t="inlineStr">
         <is>
-          <t>00166923</t>
+          <t>00168993</t>
         </is>
       </c>
       <c r="N41" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O41" s="12" t="n">
-        <v>3339.2</v>
+        <v>0</v>
       </c>
       <c r="P41" s="12" t="n">
         <v>0</v>
@@ -3694,12 +3690,12 @@
     <row r="42">
       <c r="A42" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33395</t>
+          <t>PDMDEP-33500</t>
         </is>
       </c>
       <c r="B42" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE MONTBELIARD] - Mise en place paiement CB sur PAX présent sur la commune </t>
+          <t xml:space="preserve">[Mairie de Carcès ] - GEODP PLACIER avec PAIEMENT CB </t>
         </is>
       </c>
       <c r="C42" s="14" t="inlineStr">
@@ -3709,12 +3705,12 @@
       </c>
       <c r="D42" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTBELIARD</t>
+          <t xml:space="preserve">Mairie de Carcès </t>
         </is>
       </c>
       <c r="E42" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mise en place paiement CB sur PAX présent sur la commune </t>
+          <t xml:space="preserve">GEODP PLACIER avec PAIEMENT CB </t>
         </is>
       </c>
       <c r="F42" s="14" t="inlineStr">
@@ -3729,69 +3725,69 @@
       </c>
       <c r="H42" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I42" s="14" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="J42" s="14" t="n">
         <v>4</v>
       </c>
       <c r="K42" s="14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="L42" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33401</t>
+          <t>PDMDEP-33509</t>
         </is>
       </c>
       <c r="M42" s="14" t="inlineStr">
         <is>
-          <t>00167624</t>
+          <t>00168117</t>
         </is>
       </c>
       <c r="N42" s="15" t="n">
-        <v>344</v>
-      </c>
-      <c r="O42" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O42" s="15" t="n">
+        <v>691.9</v>
       </c>
       <c r="P42" s="15" t="n">
-        <v>0</v>
+        <v>461.27</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33266</t>
+          <t>PDMDEP-33471</t>
         </is>
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>[MAIRIE DE CAPBRETON] - Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
+          <t>[COMMUNE D AUCH] - FDS Facture LiS</t>
         </is>
       </c>
       <c r="C43" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D43" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE CAPBRETON</t>
+          <t>COMMUNE D AUCH</t>
         </is>
       </c>
       <c r="E43" s="11" t="inlineStr">
         <is>
-          <t>Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
+          <t>FDS Facture LiS</t>
         </is>
       </c>
       <c r="F43" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G43" s="11" t="inlineStr">
@@ -3806,7 +3802,7 @@
       </c>
       <c r="I43" s="11" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="J43" s="11" t="n">
@@ -3817,16 +3813,16 @@
       </c>
       <c r="L43" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33272</t>
+          <t>PDMDEP-33475</t>
         </is>
       </c>
       <c r="M43" s="11" t="inlineStr">
         <is>
-          <t>00166910</t>
+          <t>00168025</t>
         </is>
       </c>
       <c r="N43" s="12" t="n">
-        <v>500</v>
+        <v>171.4</v>
       </c>
       <c r="O43" s="16" t="n">
         <v>0</v>
@@ -3838,27 +3834,27 @@
     <row r="44">
       <c r="A44" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33239</t>
+          <t>PDMDEP-33431</t>
         </is>
       </c>
       <c r="B44" s="14" t="inlineStr">
         <is>
-          <t>[MAIRIE DE LODEVE] - Migracier activité Placier vers Geodp V2</t>
+          <t xml:space="preserve">[COMMUNE DE VERSAILLES] - Migration multi-modules (hors taxi) </t>
         </is>
       </c>
       <c r="C44" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D44" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE LODEVE</t>
+          <t xml:space="preserve">COMMUNE DE VERSAILLES </t>
         </is>
       </c>
       <c r="E44" s="14" t="inlineStr">
         <is>
-          <t>Migracier activité Placier vers Geodp V2</t>
+          <t xml:space="preserve">Migration multi-modules (hors taxi) </t>
         </is>
       </c>
       <c r="F44" s="14" t="inlineStr">
@@ -3878,7 +3874,7 @@
       </c>
       <c r="I44" s="14" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="J44" s="14" t="n">
@@ -3889,19 +3885,19 @@
       </c>
       <c r="L44" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33245</t>
+          <t>PDMDEP-33440</t>
         </is>
       </c>
       <c r="M44" s="14" t="inlineStr">
         <is>
-          <t>00166748</t>
+          <t>00166923</t>
         </is>
       </c>
       <c r="N44" s="15" t="n">
-        <v>149</v>
-      </c>
-      <c r="O44" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O44" s="15" t="n">
+        <v>3339.2</v>
       </c>
       <c r="P44" s="15" t="n">
         <v>0</v>
@@ -3910,32 +3906,32 @@
     <row r="45">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33227</t>
+          <t>PDMDEP-33395</t>
         </is>
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>[METROPOLE EUROPEENNE DE LILLE] - MEL Crédits 21 heures (3j)     mai 2026</t>
+          <t xml:space="preserve">[COMMUNE DE MONTBELIARD] - Mise en place paiement CB sur PAX présent sur la commune </t>
         </is>
       </c>
       <c r="C45" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D45" s="11" t="inlineStr">
         <is>
-          <t>METROPOLE EUROPEENNE DE LILLE</t>
+          <t>COMMUNE DE MONTBELIARD</t>
         </is>
       </c>
       <c r="E45" s="11" t="inlineStr">
         <is>
-          <t>21 crédits d'heure</t>
+          <t xml:space="preserve">Mise en place paiement CB sur PAX présent sur la commune </t>
         </is>
       </c>
       <c r="F45" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G45" s="11" t="inlineStr">
@@ -3950,64 +3946,64 @@
       </c>
       <c r="I45" s="11" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="J45" s="11" t="n">
         <v>4</v>
       </c>
       <c r="K45" s="11" t="n">
-        <v>0.62</v>
+        <v>0</v>
       </c>
       <c r="L45" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33232</t>
+          <t>PDMDEP-33401</t>
         </is>
       </c>
       <c r="M45" s="11" t="inlineStr">
         <is>
-          <t>00166708</t>
+          <t>00167624</t>
         </is>
       </c>
       <c r="N45" s="12" t="n">
-        <v>625</v>
+        <v>344</v>
       </c>
       <c r="O45" s="16" t="n">
-        <v>337.5</v>
+        <v>0</v>
       </c>
       <c r="P45" s="12" t="n">
-        <v>540</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33227</t>
+          <t>PDMDEP-33266</t>
         </is>
       </c>
       <c r="B46" s="14" t="inlineStr">
         <is>
-          <t>[METROPOLE EUROPEENNE DE LILLE] - MEL Crédits 21 heures (3j)     mai 2026</t>
+          <t>[MAIRIE DE CAPBRETON] - Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
         </is>
       </c>
       <c r="C46" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D46" s="14" t="inlineStr">
         <is>
-          <t>METROPOLE EUROPEENNE DE LILLE</t>
+          <t>MAIRIE DE CAPBRETON</t>
         </is>
       </c>
       <c r="E46" s="14" t="inlineStr">
         <is>
-          <t>21 crédits d'heure</t>
+          <t>Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
         </is>
       </c>
       <c r="F46" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G46" s="14" t="inlineStr">
@@ -4022,44 +4018,44 @@
       </c>
       <c r="I46" s="14" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="J46" s="14" t="n">
         <v>4</v>
       </c>
       <c r="K46" s="14" t="n">
-        <v>0.62</v>
+        <v>0</v>
       </c>
       <c r="L46" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33231</t>
+          <t>PDMDEP-33272</t>
         </is>
       </c>
       <c r="M46" s="14" t="inlineStr">
         <is>
-          <t>00166707</t>
+          <t>00166910</t>
         </is>
       </c>
       <c r="N46" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O46" s="15" t="n">
-        <v>16</v>
+        <v>500</v>
+      </c>
+      <c r="O46" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P46" s="15" t="n">
-        <v>25.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33170</t>
+          <t>PDMDEP-33239</t>
         </is>
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>[Commune de Bonneville] - MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
+          <t>[MAIRIE DE LODEVE] - Migracier activité Placier vers Geodp V2</t>
         </is>
       </c>
       <c r="C47" s="11" t="inlineStr">
@@ -4069,12 +4065,12 @@
       </c>
       <c r="D47" s="11" t="inlineStr">
         <is>
-          <t>Commune de Bonneville</t>
+          <t>MAIRIE DE LODEVE</t>
         </is>
       </c>
       <c r="E47" s="11" t="inlineStr">
         <is>
-          <t>MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
+          <t>Migracier activité Placier vers Geodp V2</t>
         </is>
       </c>
       <c r="F47" s="11" t="inlineStr">
@@ -4094,7 +4090,7 @@
       </c>
       <c r="I47" s="11" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="J47" s="11" t="n">
@@ -4105,16 +4101,16 @@
       </c>
       <c r="L47" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33177</t>
+          <t>PDMDEP-33245</t>
         </is>
       </c>
       <c r="M47" s="11" t="inlineStr">
         <is>
-          <t>00166356</t>
+          <t>00166748</t>
         </is>
       </c>
       <c r="N47" s="12" t="n">
-        <v>910</v>
+        <v>149</v>
       </c>
       <c r="O47" s="16" t="n">
         <v>0</v>
@@ -4126,32 +4122,32 @@
     <row r="48">
       <c r="A48" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33064</t>
+          <t>PDMDEP-33227</t>
         </is>
       </c>
       <c r="B48" s="14" t="inlineStr">
         <is>
-          <t>[MAIRIE DE LONGWY] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>[METROPOLE EUROPEENNE DE LILLE] - MEL Crédits 21 heures (3j)     mai 2026</t>
         </is>
       </c>
       <c r="C48" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D48" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE LONGWY</t>
+          <t>METROPOLE EUROPEENNE DE LILLE</t>
         </is>
       </c>
       <c r="E48" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>21 crédits d'heure</t>
         </is>
       </c>
       <c r="F48" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G48" s="14" t="inlineStr">
@@ -4161,49 +4157,49 @@
       </c>
       <c r="H48" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I48" s="14" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="J48" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K48" s="14" t="n">
-        <v>2</v>
+        <v>0.62</v>
       </c>
       <c r="L48" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33073</t>
+          <t>PDMDEP-33232</t>
         </is>
       </c>
       <c r="M48" s="14" t="inlineStr">
         <is>
-          <t>00165708</t>
+          <t>00166708</t>
         </is>
       </c>
       <c r="N48" s="15" t="n">
-        <v>1207</v>
+        <v>625</v>
       </c>
       <c r="O48" s="16" t="n">
-        <v>0</v>
+        <v>337.5</v>
       </c>
       <c r="P48" s="15" t="n">
-        <v>0</v>
+        <v>540</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32984</t>
+          <t>PDMDEP-33227</t>
         </is>
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTELIMAR] - Interface Civil net finance avec Littéralis</t>
+          <t>[METROPOLE EUROPEENNE DE LILLE] - MEL Crédits 21 heures (3j)     mai 2026</t>
         </is>
       </c>
       <c r="C49" s="11" t="inlineStr">
@@ -4213,12 +4209,12 @@
       </c>
       <c r="D49" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTELIMAR</t>
+          <t>METROPOLE EUROPEENNE DE LILLE</t>
         </is>
       </c>
       <c r="E49" s="11" t="inlineStr">
         <is>
-          <t>Interface Civil net finance avec Littéralis</t>
+          <t>21 crédits d'heure</t>
         </is>
       </c>
       <c r="F49" s="11" t="inlineStr">
@@ -4238,64 +4234,64 @@
       </c>
       <c r="I49" s="11" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="J49" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K49" s="11" t="n">
-        <v>0</v>
+        <v>0.62</v>
       </c>
       <c r="L49" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32990</t>
+          <t>PDMDEP-33231</t>
         </is>
       </c>
       <c r="M49" s="11" t="inlineStr">
         <is>
-          <t>00165270</t>
+          <t>00166707</t>
         </is>
       </c>
       <c r="N49" s="12" t="n">
-        <v>500</v>
-      </c>
-      <c r="O49" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O49" s="12" t="n">
+        <v>16</v>
       </c>
       <c r="P49" s="12" t="n">
-        <v>0</v>
+        <v>25.6</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32768</t>
+          <t>PDMDEP-33170</t>
         </is>
       </c>
       <c r="B50" s="14" t="inlineStr">
         <is>
-          <t>[VILLE DE REIMS] - MV app/ infra + màj carto - ON prem</t>
+          <t>[Commune de Bonneville] - MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
         </is>
       </c>
       <c r="C50" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D50" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE REIMS</t>
+          <t>Commune de Bonneville</t>
         </is>
       </c>
       <c r="E50" s="14" t="inlineStr">
         <is>
-          <t>MV app/ infra + màj carto</t>
+          <t>MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
         </is>
       </c>
       <c r="F50" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G50" s="14" t="inlineStr">
@@ -4305,34 +4301,34 @@
       </c>
       <c r="H50" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I50" s="14" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="J50" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K50" s="14" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L50" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32772</t>
+          <t>PDMDEP-33177</t>
         </is>
       </c>
       <c r="M50" s="14" t="inlineStr">
         <is>
-          <t>00163806</t>
+          <t>00166356</t>
         </is>
       </c>
       <c r="N50" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O50" s="15" t="n">
+        <v>910</v>
+      </c>
+      <c r="O50" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P50" s="15" t="n">
@@ -4342,32 +4338,32 @@
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32552</t>
+          <t>PDMDEP-33064</t>
         </is>
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>[CHALON SUR SAONE] - Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
+          <t>[MAIRIE DE LONGWY] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE CHALON SUR SAONE</t>
+          <t>MAIRIE DE LONGWY</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
+          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="F51" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G51" s="11" t="inlineStr">
@@ -4377,32 +4373,32 @@
       </c>
       <c r="H51" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I51" s="11" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="J51" s="11" t="n">
         <v>5</v>
       </c>
       <c r="K51" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L51" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32556</t>
+          <t>PDMDEP-33073</t>
         </is>
       </c>
       <c r="M51" s="11" t="inlineStr">
         <is>
-          <t>00162313</t>
+          <t>00165708</t>
         </is>
       </c>
       <c r="N51" s="12" t="n">
-        <v>142.1</v>
+        <v>1207</v>
       </c>
       <c r="O51" s="16" t="n">
         <v>0</v>
@@ -4414,32 +4410,32 @@
     <row r="52">
       <c r="A52" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32461</t>
+          <t>PDMDEP-32984</t>
         </is>
       </c>
       <c r="B52" s="14" t="inlineStr">
         <is>
-          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
+          <t>[COMMUNE DE MONTELIMAR] - Interface Civil net finance avec Littéralis</t>
         </is>
       </c>
       <c r="C52" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D52" s="14" t="inlineStr">
         <is>
-          <t>NANTES METROPOLE - VDC</t>
+          <t>COMMUNE DE MONTELIMAR</t>
         </is>
       </c>
       <c r="E52" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2</t>
+          <t>Interface Civil net finance avec Littéralis</t>
         </is>
       </c>
       <c r="F52" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G52" s="14" t="inlineStr">
@@ -4449,32 +4445,32 @@
       </c>
       <c r="H52" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I52" s="14" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="J52" s="14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K52" s="14" t="n">
         <v>0</v>
       </c>
       <c r="L52" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32470</t>
+          <t>PDMDEP-32990</t>
         </is>
       </c>
       <c r="M52" s="14" t="inlineStr">
         <is>
-          <t>00161950</t>
+          <t>00165270</t>
         </is>
       </c>
       <c r="N52" s="15" t="n">
-        <v>2335</v>
+        <v>500</v>
       </c>
       <c r="O52" s="16" t="n">
         <v>0</v>
@@ -4486,27 +4482,27 @@
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32442</t>
+          <t>PDMDEP-32768</t>
         </is>
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE CHAMBERY] - Montée de version LiEx Test et prod  (03/26)</t>
+          <t>[VILLE DE REIMS] - MV app/ infra + màj carto - ON prem</t>
         </is>
       </c>
       <c r="C53" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D53" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHAMBERY</t>
+          <t>VILLE DE REIMS</t>
         </is>
       </c>
       <c r="E53" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Montée de version LiEx Test et prod </t>
+          <t>MV app/ infra + màj carto</t>
         </is>
       </c>
       <c r="F53" s="11" t="inlineStr">
@@ -4526,23 +4522,23 @@
       </c>
       <c r="I53" s="11" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="J53" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K53" s="11" t="n">
         <v>0.25</v>
       </c>
       <c r="L53" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32446</t>
+          <t>PDMDEP-32772</t>
         </is>
       </c>
       <c r="M53" s="11" t="inlineStr">
         <is>
-          <t>00161842</t>
+          <t>00163806</t>
         </is>
       </c>
       <c r="N53" s="12" t="n">
@@ -4558,32 +4554,32 @@
     <row r="54">
       <c r="A54" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32366</t>
+          <t>PDMDEP-32552</t>
         </is>
       </c>
       <c r="B54" s="14" t="inlineStr">
         <is>
-          <t>[Commune de Pleneuf Val André] - Migration de GEODP-Placier simple</t>
+          <t>[CHALON SUR SAONE] - Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
         </is>
       </c>
       <c r="C54" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D54" s="14" t="inlineStr">
         <is>
-          <t>Commune de Pleneuf Val André</t>
+          <t>VILLE DE CHALON SUR SAONE</t>
         </is>
       </c>
       <c r="E54" s="14" t="inlineStr">
         <is>
-          <t>Migration de GEODP-Placier simple</t>
+          <t>Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
         </is>
       </c>
       <c r="F54" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G54" s="14" t="inlineStr">
@@ -4593,34 +4589,34 @@
       </c>
       <c r="H54" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I54" s="14" t="inlineStr">
         <is>
-          <t>26/03/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="J54" s="14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K54" s="14" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L54" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32372</t>
+          <t>PDMDEP-32556</t>
         </is>
       </c>
       <c r="M54" s="14" t="inlineStr">
         <is>
-          <t>00161594</t>
+          <t>00162313</t>
         </is>
       </c>
       <c r="N54" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O54" s="15" t="n">
+        <v>142.1</v>
+      </c>
+      <c r="O54" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P54" s="15" t="n">
@@ -4630,27 +4626,27 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32331</t>
+          <t>PDMDEP-32461</t>
         </is>
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
+          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="C55" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D55" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
+          <t>NANTES METROPOLE - VDC</t>
         </is>
       </c>
       <c r="E55" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GEODP Placier </t>
+          <t>Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="F55" s="11" t="inlineStr">
@@ -4670,7 +4666,7 @@
       </c>
       <c r="I55" s="11" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
       <c r="J55" s="11" t="n">
@@ -4681,16 +4677,16 @@
       </c>
       <c r="L55" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32340</t>
+          <t>PDMDEP-32470</t>
         </is>
       </c>
       <c r="M55" s="11" t="inlineStr">
         <is>
-          <t>00161493</t>
+          <t>00161950</t>
         </is>
       </c>
       <c r="N55" s="12" t="n">
-        <v>450</v>
+        <v>2335</v>
       </c>
       <c r="O55" s="16" t="n">
         <v>0</v>
@@ -4702,12 +4698,12 @@
     <row r="56">
       <c r="A56" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32264</t>
+          <t>PDMDEP-32442</t>
         </is>
       </c>
       <c r="B56" s="14" t="inlineStr">
         <is>
-          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
+          <t>[COMMUNE DE CHAMBERY] - Montée de version LiEx Test et prod  (03/26)</t>
         </is>
       </c>
       <c r="C56" s="14" t="inlineStr">
@@ -4717,12 +4713,12 @@
       </c>
       <c r="D56" s="14" t="inlineStr">
         <is>
-          <t>CA DU NIORTAIS</t>
+          <t>COMMUNE DE CHAMBERY</t>
         </is>
       </c>
       <c r="E56" s="14" t="inlineStr">
         <is>
-          <t>Modélisation</t>
+          <t xml:space="preserve">Montée de version LiEx Test et prod </t>
         </is>
       </c>
       <c r="F56" s="14" t="inlineStr">
@@ -4742,44 +4738,44 @@
       </c>
       <c r="I56" s="14" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>27/03/2026</t>
         </is>
       </c>
       <c r="J56" s="14" t="n">
         <v>6</v>
       </c>
       <c r="K56" s="14" t="n">
-        <v>2</v>
+        <v>0.25</v>
       </c>
       <c r="L56" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32268</t>
+          <t>PDMDEP-32446</t>
         </is>
       </c>
       <c r="M56" s="14" t="inlineStr">
         <is>
-          <t>00161073</t>
+          <t>00161842</t>
         </is>
       </c>
       <c r="N56" s="15" t="n">
-        <v>910</v>
-      </c>
-      <c r="O56" s="16" t="n">
-        <v>136.5</v>
+        <v>0</v>
+      </c>
+      <c r="O56" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="P56" s="15" t="n">
-        <v>68.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32086</t>
+          <t>PDMDEP-32366</t>
         </is>
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE VITRY LE FRANCOIS] - Acquisition Geodp Placier</t>
+          <t>[Commune de Pleneuf Val André] - Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="C57" s="11" t="inlineStr">
@@ -4789,12 +4785,12 @@
       </c>
       <c r="D57" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY LE FRANCOIS</t>
+          <t>Commune de Pleneuf Val André</t>
         </is>
       </c>
       <c r="E57" s="11" t="inlineStr">
         <is>
-          <t>Acquisition Geodp Placier</t>
+          <t>Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="F57" s="11" t="inlineStr">
@@ -4809,34 +4805,34 @@
       </c>
       <c r="H57" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I57" s="11" t="inlineStr">
         <is>
-          <t>17/03/2026</t>
+          <t>26/03/2026</t>
         </is>
       </c>
       <c r="J57" s="11" t="n">
         <v>6</v>
       </c>
       <c r="K57" s="11" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L57" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32095</t>
+          <t>PDMDEP-32372</t>
         </is>
       </c>
       <c r="M57" s="11" t="inlineStr">
         <is>
-          <t>00160474</t>
+          <t>00161594</t>
         </is>
       </c>
       <c r="N57" s="12" t="n">
-        <v>590.15</v>
-      </c>
-      <c r="O57" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P57" s="12" t="n">
@@ -4846,12 +4842,12 @@
     <row r="58">
       <c r="A58" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31996</t>
+          <t>PDMDEP-32331</t>
         </is>
       </c>
       <c r="B58" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
+          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
         </is>
       </c>
       <c r="C58" s="14" t="inlineStr">
@@ -4861,12 +4857,12 @@
       </c>
       <c r="D58" s="14" t="inlineStr">
         <is>
-          <t>Commune de Cluny</t>
+          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
         </is>
       </c>
       <c r="E58" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
+          <t xml:space="preserve">Migration GEODP Placier </t>
         </is>
       </c>
       <c r="F58" s="14" t="inlineStr">
@@ -4881,12 +4877,12 @@
       </c>
       <c r="H58" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I58" s="14" t="inlineStr">
         <is>
-          <t>12/03/2026</t>
+          <t>25/03/2026</t>
         </is>
       </c>
       <c r="J58" s="14" t="n">
@@ -4897,16 +4893,16 @@
       </c>
       <c r="L58" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32002</t>
+          <t>PDMDEP-32340</t>
         </is>
       </c>
       <c r="M58" s="14" t="inlineStr">
         <is>
-          <t>00160078</t>
+          <t>00161493</t>
         </is>
       </c>
       <c r="N58" s="15" t="n">
-        <v>285</v>
+        <v>450</v>
       </c>
       <c r="O58" s="16" t="n">
         <v>0</v>
@@ -4918,12 +4914,12 @@
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31967</t>
+          <t>PDMDEP-32264</t>
         </is>
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU LOT -CD46] - Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
+          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
         </is>
       </c>
       <c r="C59" s="11" t="inlineStr">
@@ -4933,12 +4929,12 @@
       </c>
       <c r="D59" s="11" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU LOT -CD46</t>
+          <t>CA DU NIORTAIS</t>
         </is>
       </c>
       <c r="E59" s="11" t="inlineStr">
         <is>
-          <t>Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
+          <t>Modélisation</t>
         </is>
       </c>
       <c r="F59" s="11" t="inlineStr">
@@ -4958,64 +4954,64 @@
       </c>
       <c r="I59" s="11" t="inlineStr">
         <is>
-          <t>11/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
       <c r="J59" s="11" t="n">
         <v>6</v>
       </c>
       <c r="K59" s="11" t="n">
-        <v>0.75</v>
+        <v>2</v>
       </c>
       <c r="L59" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31971</t>
+          <t>PDMDEP-32268</t>
         </is>
       </c>
       <c r="M59" s="11" t="inlineStr">
         <is>
-          <t>00159863</t>
+          <t>00161073</t>
         </is>
       </c>
       <c r="N59" s="12" t="n">
-        <v>1325</v>
+        <v>910</v>
       </c>
       <c r="O59" s="16" t="n">
-        <v>0</v>
+        <v>136.5</v>
       </c>
       <c r="P59" s="12" t="n">
-        <v>0</v>
+        <v>68.25</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31947</t>
+          <t>PDMDEP-32086</t>
         </is>
       </c>
       <c r="B60" s="14" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
+          <t>[COMMUNE DE VITRY LE FRANCOIS] - Acquisition Geodp Placier</t>
         </is>
       </c>
       <c r="C60" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D60" s="14" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
+          <t>COMMUNE DE VITRY LE FRANCOIS</t>
         </is>
       </c>
       <c r="E60" s="14" t="inlineStr">
         <is>
-          <t>SSO/LDAP</t>
+          <t>Acquisition Geodp Placier</t>
         </is>
       </c>
       <c r="F60" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G60" s="14" t="inlineStr">
@@ -5025,12 +5021,12 @@
       </c>
       <c r="H60" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I60" s="14" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>17/03/2026</t>
         </is>
       </c>
       <c r="J60" s="14" t="n">
@@ -5041,16 +5037,16 @@
       </c>
       <c r="L60" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31951</t>
+          <t>PDMDEP-32095</t>
         </is>
       </c>
       <c r="M60" s="14" t="inlineStr">
         <is>
-          <t>00159724</t>
+          <t>00160474</t>
         </is>
       </c>
       <c r="N60" s="15" t="n">
-        <v>120</v>
+        <v>590.15</v>
       </c>
       <c r="O60" s="16" t="n">
         <v>0</v>
@@ -5062,12 +5058,12 @@
     <row r="61">
       <c r="A61" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31908</t>
+          <t>PDMDEP-32065</t>
         </is>
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t>[Commune de GUINGAMP] - Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
+          <t>[COMMUNE DE MONTBRISON] - Migration GeODP Placier + Ajout Civil Net Finance</t>
         </is>
       </c>
       <c r="C61" s="11" t="inlineStr">
@@ -5077,12 +5073,12 @@
       </c>
       <c r="D61" s="11" t="inlineStr">
         <is>
-          <t>Commune de GUINGAMP</t>
+          <t>COMMUNE DE MONTBRISON</t>
         </is>
       </c>
       <c r="E61" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
+          <t>Migration GeODP Placier + Ajout Civil Net Finance</t>
         </is>
       </c>
       <c r="F61" s="11" t="inlineStr">
@@ -5102,7 +5098,7 @@
       </c>
       <c r="I61" s="11" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="J61" s="11" t="n">
@@ -5113,19 +5109,19 @@
       </c>
       <c r="L61" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31917</t>
+          <t>PDMDEP-32074</t>
         </is>
       </c>
       <c r="M61" s="11" t="inlineStr">
         <is>
-          <t>00159608</t>
+          <t>00160409</t>
         </is>
       </c>
       <c r="N61" s="12" t="n">
-        <v>588</v>
-      </c>
-      <c r="O61" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O61" s="12" t="n">
+        <v>823.65</v>
       </c>
       <c r="P61" s="12" t="n">
         <v>0</v>
@@ -5134,27 +5130,27 @@
     <row r="62">
       <c r="A62" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31649</t>
+          <t>PDMDEP-31996</t>
         </is>
       </c>
       <c r="B62" s="14" t="inlineStr">
         <is>
-          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
+          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="C62" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D62" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE GUILLESTRE</t>
+          <t>Commune de Cluny</t>
         </is>
       </c>
       <c r="E62" s="14" t="inlineStr">
         <is>
-          <t>GeoDP Placier</t>
+          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="F62" s="14" t="inlineStr">
@@ -5169,32 +5165,32 @@
       </c>
       <c r="H62" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I62" s="14" t="inlineStr">
         <is>
-          <t>27/02/2026</t>
+          <t>12/03/2026</t>
         </is>
       </c>
       <c r="J62" s="14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K62" s="14" t="n">
         <v>0</v>
       </c>
       <c r="L62" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31658</t>
+          <t>PDMDEP-32002</t>
         </is>
       </c>
       <c r="M62" s="14" t="inlineStr">
         <is>
-          <t>00158175</t>
+          <t>00160078</t>
         </is>
       </c>
       <c r="N62" s="15" t="n">
-        <v>203.5</v>
+        <v>285</v>
       </c>
       <c r="O62" s="16" t="n">
         <v>0</v>
@@ -5206,32 +5202,32 @@
     <row r="63">
       <c r="A63" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31589</t>
+          <t>PDMDEP-31967</t>
         </is>
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE LEVALLOIS PERRET] - Migration GEODP - 3 MODULES + mise en service export finance </t>
+          <t>[DEPARTEMENT DU LOT -CD46] - Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
         </is>
       </c>
       <c r="C63" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D63" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE LEVALLOIS PERRET</t>
+          <t>DEPARTEMENT DU LOT -CD46</t>
         </is>
       </c>
       <c r="E63" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GEODP - 3 MODULES + mise en service export finance </t>
+          <t>Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
         </is>
       </c>
       <c r="F63" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G63" s="11" t="inlineStr">
@@ -5241,32 +5237,32 @@
       </c>
       <c r="H63" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I63" s="11" t="inlineStr">
         <is>
-          <t>26/02/2026</t>
+          <t>11/03/2026</t>
         </is>
       </c>
       <c r="J63" s="11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K63" s="11" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="L63" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31596</t>
+          <t>PDMDEP-31971</t>
         </is>
       </c>
       <c r="M63" s="11" t="inlineStr">
         <is>
-          <t>00157967</t>
+          <t>00159863</t>
         </is>
       </c>
       <c r="N63" s="12" t="n">
-        <v>300</v>
+        <v>1325</v>
       </c>
       <c r="O63" s="16" t="n">
         <v>0</v>
@@ -5278,12 +5274,12 @@
     <row r="64">
       <c r="A64" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31540</t>
+          <t>PDMDEP-31947</t>
         </is>
       </c>
       <c r="B64" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTELIMAR] - Modélisation LiEx et redevances</t>
+          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
         </is>
       </c>
       <c r="C64" s="14" t="inlineStr">
@@ -5293,12 +5289,12 @@
       </c>
       <c r="D64" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTELIMAR</t>
+          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
         </is>
       </c>
       <c r="E64" s="14" t="inlineStr">
         <is>
-          <t>Modélisation LiEx</t>
+          <t>SSO/LDAP</t>
         </is>
       </c>
       <c r="F64" s="14" t="inlineStr">
@@ -5318,27 +5314,27 @@
       </c>
       <c r="I64" s="14" t="inlineStr">
         <is>
-          <t>24/02/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
       <c r="J64" s="14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K64" s="14" t="n">
         <v>0</v>
       </c>
       <c r="L64" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31546</t>
+          <t>PDMDEP-31951</t>
         </is>
       </c>
       <c r="M64" s="14" t="inlineStr">
         <is>
-          <t>00157816</t>
+          <t>00159724</t>
         </is>
       </c>
       <c r="N64" s="15" t="n">
-        <v>700</v>
+        <v>120</v>
       </c>
       <c r="O64" s="16" t="n">
         <v>0</v>
@@ -5350,12 +5346,12 @@
     <row r="65">
       <c r="A65" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31351</t>
+          <t>PDMDEP-31908</t>
         </is>
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
+          <t>[Commune de GUINGAMP] - Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
         </is>
       </c>
       <c r="C65" s="11" t="inlineStr">
@@ -5365,12 +5361,12 @@
       </c>
       <c r="D65" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
+          <t>Commune de GUINGAMP</t>
         </is>
       </c>
       <c r="E65" s="11" t="inlineStr">
         <is>
-          <t>Migration vers GeoDP V2</t>
+          <t>Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
         </is>
       </c>
       <c r="F65" s="11" t="inlineStr">
@@ -5390,27 +5386,27 @@
       </c>
       <c r="I65" s="11" t="inlineStr">
         <is>
-          <t>17/02/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
       <c r="J65" s="11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K65" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L65" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31360</t>
+          <t>PDMDEP-31917</t>
         </is>
       </c>
       <c r="M65" s="11" t="inlineStr">
         <is>
-          <t>00157041</t>
+          <t>00159608</t>
         </is>
       </c>
       <c r="N65" s="12" t="n">
-        <v>210</v>
+        <v>588</v>
       </c>
       <c r="O65" s="16" t="n">
         <v>0</v>
@@ -5422,12 +5418,12 @@
     <row r="66">
       <c r="A66" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31319</t>
+          <t>PDMDEP-31812</t>
         </is>
       </c>
       <c r="B66" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LARMOR PLAGE] - Migration de GEODP-Placier simple</t>
+          <t>[COMMUNE PROVINS] - Migration V2 classique</t>
         </is>
       </c>
       <c r="C66" s="14" t="inlineStr">
@@ -5437,12 +5433,12 @@
       </c>
       <c r="D66" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE LARMOR PLAGE</t>
+          <t>COMMUNE PROVINS</t>
         </is>
       </c>
       <c r="E66" s="14" t="inlineStr">
         <is>
-          <t>Migration de GEODP-Placier simple</t>
+          <t>Migration V2 classique</t>
         </is>
       </c>
       <c r="F66" s="14" t="inlineStr">
@@ -5462,30 +5458,30 @@
       </c>
       <c r="I66" s="14" t="inlineStr">
         <is>
-          <t>17/02/2026</t>
+          <t>06/03/2026</t>
         </is>
       </c>
       <c r="J66" s="14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K66" s="14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L66" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31328</t>
+          <t>PDMDEP-31821</t>
         </is>
       </c>
       <c r="M66" s="14" t="inlineStr">
         <is>
-          <t>00156518</t>
+          <t>00159471</t>
         </is>
       </c>
       <c r="N66" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O66" s="15" t="n">
-        <v>281</v>
+        <v>0</v>
       </c>
       <c r="P66" s="15" t="n">
         <v>0</v>
@@ -5494,27 +5490,27 @@
     <row r="67">
       <c r="A67" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31188</t>
+          <t>PDMDEP-31649</t>
         </is>
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
+          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
         </is>
       </c>
       <c r="C67" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D67" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE D HENDAYE</t>
+          <t>MAIRIE DE GUILLESTRE</t>
         </is>
       </c>
       <c r="E67" s="11" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>GeoDP Placier</t>
         </is>
       </c>
       <c r="F67" s="11" t="inlineStr">
@@ -5529,12 +5525,12 @@
       </c>
       <c r="H67" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I67" s="11" t="inlineStr">
         <is>
-          <t>12/02/2026</t>
+          <t>27/02/2026</t>
         </is>
       </c>
       <c r="J67" s="11" t="n">
@@ -5545,16 +5541,16 @@
       </c>
       <c r="L67" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31197</t>
+          <t>PDMDEP-31658</t>
         </is>
       </c>
       <c r="M67" s="11" t="inlineStr">
         <is>
-          <t>00156556</t>
+          <t>00158175</t>
         </is>
       </c>
       <c r="N67" s="12" t="n">
-        <v>130</v>
+        <v>203.5</v>
       </c>
       <c r="O67" s="16" t="n">
         <v>0</v>
@@ -5566,27 +5562,27 @@
     <row r="68">
       <c r="A68" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31036</t>
+          <t>PDMDEP-31589</t>
         </is>
       </c>
       <c r="B68" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
+          <t xml:space="preserve">[COMMUNE DE LEVALLOIS PERRET] - Migration GEODP - 3 MODULES + mise en service export finance </t>
         </is>
       </c>
       <c r="C68" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D68" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE SARLAT LA CANEDA</t>
+          <t>COMMUNE DE LEVALLOIS PERRET</t>
         </is>
       </c>
       <c r="E68" s="14" t="inlineStr">
         <is>
-          <t>Migration V2 classique + abo CB</t>
+          <t xml:space="preserve">Migration GEODP - 3 MODULES + mise en service export finance </t>
         </is>
       </c>
       <c r="F68" s="14" t="inlineStr">
@@ -5606,7 +5602,7 @@
       </c>
       <c r="I68" s="14" t="inlineStr">
         <is>
-          <t>10/02/2026</t>
+          <t>26/02/2026</t>
         </is>
       </c>
       <c r="J68" s="14" t="n">
@@ -5617,16 +5613,16 @@
       </c>
       <c r="L68" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31045</t>
+          <t>PDMDEP-31596</t>
         </is>
       </c>
       <c r="M68" s="14" t="inlineStr">
         <is>
-          <t>00156095</t>
+          <t>00157967</t>
         </is>
       </c>
       <c r="N68" s="15" t="n">
-        <v>255</v>
+        <v>300</v>
       </c>
       <c r="O68" s="16" t="n">
         <v>0</v>
@@ -5638,32 +5634,32 @@
     <row r="69">
       <c r="A69" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-30330</t>
+          <t>PDMDEP-31540</t>
         </is>
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
+          <t>[COMMUNE DE MONTELIMAR] - Modélisation LiEx et redevances</t>
         </is>
       </c>
       <c r="C69" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D69" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE ALENCON</t>
+          <t>COMMUNE DE MONTELIMAR</t>
         </is>
       </c>
       <c r="E69" s="11" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>Modélisation LiEx</t>
         </is>
       </c>
       <c r="F69" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G69" s="11" t="inlineStr">
@@ -5673,32 +5669,32 @@
       </c>
       <c r="H69" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I69" s="11" t="inlineStr">
         <is>
-          <t>28/01/2026</t>
+          <t>24/02/2026</t>
         </is>
       </c>
       <c r="J69" s="11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K69" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L69" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30335</t>
+          <t>PDMDEP-31546</t>
         </is>
       </c>
       <c r="M69" s="11" t="inlineStr">
         <is>
-          <t>00154411</t>
+          <t>00157816</t>
         </is>
       </c>
       <c r="N69" s="12" t="n">
-        <v>140</v>
+        <v>700</v>
       </c>
       <c r="O69" s="16" t="n">
         <v>0</v>
@@ -5710,32 +5706,32 @@
     <row r="70">
       <c r="A70" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-30196</t>
+          <t>PDMDEP-31351</t>
         </is>
       </c>
       <c r="B70" s="14" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
+          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="C70" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D70" s="14" t="inlineStr">
         <is>
-          <t>CD56</t>
+          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
         </is>
       </c>
       <c r="E70" s="14" t="inlineStr">
         <is>
-          <t>Paramétrage interface Pastell</t>
+          <t>Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="F70" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G70" s="14" t="inlineStr">
@@ -5745,32 +5741,32 @@
       </c>
       <c r="H70" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I70" s="14" t="inlineStr">
         <is>
-          <t>21/01/2026</t>
+          <t>17/02/2026</t>
         </is>
       </c>
       <c r="J70" s="14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K70" s="14" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="L70" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30197</t>
+          <t>PDMDEP-31360</t>
         </is>
       </c>
       <c r="M70" s="14" t="inlineStr">
         <is>
-          <t>00153939</t>
+          <t>00157041</t>
         </is>
       </c>
       <c r="N70" s="15" t="n">
-        <v>690</v>
+        <v>210</v>
       </c>
       <c r="O70" s="16" t="n">
         <v>0</v>
@@ -5782,32 +5778,32 @@
     <row r="71">
       <c r="A71" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-29606</t>
+          <t>PDMDEP-31319</t>
         </is>
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
+          <t>[COMMUNE DE LARMOR PLAGE] - Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="C71" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D71" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE BIARRITZ</t>
+          <t>COMMUNE DE LARMOR PLAGE</t>
         </is>
       </c>
       <c r="E71" s="11" t="inlineStr">
         <is>
-          <t>Paramétrages complémentaires + Vision</t>
+          <t>Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="F71" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G71" s="11" t="inlineStr">
@@ -5817,35 +5813,35 @@
       </c>
       <c r="H71" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I71" s="11" t="inlineStr">
         <is>
-          <t>09/01/2026</t>
+          <t>17/02/2026</t>
         </is>
       </c>
       <c r="J71" s="11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K71" s="11" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L71" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30431</t>
+          <t>PDMDEP-31328</t>
         </is>
       </c>
       <c r="M71" s="11" t="inlineStr">
         <is>
-          <t>00154684</t>
+          <t>00156518</t>
         </is>
       </c>
       <c r="N71" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O71" s="12" t="n">
-        <v>0</v>
+        <v>281</v>
       </c>
       <c r="P71" s="12" t="n">
         <v>0</v>
@@ -5854,32 +5850,32 @@
     <row r="72">
       <c r="A72" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-29606</t>
+          <t>PDMDEP-31188</t>
         </is>
       </c>
       <c r="B72" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
+          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C72" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D72" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE BIARRITZ</t>
+          <t>COMMUNE D HENDAYE</t>
         </is>
       </c>
       <c r="E72" s="14" t="inlineStr">
         <is>
-          <t>Paramétrages complémentaires + Vision</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F72" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G72" s="14" t="inlineStr">
@@ -5889,32 +5885,32 @@
       </c>
       <c r="H72" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I72" s="14" t="inlineStr">
         <is>
-          <t>09/01/2026</t>
+          <t>12/02/2026</t>
         </is>
       </c>
       <c r="J72" s="14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K72" s="14" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L72" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-29625</t>
+          <t>PDMDEP-31197</t>
         </is>
       </c>
       <c r="M72" s="14" t="inlineStr">
         <is>
-          <t>00145091</t>
+          <t>00156556</t>
         </is>
       </c>
       <c r="N72" s="15" t="n">
-        <v>187.5</v>
+        <v>130</v>
       </c>
       <c r="O72" s="16" t="n">
         <v>0</v>
@@ -5926,32 +5922,32 @@
     <row r="73">
       <c r="A73" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-29606</t>
+          <t>PDMDEP-31036</t>
         </is>
       </c>
       <c r="B73" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
+          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="C73" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D73" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE BIARRITZ</t>
+          <t>COMMUNE DE SARLAT LA CANEDA</t>
         </is>
       </c>
       <c r="E73" s="11" t="inlineStr">
         <is>
-          <t>Paramétrages complémentaires + Vision</t>
+          <t>Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="F73" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G73" s="11" t="inlineStr">
@@ -5961,32 +5957,32 @@
       </c>
       <c r="H73" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I73" s="11" t="inlineStr">
         <is>
-          <t>09/01/2026</t>
+          <t>10/02/2026</t>
         </is>
       </c>
       <c r="J73" s="11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K73" s="11" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L73" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-29608</t>
+          <t>PDMDEP-31045</t>
         </is>
       </c>
       <c r="M73" s="11" t="inlineStr">
         <is>
-          <t>00152338</t>
+          <t>00156095</t>
         </is>
       </c>
       <c r="N73" s="12" t="n">
-        <v>787.5</v>
+        <v>255</v>
       </c>
       <c r="O73" s="16" t="n">
         <v>0</v>
@@ -5998,12 +5994,12 @@
     <row r="74">
       <c r="A74" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-28306</t>
+          <t>PDMDEP-30330</t>
         </is>
       </c>
       <c r="B74" s="14" t="inlineStr">
         <is>
-          <t>Commune de CLAMART - GEODP2 migration</t>
+          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C74" s="14" t="inlineStr">
@@ -6013,12 +6009,12 @@
       </c>
       <c r="D74" s="14" t="inlineStr">
         <is>
-          <t>Commune de CLAMART</t>
+          <t>COMMUNE DE ALENCON</t>
         </is>
       </c>
       <c r="E74" s="14" t="inlineStr">
         <is>
-          <t>Migration V2</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F74" s="14" t="inlineStr">
@@ -6038,30 +6034,30 @@
       </c>
       <c r="I74" s="14" t="inlineStr">
         <is>
-          <t>28/11/2025</t>
+          <t>28/01/2026</t>
         </is>
       </c>
       <c r="J74" s="14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K74" s="14" t="n">
         <v>0</v>
       </c>
       <c r="L74" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28310</t>
+          <t>PDMDEP-30335</t>
         </is>
       </c>
       <c r="M74" s="14" t="inlineStr">
         <is>
-          <t>00145374</t>
+          <t>00154411</t>
         </is>
       </c>
       <c r="N74" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O74" s="15" t="n">
-        <v>362.5</v>
+        <v>140</v>
+      </c>
+      <c r="O74" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P74" s="15" t="n">
         <v>0</v>
@@ -6070,12 +6066,12 @@
     <row r="75">
       <c r="A75" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-28174</t>
+          <t>PDMDEP-30196</t>
         </is>
       </c>
       <c r="B75" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOBIGNY - LITTERALIS</t>
+          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="C75" s="11" t="inlineStr">
@@ -6085,11 +6081,13 @@
       </c>
       <c r="D75" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOBIGNY</t>
-        </is>
-      </c>
-      <c r="E75" s="11" t="n">
-        <v/>
+          <t>CD56</t>
+        </is>
+      </c>
+      <c r="E75" s="11" t="inlineStr">
+        <is>
+          <t>Paramétrage interface Pastell</t>
+        </is>
       </c>
       <c r="F75" s="11" t="inlineStr">
         <is>
@@ -6103,34 +6101,34 @@
       </c>
       <c r="H75" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I75" s="11" t="inlineStr">
         <is>
-          <t>25/11/2025</t>
+          <t>21/01/2026</t>
         </is>
       </c>
       <c r="J75" s="11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K75" s="11" t="n">
-        <v>2.75</v>
+        <v>1.5</v>
       </c>
       <c r="L75" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28175</t>
+          <t>PDMDEP-30197</t>
         </is>
       </c>
       <c r="M75" s="11" t="inlineStr">
         <is>
-          <t>00145001</t>
+          <t>00153939</t>
         </is>
       </c>
       <c r="N75" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O75" s="12" t="n">
+        <v>690</v>
+      </c>
+      <c r="O75" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P75" s="12" t="n">
@@ -6140,27 +6138,27 @@
     <row r="76">
       <c r="A76" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-29606</t>
         </is>
       </c>
       <c r="B76" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="C76" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D76" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+          <t>COMMUNE DE BIARRITZ</t>
         </is>
       </c>
       <c r="E76" s="14" t="inlineStr">
         <is>
-          <t>Déploiement Littéralis Expert</t>
+          <t>Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="F76" s="14" t="inlineStr">
@@ -6175,28 +6173,28 @@
       </c>
       <c r="H76" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I76" s="14" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>09/01/2026</t>
         </is>
       </c>
       <c r="J76" s="14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K76" s="14" t="n">
-        <v>0.95</v>
+        <v>0.25</v>
       </c>
       <c r="L76" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28206</t>
+          <t>PDMDEP-30431</t>
         </is>
       </c>
       <c r="M76" s="14" t="inlineStr">
         <is>
-          <t>00144864</t>
+          <t>00154684</t>
         </is>
       </c>
       <c r="N76" s="15" t="n">
@@ -6212,27 +6210,27 @@
     <row r="77">
       <c r="A77" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-29606</t>
         </is>
       </c>
       <c r="B77" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="C77" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D77" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+          <t>COMMUNE DE BIARRITZ</t>
         </is>
       </c>
       <c r="E77" s="11" t="inlineStr">
         <is>
-          <t>Déploiement Littéralis Expert</t>
+          <t>Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="F77" s="11" t="inlineStr">
@@ -6247,34 +6245,34 @@
       </c>
       <c r="H77" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I77" s="11" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>09/01/2026</t>
         </is>
       </c>
       <c r="J77" s="11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K77" s="11" t="n">
-        <v>0.95</v>
+        <v>0.25</v>
       </c>
       <c r="L77" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28205</t>
+          <t>PDMDEP-29625</t>
         </is>
       </c>
       <c r="M77" s="11" t="inlineStr">
         <is>
-          <t>00144863</t>
+          <t>00145091</t>
         </is>
       </c>
       <c r="N77" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O77" s="12" t="n">
+        <v>187.5</v>
+      </c>
+      <c r="O77" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P77" s="12" t="n">
@@ -6284,27 +6282,27 @@
     <row r="78">
       <c r="A78" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-29606</t>
         </is>
       </c>
       <c r="B78" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="C78" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D78" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+          <t>COMMUNE DE BIARRITZ</t>
         </is>
       </c>
       <c r="E78" s="14" t="inlineStr">
         <is>
-          <t>Déploiement Littéralis Expert</t>
+          <t>Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="F78" s="14" t="inlineStr">
@@ -6319,34 +6317,34 @@
       </c>
       <c r="H78" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I78" s="14" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>09/01/2026</t>
         </is>
       </c>
       <c r="J78" s="14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K78" s="14" t="n">
-        <v>0.95</v>
+        <v>0.25</v>
       </c>
       <c r="L78" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28204</t>
+          <t>PDMDEP-29608</t>
         </is>
       </c>
       <c r="M78" s="14" t="inlineStr">
         <is>
-          <t>00144862</t>
+          <t>00152338</t>
         </is>
       </c>
       <c r="N78" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O78" s="15" t="n">
+        <v>787.5</v>
+      </c>
+      <c r="O78" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P78" s="15" t="n">
@@ -6356,32 +6354,32 @@
     <row r="79">
       <c r="A79" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-28306</t>
         </is>
       </c>
       <c r="B79" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t>Commune de CLAMART - GEODP2 migration</t>
         </is>
       </c>
       <c r="C79" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D79" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+          <t>Commune de CLAMART</t>
         </is>
       </c>
       <c r="E79" s="11" t="inlineStr">
         <is>
-          <t>Déploiement Littéralis Expert</t>
+          <t>Migration V2</t>
         </is>
       </c>
       <c r="F79" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G79" s="11" t="inlineStr">
@@ -6391,35 +6389,35 @@
       </c>
       <c r="H79" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I79" s="11" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>28/11/2025</t>
         </is>
       </c>
       <c r="J79" s="11" t="n">
         <v>10</v>
       </c>
       <c r="K79" s="11" t="n">
-        <v>0.95</v>
+        <v>0</v>
       </c>
       <c r="L79" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28203</t>
+          <t>PDMDEP-28310</t>
         </is>
       </c>
       <c r="M79" s="11" t="inlineStr">
         <is>
-          <t>00144860</t>
+          <t>00145374</t>
         </is>
       </c>
       <c r="N79" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O79" s="12" t="n">
-        <v>0</v>
+        <v>362.5</v>
       </c>
       <c r="P79" s="12" t="n">
         <v>0</v>
@@ -6428,12 +6426,12 @@
     <row r="80">
       <c r="A80" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-28174</t>
         </is>
       </c>
       <c r="B80" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t>COMMUNE DE BOBIGNY - LITTERALIS</t>
         </is>
       </c>
       <c r="C80" s="14" t="inlineStr">
@@ -6443,13 +6441,11 @@
       </c>
       <c r="D80" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
-        </is>
-      </c>
-      <c r="E80" s="14" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
+          <t>COMMUNE DE BOBIGNY</t>
+        </is>
+      </c>
+      <c r="E80" s="14" t="n">
+        <v/>
       </c>
       <c r="F80" s="14" t="inlineStr">
         <is>
@@ -6468,29 +6464,29 @@
       </c>
       <c r="I80" s="14" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>25/11/2025</t>
         </is>
       </c>
       <c r="J80" s="14" t="n">
         <v>10</v>
       </c>
       <c r="K80" s="14" t="n">
-        <v>0.95</v>
+        <v>2.75</v>
       </c>
       <c r="L80" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28202</t>
+          <t>PDMDEP-28175</t>
         </is>
       </c>
       <c r="M80" s="14" t="inlineStr">
         <is>
-          <t>00144857</t>
+          <t>00145001</t>
         </is>
       </c>
       <c r="N80" s="15" t="n">
-        <v>1320</v>
-      </c>
-      <c r="O80" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O80" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P80" s="15" t="n">
@@ -6500,12 +6496,12 @@
     <row r="81">
       <c r="A81" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-27634</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B81" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes - LITTERALIS</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C81" s="11" t="inlineStr">
@@ -6515,11 +6511,13 @@
       </c>
       <c r="D81" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes</t>
-        </is>
-      </c>
-      <c r="E81" s="11" t="n">
-        <v/>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+        </is>
+      </c>
+      <c r="E81" s="11" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F81" s="11" t="inlineStr">
         <is>
@@ -6533,28 +6531,28 @@
       </c>
       <c r="H81" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I81" s="11" t="inlineStr">
         <is>
-          <t>21/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J81" s="11" t="n">
         <v>10</v>
       </c>
       <c r="K81" s="11" t="n">
-        <v>0.5</v>
+        <v>0.95</v>
       </c>
       <c r="L81" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27642</t>
+          <t>PDMDEP-28206</t>
         </is>
       </c>
       <c r="M81" s="11" t="inlineStr">
         <is>
-          <t>00143935</t>
+          <t>00144864</t>
         </is>
       </c>
       <c r="N81" s="12" t="n">
@@ -6570,12 +6568,12 @@
     <row r="82">
       <c r="A82" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-26831</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B82" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [CD74] - Maj Ref carto dans le cadre de la maintenance</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C82" s="14" t="inlineStr">
@@ -6585,34 +6583,50 @@
       </c>
       <c r="D82" s="14" t="inlineStr">
         <is>
-          <t>CD74</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
         </is>
       </c>
       <c r="E82" s="14" t="inlineStr">
         <is>
-          <t>MAJ carto</t>
-        </is>
-      </c>
-      <c r="F82" s="14" t="inlineStr"/>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
+      </c>
+      <c r="F82" s="14" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
       <c r="G82" s="14" t="inlineStr">
         <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="H82" s="14" t="inlineStr"/>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H82" s="14" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I82" s="14" t="inlineStr">
         <is>
-          <t>05/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J82" s="14" t="n">
         <v>10</v>
       </c>
       <c r="K82" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="L82" s="14" t="inlineStr"/>
-      <c r="M82" s="14" t="inlineStr"/>
+        <v>0.95</v>
+      </c>
+      <c r="L82" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-28205</t>
+        </is>
+      </c>
+      <c r="M82" s="14" t="inlineStr">
+        <is>
+          <t>00144863</t>
+        </is>
+      </c>
       <c r="N82" s="15" t="n">
         <v>0</v>
       </c>
@@ -6626,12 +6640,12 @@
     <row r="83">
       <c r="A83" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-26813</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B83" s="11" t="inlineStr">
         <is>
-          <t>[VILLEJUIF] - Litteralis Modèle facture + param Civil Net</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C83" s="11" t="inlineStr">
@@ -6641,11 +6655,13 @@
       </c>
       <c r="D83" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE VILLEJUIF</t>
-        </is>
-      </c>
-      <c r="E83" s="11" t="n">
-        <v/>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+        </is>
+      </c>
+      <c r="E83" s="11" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F83" s="11" t="inlineStr">
         <is>
@@ -6659,28 +6675,28 @@
       </c>
       <c r="H83" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I83" s="11" t="inlineStr">
         <is>
-          <t>04/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J83" s="11" t="n">
         <v>10</v>
       </c>
       <c r="K83" s="11" t="n">
-        <v>0.25</v>
+        <v>0.95</v>
       </c>
       <c r="L83" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-26814</t>
+          <t>PDMDEP-28204</t>
         </is>
       </c>
       <c r="M83" s="11" t="inlineStr">
         <is>
-          <t>00142941</t>
+          <t>00144862</t>
         </is>
       </c>
       <c r="N83" s="12" t="n">
@@ -6696,12 +6712,12 @@
     <row r="84">
       <c r="A84" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-24866</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B84" s="14" t="inlineStr">
         <is>
-          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C84" s="14" t="inlineStr">
@@ -6711,11 +6727,13 @@
       </c>
       <c r="D84" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
-        </is>
-      </c>
-      <c r="E84" s="14" t="n">
-        <v/>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+        </is>
+      </c>
+      <c r="E84" s="14" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F84" s="14" t="inlineStr">
         <is>
@@ -6734,29 +6752,29 @@
       </c>
       <c r="I84" s="14" t="inlineStr">
         <is>
-          <t>16/10/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J84" s="14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K84" s="14" t="n">
-        <v>0</v>
+        <v>0.95</v>
       </c>
       <c r="L84" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27017</t>
+          <t>PDMDEP-28203</t>
         </is>
       </c>
       <c r="M84" s="14" t="inlineStr">
         <is>
-          <t>00141205</t>
+          <t>00144860</t>
         </is>
       </c>
       <c r="N84" s="15" t="n">
-        <v>1212</v>
-      </c>
-      <c r="O84" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O84" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P84" s="15" t="n">
@@ -6766,12 +6784,12 @@
     <row r="85">
       <c r="A85" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-23918</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B85" s="11" t="inlineStr">
         <is>
-          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C85" s="11" t="inlineStr">
@@ -6781,11 +6799,13 @@
       </c>
       <c r="D85" s="11" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
-        </is>
-      </c>
-      <c r="E85" s="11" t="n">
-        <v/>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+        </is>
+      </c>
+      <c r="E85" s="11" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F85" s="11" t="inlineStr">
         <is>
@@ -6804,29 +6824,29 @@
       </c>
       <c r="I85" s="11" t="inlineStr">
         <is>
-          <t>26/08/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J85" s="11" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="K85" s="11" t="n">
-        <v>1.5</v>
+        <v>0.95</v>
       </c>
       <c r="L85" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28055</t>
+          <t>PDMDEP-28202</t>
         </is>
       </c>
       <c r="M85" s="11" t="inlineStr">
         <is>
-          <t>499132</t>
+          <t>00144857</t>
         </is>
       </c>
       <c r="N85" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O85" s="12" t="n">
+        <v>1320</v>
+      </c>
+      <c r="O85" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P85" s="12" t="n">
@@ -6836,12 +6856,12 @@
     <row r="86">
       <c r="A86" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-23750</t>
+          <t>PDMDEP-27634</t>
         </is>
       </c>
       <c r="B86" s="14" t="inlineStr">
         <is>
-          <t>MEL - LITTERALIS x AXION</t>
+          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes - LITTERALIS</t>
         </is>
       </c>
       <c r="C86" s="14" t="inlineStr">
@@ -6851,13 +6871,11 @@
       </c>
       <c r="D86" s="14" t="inlineStr">
         <is>
-          <t>METROPOLE EUROPEENNE DE LILLE</t>
-        </is>
-      </c>
-      <c r="E86" s="14" t="inlineStr">
-        <is>
-          <t>AXION</t>
-        </is>
+          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes</t>
+        </is>
+      </c>
+      <c r="E86" s="14" t="n">
+        <v/>
       </c>
       <c r="F86" s="14" t="inlineStr">
         <is>
@@ -6866,7 +6884,7 @@
       </c>
       <c r="G86" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H86" s="14" t="inlineStr">
@@ -6876,23 +6894,23 @@
       </c>
       <c r="I86" s="14" t="inlineStr">
         <is>
-          <t>08/08/2025</t>
+          <t>21/11/2025</t>
         </is>
       </c>
       <c r="J86" s="14" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="K86" s="14" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="L86" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27033</t>
+          <t>PDMDEP-27642</t>
         </is>
       </c>
       <c r="M86" s="14" t="inlineStr">
         <is>
-          <t>497304</t>
+          <t>00143935</t>
         </is>
       </c>
       <c r="N86" s="15" t="n">
@@ -6908,12 +6926,12 @@
     <row r="87">
       <c r="A87" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-22757</t>
+          <t>PDMDEP-26831</t>
         </is>
       </c>
       <c r="B87" s="11" t="inlineStr">
         <is>
-          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
+          <t xml:space="preserve"> [CD74] - Maj Ref carto dans le cadre de la maintenance</t>
         </is>
       </c>
       <c r="C87" s="11" t="inlineStr">
@@ -6923,48 +6941,34 @@
       </c>
       <c r="D87" s="11" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
-        </is>
-      </c>
-      <c r="E87" s="11" t="n">
-        <v/>
-      </c>
-      <c r="F87" s="11" t="inlineStr">
-        <is>
-          <t>LITTERALIS</t>
-        </is>
-      </c>
+          <t>CD74</t>
+        </is>
+      </c>
+      <c r="E87" s="11" t="inlineStr">
+        <is>
+          <t>MAJ carto</t>
+        </is>
+      </c>
+      <c r="F87" s="11" t="inlineStr"/>
       <c r="G87" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H87" s="11" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="H87" s="11" t="inlineStr"/>
       <c r="I87" s="11" t="inlineStr">
         <is>
-          <t>01/07/2025</t>
+          <t>05/11/2025</t>
         </is>
       </c>
       <c r="J87" s="11" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="K87" s="11" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="L87" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-30081</t>
-        </is>
-      </c>
-      <c r="M87" s="11" t="inlineStr">
-        <is>
-          <t>00152628</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="L87" s="11" t="inlineStr"/>
+      <c r="M87" s="11" t="inlineStr"/>
       <c r="N87" s="12" t="n">
         <v>0</v>
       </c>
@@ -6978,12 +6982,12 @@
     <row r="88">
       <c r="A88" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-22757</t>
+          <t>PDMDEP-26813</t>
         </is>
       </c>
       <c r="B88" s="14" t="inlineStr">
         <is>
-          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
+          <t>[VILLEJUIF] - Litteralis Modèle facture + param Civil Net</t>
         </is>
       </c>
       <c r="C88" s="14" t="inlineStr">
@@ -6993,7 +6997,7 @@
       </c>
       <c r="D88" s="14" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>VILLE DE VILLEJUIF</t>
         </is>
       </c>
       <c r="E88" s="14" t="n">
@@ -7011,28 +7015,28 @@
       </c>
       <c r="H88" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I88" s="14" t="inlineStr">
         <is>
-          <t>01/07/2025</t>
+          <t>04/11/2025</t>
         </is>
       </c>
       <c r="J88" s="14" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="K88" s="14" t="n">
-        <v>0.06</v>
+        <v>0.25</v>
       </c>
       <c r="L88" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30080</t>
+          <t>PDMDEP-26814</t>
         </is>
       </c>
       <c r="M88" s="14" t="inlineStr">
         <is>
-          <t>00152635</t>
+          <t>00142941</t>
         </is>
       </c>
       <c r="N88" s="15" t="n">
@@ -7048,12 +7052,12 @@
     <row r="89">
       <c r="A89" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-22757</t>
+          <t>PDMDEP-24866</t>
         </is>
       </c>
       <c r="B89" s="11" t="inlineStr">
         <is>
-          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
+          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
         </is>
       </c>
       <c r="C89" s="11" t="inlineStr">
@@ -7063,7 +7067,7 @@
       </c>
       <c r="D89" s="11" t="inlineStr">
         <is>
-          <t>Brest Métropole</t>
+          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
         </is>
       </c>
       <c r="E89" s="11" t="n">
@@ -7086,29 +7090,29 @@
       </c>
       <c r="I89" s="11" t="inlineStr">
         <is>
-          <t>01/07/2025</t>
+          <t>16/10/2025</t>
         </is>
       </c>
       <c r="J89" s="11" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="K89" s="11" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="L89" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30079</t>
+          <t>PDMDEP-27017</t>
         </is>
       </c>
       <c r="M89" s="11" t="inlineStr">
         <is>
-          <t>00152632</t>
+          <t>00141205</t>
         </is>
       </c>
       <c r="N89" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O89" s="12" t="n">
+        <v>1212</v>
+      </c>
+      <c r="O89" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P89" s="12" t="n">
@@ -7118,12 +7122,12 @@
     <row r="90">
       <c r="A90" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-22757</t>
+          <t>PDMDEP-23918</t>
         </is>
       </c>
       <c r="B90" s="14" t="inlineStr">
         <is>
-          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
+          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C90" s="14" t="inlineStr">
@@ -7133,7 +7137,7 @@
       </c>
       <c r="D90" s="14" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
         </is>
       </c>
       <c r="E90" s="14" t="n">
@@ -7156,23 +7160,23 @@
       </c>
       <c r="I90" s="14" t="inlineStr">
         <is>
-          <t>01/07/2025</t>
+          <t>26/08/2025</t>
         </is>
       </c>
       <c r="J90" s="14" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K90" s="14" t="n">
-        <v>0.06</v>
+        <v>1.5</v>
       </c>
       <c r="L90" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27365</t>
+          <t>PDMDEP-28055</t>
         </is>
       </c>
       <c r="M90" s="14" t="inlineStr">
         <is>
-          <t>491593</t>
+          <t>499132</t>
         </is>
       </c>
       <c r="N90" s="15" t="n">
@@ -7188,12 +7192,12 @@
     <row r="91">
       <c r="A91" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-22126</t>
+          <t>PDMDEP-23750</t>
         </is>
       </c>
       <c r="B91" s="11" t="inlineStr">
         <is>
-          <t>[MEL Lille] - LITTERALIS - 3 jours de modélisation / param / accomp (21h)</t>
+          <t>MEL - LITTERALIS x AXION</t>
         </is>
       </c>
       <c r="C91" s="11" t="inlineStr">
@@ -7203,11 +7207,13 @@
       </c>
       <c r="D91" s="11" t="inlineStr">
         <is>
-          <t>Métropole Européenne de Lille</t>
-        </is>
-      </c>
-      <c r="E91" s="11" t="n">
-        <v/>
+          <t>METROPOLE EUROPEENNE DE LILLE</t>
+        </is>
+      </c>
+      <c r="E91" s="11" t="inlineStr">
+        <is>
+          <t>AXION</t>
+        </is>
       </c>
       <c r="F91" s="11" t="inlineStr">
         <is>
@@ -7216,7 +7222,7 @@
       </c>
       <c r="G91" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H91" s="11" t="inlineStr">
@@ -7226,23 +7232,23 @@
       </c>
       <c r="I91" s="11" t="inlineStr">
         <is>
-          <t>02/06/2025</t>
+          <t>08/08/2025</t>
         </is>
       </c>
       <c r="J91" s="11" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="K91" s="11" t="n">
         <v>0.25</v>
       </c>
       <c r="L91" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27368</t>
+          <t>PDMDEP-27033</t>
         </is>
       </c>
       <c r="M91" s="11" t="inlineStr">
         <is>
-          <t>484163</t>
+          <t>497304</t>
         </is>
       </c>
       <c r="N91" s="12" t="n">
@@ -7258,22 +7264,22 @@
     <row r="92">
       <c r="A92" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-21661</t>
+          <t>PDMDEP-23323</t>
         </is>
       </c>
       <c r="B92" s="14" t="inlineStr">
         <is>
-          <t>[Grand Dax] - Pastell</t>
+          <t>[BAGNOLET] - LITTERALIS projet</t>
         </is>
       </c>
       <c r="C92" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D92" s="14" t="inlineStr">
         <is>
-          <t>GRAND DAX</t>
+          <t>VILLE DE BAGNOLET</t>
         </is>
       </c>
       <c r="E92" s="14" t="n">
@@ -7291,34 +7297,34 @@
       </c>
       <c r="H92" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I92" s="14" t="inlineStr">
         <is>
-          <t>07/05/2025</t>
+          <t>21/07/2025</t>
         </is>
       </c>
       <c r="J92" s="14" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K92" s="14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="L92" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27373</t>
+          <t>PDMDEP-27570</t>
         </is>
       </c>
       <c r="M92" s="14" t="inlineStr">
         <is>
-          <t>466234</t>
+          <t>493613</t>
         </is>
       </c>
       <c r="N92" s="15" t="n">
-        <v>401</v>
-      </c>
-      <c r="O92" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O92" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P92" s="15" t="n">
@@ -7328,22 +7334,22 @@
     <row r="93">
       <c r="A93" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-21222</t>
+          <t>PDMDEP-22757</t>
         </is>
       </c>
       <c r="B93" s="11" t="inlineStr">
         <is>
-          <t>[Issy les Moulineaux] Litteralis Expert</t>
+          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C93" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D93" s="11" t="inlineStr">
         <is>
-          <t>ISSY LES MOULINEAUX</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E93" s="11" t="n">
@@ -7366,23 +7372,23 @@
       </c>
       <c r="I93" s="11" t="inlineStr">
         <is>
-          <t>23/04/2025</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="J93" s="11" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="K93" s="11" t="n">
-        <v>3.25</v>
+        <v>0.06</v>
       </c>
       <c r="L93" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28036</t>
+          <t>PDMDEP-30081</t>
         </is>
       </c>
       <c r="M93" s="11" t="inlineStr">
         <is>
-          <t>483799</t>
+          <t>00152628</t>
         </is>
       </c>
       <c r="N93" s="12" t="n">
@@ -7398,12 +7404,12 @@
     <row r="94">
       <c r="A94" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-21165</t>
+          <t>PDMDEP-22757</t>
         </is>
       </c>
       <c r="B94" s="14" t="inlineStr">
         <is>
-          <t>[Montreuil] Mise à jour carto (SaaS)</t>
+          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C94" s="14" t="inlineStr">
@@ -7413,7 +7419,7 @@
       </c>
       <c r="D94" s="14" t="inlineStr">
         <is>
-          <t>MONTREUIL</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E94" s="14" t="n">
@@ -7431,28 +7437,28 @@
       </c>
       <c r="H94" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I94" s="14" t="inlineStr">
         <is>
-          <t>18/04/2025</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="J94" s="14" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="K94" s="14" t="n">
-        <v>1</v>
+        <v>0.06</v>
       </c>
       <c r="L94" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28035</t>
+          <t>PDMDEP-30080</t>
         </is>
       </c>
       <c r="M94" s="14" t="inlineStr">
         <is>
-          <t>468660</t>
+          <t>00152635</t>
         </is>
       </c>
       <c r="N94" s="15" t="n">
@@ -7468,22 +7474,22 @@
     <row r="95">
       <c r="A95" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-20907</t>
+          <t>PDMDEP-22757</t>
         </is>
       </c>
       <c r="B95" s="11" t="inlineStr">
         <is>
-          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
+          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C95" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D95" s="11" t="inlineStr">
         <is>
-          <t>SAINT PIERRE (LA REUNION)</t>
+          <t>Brest Métropole</t>
         </is>
       </c>
       <c r="E95" s="11" t="n">
@@ -7501,34 +7507,34 @@
       </c>
       <c r="H95" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I95" s="11" t="inlineStr">
         <is>
-          <t>14/04/2025</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="J95" s="11" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="K95" s="11" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="L95" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28034</t>
+          <t>PDMDEP-30079</t>
         </is>
       </c>
       <c r="M95" s="11" t="inlineStr">
         <is>
-          <t>475575</t>
+          <t>00152632</t>
         </is>
       </c>
       <c r="N95" s="12" t="n">
-        <v>230</v>
-      </c>
-      <c r="O95" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O95" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P95" s="12" t="n">
@@ -7538,22 +7544,22 @@
     <row r="96">
       <c r="A96" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-19909</t>
+          <t>PDMDEP-22757</t>
         </is>
       </c>
       <c r="B96" s="14" t="inlineStr">
         <is>
-          <t>[CD 29] Interface Pastell</t>
+          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C96" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D96" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU FINISTERE (CD29)</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E96" s="14" t="n">
@@ -7571,28 +7577,28 @@
       </c>
       <c r="H96" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I96" s="14" t="inlineStr">
         <is>
-          <t>11/03/2025</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="J96" s="14" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="K96" s="14" t="n">
-        <v>0.5</v>
+        <v>0.06</v>
       </c>
       <c r="L96" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27568</t>
+          <t>PDMDEP-27365</t>
         </is>
       </c>
       <c r="M96" s="14" t="inlineStr">
         <is>
-          <t>471958</t>
+          <t>491593</t>
         </is>
       </c>
       <c r="N96" s="15" t="n">
@@ -7608,12 +7614,12 @@
     <row r="97">
       <c r="A97" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-19558</t>
+          <t>PDMDEP-22126</t>
         </is>
       </c>
       <c r="B97" s="11" t="inlineStr">
         <is>
-          <t>[VILLEFONTAINE] - Litteralis Expert SAAS</t>
+          <t>[MEL Lille] - LITTERALIS - 3 jours de modélisation / param / accomp (21h)</t>
         </is>
       </c>
       <c r="C97" s="11" t="inlineStr">
@@ -7623,7 +7629,7 @@
       </c>
       <c r="D97" s="11" t="inlineStr">
         <is>
-          <t>VILLEFONTAINE</t>
+          <t>Métropole Européenne de Lille</t>
         </is>
       </c>
       <c r="E97" s="11" t="n">
@@ -7641,28 +7647,28 @@
       </c>
       <c r="H97" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I97" s="11" t="inlineStr">
         <is>
-          <t>28/02/2025</t>
+          <t>02/06/2025</t>
         </is>
       </c>
       <c r="J97" s="11" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="K97" s="11" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="L97" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28215</t>
+          <t>PDMDEP-27368</t>
         </is>
       </c>
       <c r="M97" s="11" t="inlineStr">
         <is>
-          <t>458306</t>
+          <t>484163</t>
         </is>
       </c>
       <c r="N97" s="12" t="n">
@@ -7678,22 +7684,22 @@
     <row r="98">
       <c r="A98" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-19558</t>
+          <t>PDMDEP-21661</t>
         </is>
       </c>
       <c r="B98" s="14" t="inlineStr">
         <is>
-          <t>[VILLEFONTAINE] - Litteralis Expert SAAS</t>
+          <t>[Grand Dax] - Pastell</t>
         </is>
       </c>
       <c r="C98" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D98" s="14" t="inlineStr">
         <is>
-          <t>VILLEFONTAINE</t>
+          <t>GRAND DAX</t>
         </is>
       </c>
       <c r="E98" s="14" t="n">
@@ -7711,34 +7717,34 @@
       </c>
       <c r="H98" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I98" s="14" t="inlineStr">
         <is>
-          <t>28/02/2025</t>
+          <t>07/05/2025</t>
         </is>
       </c>
       <c r="J98" s="14" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="K98" s="14" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L98" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28214</t>
+          <t>PDMDEP-27373</t>
         </is>
       </c>
       <c r="M98" s="14" t="inlineStr">
         <is>
-          <t>458286</t>
+          <t>466234</t>
         </is>
       </c>
       <c r="N98" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O98" s="15" t="n">
+        <v>401</v>
+      </c>
+      <c r="O98" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P98" s="15" t="n">
@@ -7748,22 +7754,22 @@
     <row r="99">
       <c r="A99" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18241</t>
+          <t>PDMDEP-21222</t>
         </is>
       </c>
       <c r="B99" s="11" t="inlineStr">
         <is>
-          <t>[CD74 - HAUTE SAVOIE] - Interface LiEx Maj Ref BG</t>
+          <t>[Issy les Moulineaux] Litteralis Expert</t>
         </is>
       </c>
       <c r="C99" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D99" s="11" t="inlineStr">
         <is>
-          <t>CD 74 - HAUTE SAVOIE</t>
+          <t>ISSY LES MOULINEAUX</t>
         </is>
       </c>
       <c r="E99" s="11" t="n">
@@ -7776,27 +7782,35 @@
       </c>
       <c r="G99" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H99" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I99" s="11" t="inlineStr">
         <is>
-          <t>20/12/2024</t>
+          <t>23/04/2025</t>
         </is>
       </c>
       <c r="J99" s="11" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="K99" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="L99" s="11" t="inlineStr"/>
-      <c r="M99" s="11" t="inlineStr"/>
+        <v>3.25</v>
+      </c>
+      <c r="L99" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-28036</t>
+        </is>
+      </c>
+      <c r="M99" s="11" t="inlineStr">
+        <is>
+          <t>483799</t>
+        </is>
+      </c>
       <c r="N99" s="12" t="n">
         <v>0</v>
       </c>
@@ -7810,22 +7824,22 @@
     <row r="100">
       <c r="A100" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-18240</t>
+          <t>PDMDEP-21165</t>
         </is>
       </c>
       <c r="B100" s="14" t="inlineStr">
         <is>
-          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
+          <t>[Montreuil] Mise à jour carto (SaaS)</t>
         </is>
       </c>
       <c r="C100" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D100" s="14" t="inlineStr">
         <is>
-          <t>Biarritz</t>
+          <t>MONTREUIL</t>
         </is>
       </c>
       <c r="E100" s="14" t="n">
@@ -7838,27 +7852,35 @@
       </c>
       <c r="G100" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H100" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I100" s="14" t="inlineStr">
         <is>
-          <t>20/12/2024</t>
+          <t>18/04/2025</t>
         </is>
       </c>
       <c r="J100" s="14" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="K100" s="14" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="L100" s="14" t="inlineStr"/>
-      <c r="M100" s="14" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="L100" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-28035</t>
+        </is>
+      </c>
+      <c r="M100" s="14" t="inlineStr">
+        <is>
+          <t>468660</t>
+        </is>
+      </c>
       <c r="N100" s="15" t="n">
         <v>0</v>
       </c>
@@ -7872,22 +7894,22 @@
     <row r="101">
       <c r="A101" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18115</t>
+          <t>PDMDEP-20907</t>
         </is>
       </c>
       <c r="B101" s="11" t="inlineStr">
         <is>
-          <t>[Bischwiller] Migration + Pax + M2M</t>
+          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
         </is>
       </c>
       <c r="C101" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D101" s="11" t="inlineStr">
         <is>
-          <t>BISCHWILLER</t>
+          <t>SAINT PIERRE (LA REUNION)</t>
         </is>
       </c>
       <c r="E101" s="11" t="n">
@@ -7895,7 +7917,7 @@
       </c>
       <c r="F101" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G101" s="11" t="inlineStr">
@@ -7905,32 +7927,32 @@
       </c>
       <c r="H101" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I101" s="11" t="inlineStr">
         <is>
-          <t>17/12/2024</t>
+          <t>14/04/2025</t>
         </is>
       </c>
       <c r="J101" s="11" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="K101" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L101" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28019</t>
+          <t>PDMDEP-28034</t>
         </is>
       </c>
       <c r="M101" s="11" t="inlineStr">
         <is>
-          <t>455151</t>
+          <t>475575</t>
         </is>
       </c>
       <c r="N101" s="12" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="O101" s="16" t="n">
         <v>0</v>
@@ -7942,12 +7964,12 @@
     <row r="102">
       <c r="A102" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-18037</t>
+          <t>PDMDEP-19909</t>
         </is>
       </c>
       <c r="B102" s="14" t="inlineStr">
         <is>
-          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
+          <t>[CD 29] Interface Pastell</t>
         </is>
       </c>
       <c r="C102" s="14" t="inlineStr">
@@ -7957,7 +7979,7 @@
       </c>
       <c r="D102" s="14" t="inlineStr">
         <is>
-          <t>LE PERREUX SUR MARNE</t>
+          <t>CONSEIL DEPARTEMENTAL DU FINISTERE (CD29)</t>
         </is>
       </c>
       <c r="E102" s="14" t="n">
@@ -7980,29 +8002,29 @@
       </c>
       <c r="I102" s="14" t="inlineStr">
         <is>
-          <t>12/12/2024</t>
+          <t>11/03/2025</t>
         </is>
       </c>
       <c r="J102" s="14" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="K102" s="14" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L102" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28023</t>
+          <t>PDMDEP-27568</t>
         </is>
       </c>
       <c r="M102" s="14" t="inlineStr">
         <is>
-          <t>454387</t>
+          <t>471958</t>
         </is>
       </c>
       <c r="N102" s="15" t="n">
-        <v>557.145</v>
-      </c>
-      <c r="O102" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O102" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P102" s="15" t="n">
@@ -8012,12 +8034,12 @@
     <row r="103">
       <c r="A103" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-14118</t>
+          <t>PDMDEP-19558</t>
         </is>
       </c>
       <c r="B103" s="11" t="inlineStr">
         <is>
-          <t>[SURESNES] Interface FAST-Parapheur</t>
+          <t>[VILLEFONTAINE] - Litteralis Expert SAAS</t>
         </is>
       </c>
       <c r="C103" s="11" t="inlineStr">
@@ -8027,7 +8049,7 @@
       </c>
       <c r="D103" s="11" t="inlineStr">
         <is>
-          <t>Suresnes</t>
+          <t>VILLEFONTAINE</t>
         </is>
       </c>
       <c r="E103" s="11" t="n">
@@ -8040,27 +8062,35 @@
       </c>
       <c r="G103" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H103" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I103" s="11" t="inlineStr">
         <is>
-          <t>01/02/2024</t>
+          <t>28/02/2025</t>
         </is>
       </c>
       <c r="J103" s="11" t="n">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="K103" s="11" t="n">
         <v>0.5</v>
       </c>
-      <c r="L103" s="11" t="inlineStr"/>
-      <c r="M103" s="11" t="inlineStr"/>
+      <c r="L103" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-28215</t>
+        </is>
+      </c>
+      <c r="M103" s="11" t="inlineStr">
+        <is>
+          <t>458306</t>
+        </is>
+      </c>
       <c r="N103" s="12" t="n">
         <v>0</v>
       </c>
@@ -8074,12 +8104,12 @@
     <row r="104">
       <c r="A104" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-13128</t>
+          <t>PDMDEP-19558</t>
         </is>
       </c>
       <c r="B104" s="14" t="inlineStr">
         <is>
-          <t>[VALENCIENNES] Littéralis Prime - RAF FAST PARAPHEUR - Déjà facturé</t>
+          <t>[VILLEFONTAINE] - Litteralis Expert SAAS</t>
         </is>
       </c>
       <c r="C104" s="14" t="inlineStr">
@@ -8089,7 +8119,7 @@
       </c>
       <c r="D104" s="14" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>VILLEFONTAINE</t>
         </is>
       </c>
       <c r="E104" s="14" t="n">
@@ -8102,7 +8132,7 @@
       </c>
       <c r="G104" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H104" s="14" t="inlineStr">
@@ -8112,17 +8142,25 @@
       </c>
       <c r="I104" s="14" t="inlineStr">
         <is>
-          <t>30/10/2023</t>
+          <t>28/02/2025</t>
         </is>
       </c>
       <c r="J104" s="14" t="n">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="K104" s="14" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="L104" s="14" t="inlineStr"/>
-      <c r="M104" s="14" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="L104" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-28214</t>
+        </is>
+      </c>
+      <c r="M104" s="14" t="inlineStr">
+        <is>
+          <t>458286</t>
+        </is>
+      </c>
       <c r="N104" s="15" t="n">
         <v>0</v>
       </c>
@@ -8136,22 +8174,22 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-12747</t>
+          <t>PDMDEP-18241</t>
         </is>
       </c>
       <c r="B105" s="11" t="inlineStr">
         <is>
-          <t>[FOUGERES] ARPEGE</t>
+          <t>[CD74 - HAUTE SAVOIE] - Interface LiEx Maj Ref BG</t>
         </is>
       </c>
       <c r="C105" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D105" s="11" t="inlineStr">
         <is>
-          <t>FOUGERES</t>
+          <t>CD 74 - HAUTE SAVOIE</t>
         </is>
       </c>
       <c r="E105" s="11" t="n">
@@ -8164,7 +8202,7 @@
       </c>
       <c r="G105" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H105" s="11" t="inlineStr">
@@ -8174,25 +8212,17 @@
       </c>
       <c r="I105" s="11" t="inlineStr">
         <is>
-          <t>26/09/2023</t>
+          <t>20/12/2024</t>
         </is>
       </c>
       <c r="J105" s="11" t="n">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="K105" s="11" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L105" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-27990</t>
-        </is>
-      </c>
-      <c r="M105" s="11" t="inlineStr">
-        <is>
-          <t>406296</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="L105" s="11" t="inlineStr"/>
+      <c r="M105" s="11" t="inlineStr"/>
       <c r="N105" s="12" t="n">
         <v>0</v>
       </c>
@@ -8206,22 +8236,22 @@
     <row r="106">
       <c r="A106" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-12708</t>
+          <t>PDMDEP-18240</t>
         </is>
       </c>
       <c r="B106" s="14" t="inlineStr">
         <is>
-          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
+          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
         </is>
       </c>
       <c r="C106" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D106" s="14" t="inlineStr">
         <is>
-          <t>CD 56 MORBIHAN</t>
+          <t>Biarritz</t>
         </is>
       </c>
       <c r="E106" s="14" t="n">
@@ -8237,17 +8267,21 @@
           <t>Rework</t>
         </is>
       </c>
-      <c r="H106" s="14" t="inlineStr"/>
+      <c r="H106" s="14" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I106" s="14" t="inlineStr">
         <is>
-          <t>22/09/2023</t>
+          <t>20/12/2024</t>
         </is>
       </c>
       <c r="J106" s="14" t="n">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="K106" s="14" t="n">
-        <v>0.75</v>
+        <v>3.08</v>
       </c>
       <c r="L106" s="14" t="inlineStr"/>
       <c r="M106" s="14" t="inlineStr"/>
@@ -8264,57 +8298,67 @@
     <row r="107">
       <c r="A107" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-11477</t>
+          <t>PDMDEP-18115</t>
         </is>
       </c>
       <c r="B107" s="11" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
-        </is>
-      </c>
-      <c r="C107" s="11" t="inlineStr"/>
+          <t>[Bischwiller] Migration + Pax + M2M</t>
+        </is>
+      </c>
+      <c r="C107" s="11" t="inlineStr">
+        <is>
+          <t>Alizée MARGOT</t>
+        </is>
+      </c>
       <c r="D107" s="11" t="inlineStr">
         <is>
-          <t>MONTPELLIER MMM</t>
-        </is>
-      </c>
-      <c r="E107" s="11" t="inlineStr">
-        <is>
-          <t>Déploiement Module AC</t>
-        </is>
+          <t>BISCHWILLER</t>
+        </is>
+      </c>
+      <c r="E107" s="11" t="n">
+        <v/>
       </c>
       <c r="F107" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G107" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H107" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I107" s="11" t="inlineStr">
         <is>
-          <t>03/09/2023</t>
+          <t>17/12/2024</t>
         </is>
       </c>
       <c r="J107" s="11" t="n">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="K107" s="11" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="L107" s="11" t="inlineStr"/>
-      <c r="M107" s="11" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L107" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-28019</t>
+        </is>
+      </c>
+      <c r="M107" s="11" t="inlineStr">
+        <is>
+          <t>455151</t>
+        </is>
+      </c>
       <c r="N107" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O107" s="12" t="n">
+        <v>240</v>
+      </c>
+      <c r="O107" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P107" s="12" t="n">
@@ -8324,89 +8368,471 @@
     <row r="108">
       <c r="A108" s="13" t="inlineStr">
         <is>
+          <t>PDMDEP-18037</t>
+        </is>
+      </c>
+      <c r="B108" s="14" t="inlineStr">
+        <is>
+          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
+        </is>
+      </c>
+      <c r="C108" s="14" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
+      <c r="D108" s="14" t="inlineStr">
+        <is>
+          <t>LE PERREUX SUR MARNE</t>
+        </is>
+      </c>
+      <c r="E108" s="14" t="n">
+        <v/>
+      </c>
+      <c r="F108" s="14" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G108" s="14" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H108" s="14" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="I108" s="14" t="inlineStr">
+        <is>
+          <t>12/12/2024</t>
+        </is>
+      </c>
+      <c r="J108" s="14" t="n">
+        <v>21</v>
+      </c>
+      <c r="K108" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L108" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-28023</t>
+        </is>
+      </c>
+      <c r="M108" s="14" t="inlineStr">
+        <is>
+          <t>454387</t>
+        </is>
+      </c>
+      <c r="N108" s="15" t="n">
+        <v>557.145</v>
+      </c>
+      <c r="O108" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P108" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="10" t="inlineStr">
+        <is>
+          <t>PDMDEP-14118</t>
+        </is>
+      </c>
+      <c r="B109" s="11" t="inlineStr">
+        <is>
+          <t>[SURESNES] Interface FAST-Parapheur</t>
+        </is>
+      </c>
+      <c r="C109" s="11" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
+      <c r="D109" s="11" t="inlineStr">
+        <is>
+          <t>Suresnes</t>
+        </is>
+      </c>
+      <c r="E109" s="11" t="n">
+        <v/>
+      </c>
+      <c r="F109" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G109" s="11" t="inlineStr">
+        <is>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H109" s="11" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="I109" s="11" t="inlineStr">
+        <is>
+          <t>01/02/2024</t>
+        </is>
+      </c>
+      <c r="J109" s="11" t="n">
+        <v>31</v>
+      </c>
+      <c r="K109" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L109" s="11" t="inlineStr"/>
+      <c r="M109" s="11" t="inlineStr"/>
+      <c r="N109" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O109" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P109" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="13" t="inlineStr">
+        <is>
+          <t>PDMDEP-13128</t>
+        </is>
+      </c>
+      <c r="B110" s="14" t="inlineStr">
+        <is>
+          <t>[VALENCIENNES] Littéralis Prime - RAF FAST PARAPHEUR - Déjà facturé</t>
+        </is>
+      </c>
+      <c r="C110" s="14" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
+      <c r="D110" s="14" t="inlineStr">
+        <is>
+          <t>Valenciennes</t>
+        </is>
+      </c>
+      <c r="E110" s="14" t="n">
+        <v/>
+      </c>
+      <c r="F110" s="14" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G110" s="14" t="inlineStr">
+        <is>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H110" s="14" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
+      <c r="I110" s="14" t="inlineStr">
+        <is>
+          <t>30/10/2023</t>
+        </is>
+      </c>
+      <c r="J110" s="14" t="n">
+        <v>35</v>
+      </c>
+      <c r="K110" s="14" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="L110" s="14" t="inlineStr"/>
+      <c r="M110" s="14" t="inlineStr"/>
+      <c r="N110" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O110" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P110" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="10" t="inlineStr">
+        <is>
+          <t>PDMDEP-12747</t>
+        </is>
+      </c>
+      <c r="B111" s="11" t="inlineStr">
+        <is>
+          <t>[FOUGERES] ARPEGE</t>
+        </is>
+      </c>
+      <c r="C111" s="11" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
+      <c r="D111" s="11" t="inlineStr">
+        <is>
+          <t>FOUGERES</t>
+        </is>
+      </c>
+      <c r="E111" s="11" t="n">
+        <v/>
+      </c>
+      <c r="F111" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G111" s="11" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H111" s="11" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="I111" s="11" t="inlineStr">
+        <is>
+          <t>26/09/2023</t>
+        </is>
+      </c>
+      <c r="J111" s="11" t="n">
+        <v>36</v>
+      </c>
+      <c r="K111" s="11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L111" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-27990</t>
+        </is>
+      </c>
+      <c r="M111" s="11" t="inlineStr">
+        <is>
+          <t>406296</t>
+        </is>
+      </c>
+      <c r="N111" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O111" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P111" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="13" t="inlineStr">
+        <is>
+          <t>PDMDEP-12708</t>
+        </is>
+      </c>
+      <c r="B112" s="14" t="inlineStr">
+        <is>
+          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
+        </is>
+      </c>
+      <c r="C112" s="14" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
+      <c r="D112" s="14" t="inlineStr">
+        <is>
+          <t>CD 56 MORBIHAN</t>
+        </is>
+      </c>
+      <c r="E112" s="14" t="n">
+        <v/>
+      </c>
+      <c r="F112" s="14" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G112" s="14" t="inlineStr">
+        <is>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H112" s="14" t="inlineStr"/>
+      <c r="I112" s="14" t="inlineStr">
+        <is>
+          <t>22/09/2023</t>
+        </is>
+      </c>
+      <c r="J112" s="14" t="n">
+        <v>36</v>
+      </c>
+      <c r="K112" s="14" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="L112" s="14" t="inlineStr"/>
+      <c r="M112" s="14" t="inlineStr"/>
+      <c r="N112" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O112" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P112" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="10" t="inlineStr">
+        <is>
+          <t>PDMDEP-11477</t>
+        </is>
+      </c>
+      <c r="B113" s="11" t="inlineStr">
+        <is>
+          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
+        </is>
+      </c>
+      <c r="C113" s="11" t="inlineStr"/>
+      <c r="D113" s="11" t="inlineStr">
+        <is>
+          <t>MONTPELLIER MMM</t>
+        </is>
+      </c>
+      <c r="E113" s="11" t="inlineStr">
+        <is>
+          <t>Déploiement Module AC</t>
+        </is>
+      </c>
+      <c r="F113" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G113" s="11" t="inlineStr">
+        <is>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H113" s="11" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
+      <c r="I113" s="11" t="inlineStr">
+        <is>
+          <t>03/09/2023</t>
+        </is>
+      </c>
+      <c r="J113" s="11" t="n">
+        <v>36</v>
+      </c>
+      <c r="K113" s="11" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="L113" s="11" t="inlineStr"/>
+      <c r="M113" s="11" t="inlineStr"/>
+      <c r="N113" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O113" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P113" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="13" t="inlineStr">
+        <is>
           <t>PSC-1270</t>
         </is>
       </c>
-      <c r="B108" s="14" t="inlineStr">
+      <c r="B114" s="14" t="inlineStr">
         <is>
           <t>COMMUNE DE CASTELNAUDARY</t>
         </is>
       </c>
-      <c r="C108" s="14" t="inlineStr"/>
-      <c r="D108" s="14" t="inlineStr">
+      <c r="C114" s="14" t="inlineStr"/>
+      <c r="D114" s="14" t="inlineStr">
         <is>
           <t>COMMUNE DE CASTELNAUDARY</t>
         </is>
       </c>
-      <c r="E108" s="14" t="inlineStr"/>
-      <c r="F108" s="14" t="inlineStr">
+      <c r="E114" s="14" t="inlineStr"/>
+      <c r="F114" s="14" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
         </is>
       </c>
-      <c r="G108" s="14" t="inlineStr">
+      <c r="G114" s="14" t="inlineStr">
         <is>
           <t>Projet</t>
         </is>
       </c>
-      <c r="H108" s="14" t="inlineStr"/>
-      <c r="I108" s="14" t="inlineStr">
+      <c r="H114" s="14" t="inlineStr"/>
+      <c r="I114" s="14" t="inlineStr">
         <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="J108" s="14" t="n">
+      <c r="J114" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="K108" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="L108" s="14" t="inlineStr">
+      <c r="K114" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="L114" s="14" t="inlineStr">
         <is>
           <t>PDMDEP-33362</t>
         </is>
       </c>
-      <c r="M108" s="14" t="inlineStr">
+      <c r="M114" s="14" t="inlineStr">
         <is>
           <t>00167140</t>
         </is>
       </c>
-      <c r="N108" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O108" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P108" s="15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="17" t="inlineStr">
+      <c r="N114" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O114" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P114" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="17" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B109" s="17" t="inlineStr"/>
-      <c r="C109" s="17" t="inlineStr"/>
-      <c r="D109" s="17" t="inlineStr"/>
-      <c r="E109" s="17" t="inlineStr"/>
-      <c r="F109" s="17" t="inlineStr"/>
-      <c r="G109" s="17" t="inlineStr"/>
-      <c r="H109" s="17" t="inlineStr"/>
-      <c r="I109" s="17" t="inlineStr"/>
-      <c r="J109" s="17" t="inlineStr"/>
-      <c r="K109" s="17" t="inlineStr"/>
-      <c r="L109" s="17" t="inlineStr"/>
-      <c r="M109" s="17" t="inlineStr"/>
-      <c r="N109" s="18" t="n">
+      <c r="B115" s="17" t="inlineStr"/>
+      <c r="C115" s="17" t="inlineStr"/>
+      <c r="D115" s="17" t="inlineStr"/>
+      <c r="E115" s="17" t="inlineStr"/>
+      <c r="F115" s="17" t="inlineStr"/>
+      <c r="G115" s="17" t="inlineStr"/>
+      <c r="H115" s="17" t="inlineStr"/>
+      <c r="I115" s="17" t="inlineStr"/>
+      <c r="J115" s="17" t="inlineStr"/>
+      <c r="K115" s="17" t="inlineStr"/>
+      <c r="L115" s="17" t="inlineStr"/>
+      <c r="M115" s="17" t="inlineStr"/>
+      <c r="N115" s="18" t="n">
         <v>47526.995</v>
       </c>
-      <c r="O109" s="18" t="n">
-        <v>10954.55</v>
-      </c>
-      <c r="P109" s="18" t="n">
-        <v>137.69</v>
+      <c r="O115" s="18" t="n">
+        <v>15986.17</v>
+      </c>
+      <c r="P115" s="18" t="n">
+        <v>177.51</v>
       </c>
     </row>
   </sheetData>
@@ -8516,6 +8942,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A106" r:id="rId102"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A107" r:id="rId103"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A108" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A109" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A110" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A111" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A112" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A113" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A114" r:id="rId110"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9273,26 +9705,26 @@
         </is>
       </c>
       <c r="B5" s="14" t="n">
-        <v>43</v>
+        <v>48.67</v>
       </c>
       <c r="C5" s="14" t="n">
-        <v>13.58</v>
+        <v>14.92</v>
       </c>
       <c r="D5" s="14" t="n">
         <v>5.75</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>62.33</v>
+        <v>69.33</v>
       </c>
       <c r="F5" s="14" t="n">
-        <v>10.67</v>
+        <v>11.17</v>
       </c>
       <c r="G5" s="14" t="n">
         <v>652.05</v>
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>10.6%</t>
         </is>
       </c>
     </row>
@@ -9303,7 +9735,7 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>13.75</v>
+        <v>17.25</v>
       </c>
       <c r="C6" s="11" t="n">
         <v>0</v>
@@ -9312,7 +9744,7 @@
         <v>2.5</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>16.25</v>
+        <v>19.75</v>
       </c>
       <c r="F6" s="11" t="n">
         <v>5.5</v>
@@ -9322,7 +9754,7 @@
       </c>
       <c r="H6" s="21" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>7.2%</t>
         </is>
       </c>
     </row>
@@ -9334,7 +9766,7 @@
         </is>
       </c>
       <c r="B8" s="23" t="n">
-        <v>38.25</v>
+        <v>41.25</v>
       </c>
     </row>
   </sheetData>
@@ -9419,22 +9851,22 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>396510</v>
+        <v>394981</v>
       </c>
       <c r="C5" s="24" t="n">
-        <v>165966</v>
+        <v>169150</v>
       </c>
       <c r="D5" s="24" t="n">
-        <v>230544</v>
+        <v>225831</v>
       </c>
       <c r="E5" s="24" t="n">
-        <v>141521</v>
+        <v>140842</v>
       </c>
       <c r="F5" s="24" t="n">
-        <v>19046</v>
+        <v>18223</v>
       </c>
       <c r="G5" s="24" t="n">
-        <v>24521</v>
+        <v>21338</v>
       </c>
     </row>
     <row r="6">
@@ -9444,16 +9876,16 @@
         </is>
       </c>
       <c r="B6" s="25" t="n">
-        <v>165355</v>
+        <v>164676</v>
       </c>
       <c r="C6" s="25" t="n">
         <v>62976</v>
       </c>
       <c r="D6" s="25" t="n">
-        <v>102379</v>
+        <v>101700</v>
       </c>
       <c r="E6" s="25" t="n">
-        <v>87495</v>
+        <v>86815</v>
       </c>
       <c r="F6" s="25" t="n">
         <v>9175</v>
@@ -9469,22 +9901,22 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>231155</v>
+        <v>230305</v>
       </c>
       <c r="C7" s="26" t="n">
-        <v>102990</v>
+        <v>106174</v>
       </c>
       <c r="D7" s="26" t="n">
-        <v>128164</v>
+        <v>124131</v>
       </c>
       <c r="E7" s="26" t="n">
         <v>54027</v>
       </c>
       <c r="F7" s="26" t="n">
-        <v>9871</v>
+        <v>9048</v>
       </c>
       <c r="G7" s="26" t="n">
-        <v>21336</v>
+        <v>18153</v>
       </c>
     </row>
   </sheetData>

--- a/jira_export_2026-09-09.xlsx
+++ b/jira_export_2026-09-09.xlsx
@@ -720,7 +720,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>15,986 €</t>
+          <t>17,397 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -734,7 +734,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>15.1%</t>
+          <t>16.4%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -760,7 +760,7 @@
     <row r="11" ht="26" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>4,036 €</t>
+          <t>5,446 €</t>
         </is>
       </c>
       <c r="B11" s="7" t="n"/>
@@ -815,7 +815,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>148 h</t>
+          <t>164 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -829,7 +829,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>49.3%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -2729,7 +2729,7 @@
         <v>3</v>
       </c>
       <c r="K28" s="14" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="L28" s="14" t="inlineStr">
         <is>
@@ -3033,10 +3033,10 @@
         <v>242.9</v>
       </c>
       <c r="O32" s="15" t="n">
-        <v>248.58</v>
+        <v>1242.9</v>
       </c>
       <c r="P32" s="15" t="n">
-        <v>124.29</v>
+        <v>621.45</v>
       </c>
     </row>
     <row r="33">
@@ -3449,7 +3449,7 @@
         <v>3</v>
       </c>
       <c r="K38" s="14" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="L38" s="14" t="inlineStr">
         <is>
@@ -3468,7 +3468,7 @@
         <v>679.5</v>
       </c>
       <c r="P38" s="15" t="n">
-        <v>1359</v>
+        <v>906</v>
       </c>
     </row>
     <row r="39">
@@ -6185,7 +6185,7 @@
         <v>8</v>
       </c>
       <c r="K76" s="14" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="L76" s="14" t="inlineStr">
         <is>
@@ -6257,7 +6257,7 @@
         <v>8</v>
       </c>
       <c r="K77" s="11" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="L77" s="11" t="inlineStr">
         <is>
@@ -6329,7 +6329,7 @@
         <v>8</v>
       </c>
       <c r="K78" s="14" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="L78" s="14" t="inlineStr">
         <is>
@@ -7183,10 +7183,10 @@
         <v>0</v>
       </c>
       <c r="O90" s="15" t="n">
-        <v>0</v>
+        <v>416.188</v>
       </c>
       <c r="P90" s="15" t="n">
-        <v>0</v>
+        <v>277.46</v>
       </c>
     </row>
     <row r="91">
@@ -7799,7 +7799,7 @@
         <v>17</v>
       </c>
       <c r="K99" s="11" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="L99" s="11" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         <v>21</v>
       </c>
       <c r="K105" s="11" t="n">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="L105" s="11" t="inlineStr"/>
       <c r="M105" s="11" t="inlineStr"/>
@@ -8829,10 +8829,10 @@
         <v>47526.995</v>
       </c>
       <c r="O115" s="18" t="n">
-        <v>15986.17</v>
+        <v>17396.678</v>
       </c>
       <c r="P115" s="18" t="n">
-        <v>177.51</v>
+        <v>185.45</v>
       </c>
     </row>
   </sheetData>
@@ -9705,16 +9705,16 @@
         </is>
       </c>
       <c r="B5" s="14" t="n">
-        <v>48.67</v>
+        <v>50.92</v>
       </c>
       <c r="C5" s="14" t="n">
-        <v>14.92</v>
+        <v>16.42</v>
       </c>
       <c r="D5" s="14" t="n">
         <v>5.75</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>69.33</v>
+        <v>73.08</v>
       </c>
       <c r="F5" s="14" t="n">
         <v>11.17</v>
@@ -9724,7 +9724,7 @@
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>11.2%</t>
         </is>
       </c>
     </row>
@@ -9766,7 +9766,7 @@
         </is>
       </c>
       <c r="B8" s="23" t="n">
-        <v>41.25</v>
+        <v>53.5</v>
       </c>
     </row>
   </sheetData>
@@ -9851,10 +9851,10 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>394981</v>
+        <v>393570</v>
       </c>
       <c r="C5" s="24" t="n">
-        <v>169150</v>
+        <v>167739</v>
       </c>
       <c r="D5" s="24" t="n">
         <v>225831</v>
@@ -9876,10 +9876,10 @@
         </is>
       </c>
       <c r="B6" s="25" t="n">
-        <v>164676</v>
+        <v>163265</v>
       </c>
       <c r="C6" s="25" t="n">
-        <v>62976</v>
+        <v>61566</v>
       </c>
       <c r="D6" s="25" t="n">
         <v>101700</v>

--- a/jira_export_2026-09-09.xlsx
+++ b/jira_export_2026-09-09.xlsx
@@ -720,7 +720,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>17,397 €</t>
+          <t>17,574 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -734,7 +734,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>16.4%</t>
+          <t>16.6%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -767,7 +767,7 @@
       <c r="C11" s="7" t="n"/>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>11,950 €</t>
+          <t>12,128 €</t>
         </is>
       </c>
       <c r="E11" s="7" t="n"/>
@@ -815,7 +815,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>164 h</t>
+          <t>166 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -829,7 +829,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>49.3%</t>
+          <t>49.8%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -900,7 +900,7 @@
       <c r="F25" s="7" t="n"/>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>273</t>
+          <t>274</t>
         </is>
       </c>
       <c r="H25" s="7" t="n"/>
@@ -933,7 +933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P115"/>
+  <dimension ref="A1:P118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -1970,12 +1970,12 @@
     <row r="18">
       <c r="A18" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34495</t>
+          <t>PDMDEP-34650</t>
         </is>
       </c>
       <c r="B18" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE CLICHY] - PRESTATION DE MODELISATION + integration RODP </t>
+          <t>[CD 01] -  Transfert de compétence Montée de version</t>
         </is>
       </c>
       <c r="C18" s="14" t="inlineStr">
@@ -1985,12 +1985,12 @@
       </c>
       <c r="D18" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE CLICHY</t>
+          <t>DEPARTEMENT DE L AIN (CD 01)</t>
         </is>
       </c>
       <c r="E18" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">PRESTATION DE MODELISATION + integration RODP </t>
+          <t xml:space="preserve"> Transfert de compétence Montée de version</t>
         </is>
       </c>
       <c r="F18" s="14" t="inlineStr">
@@ -2010,64 +2010,64 @@
       </c>
       <c r="I18" s="14" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>21/07/2026</t>
         </is>
       </c>
       <c r="J18" s="14" t="n">
         <v>2</v>
       </c>
       <c r="K18" s="14" t="n">
-        <v>3.5</v>
+        <v>1.25</v>
       </c>
       <c r="L18" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34499</t>
+          <t>PDMDEP-34654</t>
         </is>
       </c>
       <c r="M18" s="14" t="inlineStr">
         <is>
-          <t>00172678</t>
+          <t>00176582</t>
         </is>
       </c>
       <c r="N18" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O18" s="15" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="P18" s="15" t="n">
-        <v>12.29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34475</t>
+          <t>PDMDEP-34495</t>
         </is>
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>[Mairie de Pontcharra] - Migration simple placier</t>
+          <t xml:space="preserve">[COMMUNE DE CLICHY] - PRESTATION DE MODELISATION + integration RODP </t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
-          <t>Mairie de Pontcharra</t>
+          <t>COMMUNE DE CLICHY</t>
         </is>
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>Migration simple placier</t>
+          <t xml:space="preserve">PRESTATION DE MODELISATION + integration RODP </t>
         </is>
       </c>
       <c r="F19" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G19" s="11" t="inlineStr">
@@ -2077,49 +2077,49 @@
       </c>
       <c r="H19" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I19" s="11" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
       <c r="J19" s="11" t="n">
         <v>2</v>
       </c>
       <c r="K19" s="11" t="n">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="L19" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34481</t>
+          <t>PDMDEP-34499</t>
         </is>
       </c>
       <c r="M19" s="11" t="inlineStr">
         <is>
-          <t>00172611</t>
+          <t>00172678</t>
         </is>
       </c>
       <c r="N19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O19" s="12" t="n">
-        <v>105</v>
+        <v>43</v>
       </c>
       <c r="P19" s="12" t="n">
-        <v>70</v>
+        <v>12.29</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34411</t>
+          <t>PDMDEP-34475</t>
         </is>
       </c>
       <c r="B20" s="14" t="inlineStr">
         <is>
-          <t>[MAIRIE DE MAIZIERES LES METZ] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>[Mairie de Pontcharra] - Migration simple placier</t>
         </is>
       </c>
       <c r="C20" s="14" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="D20" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE MAIZIERES LES METZ</t>
+          <t>Mairie de Pontcharra</t>
         </is>
       </c>
       <c r="E20" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>Migration simple placier</t>
         </is>
       </c>
       <c r="F20" s="14" t="inlineStr">
@@ -2154,44 +2154,44 @@
       </c>
       <c r="I20" s="14" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
       <c r="J20" s="14" t="n">
         <v>2</v>
       </c>
       <c r="K20" s="14" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="L20" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34420</t>
+          <t>PDMDEP-34481</t>
         </is>
       </c>
       <c r="M20" s="14" t="inlineStr">
         <is>
-          <t>00172317</t>
+          <t>00172611</t>
         </is>
       </c>
       <c r="N20" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O20" s="15" t="n">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="P20" s="15" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34319</t>
+          <t>PDMDEP-34411</t>
         </is>
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>[Commune de Mouscron (BE)] - Migration GEODP Placier</t>
+          <t>[MAIRIE DE MAIZIERES LES METZ] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr">
@@ -2201,12 +2201,12 @@
       </c>
       <c r="D21" s="11" t="inlineStr">
         <is>
-          <t>Commune de Mouscron (BE)</t>
+          <t>MAIRIE DE MAIZIERES LES METZ</t>
         </is>
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier</t>
+          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="F21" s="11" t="inlineStr">
@@ -2226,29 +2226,29 @@
       </c>
       <c r="I21" s="11" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
       <c r="J21" s="11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K21" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34326</t>
+          <t>PDMDEP-34420</t>
         </is>
       </c>
       <c r="M21" s="11" t="inlineStr">
         <is>
-          <t>00171691</t>
+          <t>00172317</t>
         </is>
       </c>
       <c r="N21" s="12" t="n">
-        <v>769.5</v>
-      </c>
-      <c r="O21" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P21" s="12" t="n">
@@ -2258,27 +2258,27 @@
     <row r="22">
       <c r="A22" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34287</t>
+          <t>PDMDEP-34319</t>
         </is>
       </c>
       <c r="B22" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE LUNEL] - Migration GeODP </t>
+          <t>[Commune de Mouscron (BE)] - Migration GEODP Placier</t>
         </is>
       </c>
       <c r="C22" s="14" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D22" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE LUNEL</t>
+          <t>Commune de Mouscron (BE)</t>
         </is>
       </c>
       <c r="E22" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GeODP </t>
+          <t>Migration GEODP Placier</t>
         </is>
       </c>
       <c r="F22" s="14" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="G22" s="14" t="inlineStr">
         <is>
-          <t>Prestation offerte</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H22" s="14" t="inlineStr">
@@ -2298,21 +2298,29 @@
       </c>
       <c r="I22" s="14" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="J22" s="14" t="n">
         <v>3</v>
       </c>
       <c r="K22" s="14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L22" s="14" t="inlineStr"/>
-      <c r="M22" s="14" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L22" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-34326</t>
+        </is>
+      </c>
+      <c r="M22" s="14" t="inlineStr">
+        <is>
+          <t>00171691</t>
+        </is>
+      </c>
       <c r="N22" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" s="15" t="n">
+        <v>769.5</v>
+      </c>
+      <c r="O22" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P22" s="15" t="n">
@@ -2322,27 +2330,27 @@
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34249</t>
+          <t>PDMDEP-34287</t>
         </is>
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE VIENNE] - Migration Placier et ODP </t>
+          <t xml:space="preserve">[COMMUNE DE LUNEL] - Migration GeODP </t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE VIENNE</t>
+          <t>COMMUNE DE LUNEL</t>
         </is>
       </c>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration Placier et ODP </t>
+          <t xml:space="preserve">Migration GeODP </t>
         </is>
       </c>
       <c r="F23" s="11" t="inlineStr">
@@ -2352,7 +2360,7 @@
       </c>
       <c r="G23" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Prestation offerte</t>
         </is>
       </c>
       <c r="H23" s="11" t="inlineStr">
@@ -2369,22 +2377,14 @@
         <v>3</v>
       </c>
       <c r="K23" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-34258</t>
-        </is>
-      </c>
-      <c r="M23" s="11" t="inlineStr">
-        <is>
-          <t>00171361</t>
-        </is>
-      </c>
+        <v>2.5</v>
+      </c>
+      <c r="L23" s="11" t="inlineStr"/>
+      <c r="M23" s="11" t="inlineStr"/>
       <c r="N23" s="12" t="n">
-        <v>2127.2</v>
-      </c>
-      <c r="O23" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P23" s="12" t="n">
@@ -2394,32 +2394,32 @@
     <row r="24">
       <c r="A24" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34229</t>
+          <t>PDMDEP-34249</t>
         </is>
       </c>
       <c r="B24" s="14" t="inlineStr">
         <is>
-          <t>[DIJON METROPOLE] - GRC + Connecteur</t>
+          <t xml:space="preserve">[COMMUNE DE VIENNE] - Migration Placier et ODP </t>
         </is>
       </c>
       <c r="C24" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D24" s="14" t="inlineStr">
         <is>
-          <t>DIJON METROPOLE</t>
+          <t>COMMUNE DE VIENNE</t>
         </is>
       </c>
       <c r="E24" s="14" t="inlineStr">
         <is>
-          <t>GRC + Connecteur</t>
+          <t xml:space="preserve">Migration Placier et ODP </t>
         </is>
       </c>
       <c r="F24" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G24" s="14" t="inlineStr">
@@ -2429,69 +2429,69 @@
       </c>
       <c r="H24" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I24" s="14" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="J24" s="14" t="n">
         <v>3</v>
       </c>
       <c r="K24" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L24" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34235</t>
+          <t>PDMDEP-34258</t>
         </is>
       </c>
       <c r="M24" s="14" t="inlineStr">
         <is>
-          <t>00171333</t>
+          <t>00171361</t>
         </is>
       </c>
       <c r="N24" s="15" t="n">
-        <v>4536</v>
+        <v>2127.2</v>
       </c>
       <c r="O24" s="16" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="P24" s="15" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34208</t>
+          <t>PDMDEP-34229</t>
         </is>
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE CHATEAUGIRON] - Migration GEODP Placier 2</t>
+          <t>[DIJON METROPOLE] - GRC + Connecteur</t>
         </is>
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D25" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHATEAUGIRON</t>
+          <t>DIJON METROPOLE</t>
         </is>
       </c>
       <c r="E25" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier 2</t>
+          <t>GRC + Connecteur</t>
         </is>
       </c>
       <c r="F25" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G25" s="11" t="inlineStr">
@@ -2501,49 +2501,49 @@
       </c>
       <c r="H25" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I25" s="11" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="J25" s="11" t="n">
         <v>3</v>
       </c>
       <c r="K25" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L25" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34216</t>
+          <t>PDMDEP-34235</t>
         </is>
       </c>
       <c r="M25" s="11" t="inlineStr">
         <is>
-          <t>00171155</t>
+          <t>00171333</t>
         </is>
       </c>
       <c r="N25" s="12" t="n">
-        <v>525</v>
+        <v>4536</v>
       </c>
       <c r="O25" s="16" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="P25" s="12" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34192</t>
+          <t>PDMDEP-34208</t>
         </is>
       </c>
       <c r="B26" s="14" t="inlineStr">
         <is>
-          <t>[Commune de Macon ] - GEODP Placier</t>
+          <t>[COMMUNE DE CHATEAUGIRON] - Migration GEODP Placier 2</t>
         </is>
       </c>
       <c r="C26" s="14" t="inlineStr">
@@ -2553,12 +2553,12 @@
       </c>
       <c r="D26" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Commune de Macon </t>
+          <t>COMMUNE DE CHATEAUGIRON</t>
         </is>
       </c>
       <c r="E26" s="14" t="inlineStr">
         <is>
-          <t>GEODP Placier</t>
+          <t>Migration GEODP Placier 2</t>
         </is>
       </c>
       <c r="F26" s="14" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="H26" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I26" s="14" t="inlineStr">
@@ -2585,52 +2585,52 @@
         <v>3</v>
       </c>
       <c r="K26" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L26" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34201</t>
+          <t>PDMDEP-34216</t>
         </is>
       </c>
       <c r="M26" s="14" t="inlineStr">
         <is>
-          <t>00171162</t>
+          <t>00171155</t>
         </is>
       </c>
       <c r="N26" s="15" t="n">
-        <v>1662</v>
+        <v>525</v>
       </c>
       <c r="O26" s="16" t="n">
-        <v>277</v>
+        <v>0</v>
       </c>
       <c r="P26" s="15" t="n">
-        <v>277</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34169</t>
+          <t>PDMDEP-34192</t>
         </is>
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE] - Migration GEODP 1 vers GEODP 2</t>
+          <t>[Commune de Macon ] - GEODP Placier</t>
         </is>
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D27" s="11" t="inlineStr">
         <is>
-          <t>COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE</t>
+          <t xml:space="preserve">Commune de Macon </t>
         </is>
       </c>
       <c r="E27" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2</t>
+          <t>GEODP Placier</t>
         </is>
       </c>
       <c r="F27" s="11" t="inlineStr">
@@ -2645,69 +2645,69 @@
       </c>
       <c r="H27" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I27" s="11" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="J27" s="11" t="n">
         <v>3</v>
       </c>
       <c r="K27" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L27" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34227</t>
+          <t>PDMDEP-34201</t>
         </is>
       </c>
       <c r="M27" s="11" t="inlineStr">
         <is>
-          <t>2026-0210095</t>
+          <t>00171162</t>
         </is>
       </c>
       <c r="N27" s="12" t="n">
-        <v>9623.1</v>
+        <v>1662</v>
       </c>
       <c r="O27" s="16" t="n">
-        <v>3849.24</v>
+        <v>277</v>
       </c>
       <c r="P27" s="12" t="n">
-        <v>0</v>
+        <v>277</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34126</t>
+          <t>PDMDEP-34169</t>
         </is>
       </c>
       <c r="B28" s="14" t="inlineStr">
         <is>
-          <t>[SETE] - AME LiEx</t>
+          <t>[COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE] - Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="C28" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D28" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE SETE</t>
+          <t>COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE</t>
         </is>
       </c>
       <c r="E28" s="14" t="inlineStr">
         <is>
-          <t>AME LiEx</t>
+          <t>Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="F28" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G28" s="14" t="inlineStr">
@@ -2717,35 +2717,35 @@
       </c>
       <c r="H28" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I28" s="14" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="J28" s="14" t="n">
         <v>3</v>
       </c>
       <c r="K28" s="14" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L28" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34130</t>
+          <t>PDMDEP-34227</t>
         </is>
       </c>
       <c r="M28" s="14" t="inlineStr">
         <is>
-          <t>00170928</t>
+          <t>2026-0210095</t>
         </is>
       </c>
       <c r="N28" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" s="15" t="n">
-        <v>0</v>
+        <v>9623.1</v>
+      </c>
+      <c r="O28" s="16" t="n">
+        <v>3849.24</v>
       </c>
       <c r="P28" s="15" t="n">
         <v>0</v>
@@ -2754,32 +2754,32 @@
     <row r="29">
       <c r="A29" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34108</t>
+          <t>PDMDEP-34126</t>
         </is>
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DU PUY EN VELAY] - Migration GeODP Placier + migration ODP</t>
+          <t>[SETE] - AME LiEx</t>
         </is>
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D29" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DU PUY EN VELAY</t>
+          <t>COMMUNE DE SETE</t>
         </is>
       </c>
       <c r="E29" s="11" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier + migration ODP</t>
+          <t>AME LiEx</t>
         </is>
       </c>
       <c r="F29" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G29" s="11" t="inlineStr">
@@ -2789,7 +2789,7 @@
       </c>
       <c r="H29" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I29" s="11" t="inlineStr">
@@ -2801,22 +2801,22 @@
         <v>3</v>
       </c>
       <c r="K29" s="11" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L29" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34117</t>
+          <t>PDMDEP-34130</t>
         </is>
       </c>
       <c r="M29" s="11" t="inlineStr">
         <is>
-          <t>00170907</t>
+          <t>00170928</t>
         </is>
       </c>
       <c r="N29" s="12" t="n">
-        <v>707</v>
-      </c>
-      <c r="O29" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P29" s="12" t="n">
@@ -2826,12 +2826,12 @@
     <row r="30">
       <c r="A30" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34064</t>
+          <t>PDMDEP-34108</t>
         </is>
       </c>
       <c r="B30" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[VILLE DE VANNES] - ORMC pour GEODP PLACIER </t>
+          <t>[COMMUNE DU PUY EN VELAY] - Migration GeODP Placier + migration ODP</t>
         </is>
       </c>
       <c r="C30" s="14" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="D30" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE VANNES</t>
+          <t>COMMUNE DU PUY EN VELAY</t>
         </is>
       </c>
       <c r="E30" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">ORMC pour GEODP PLACIER </t>
+          <t>Migration GeODP Placier + migration ODP</t>
         </is>
       </c>
       <c r="F30" s="14" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="H30" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I30" s="14" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="J30" s="14" t="n">
@@ -2877,16 +2877,16 @@
       </c>
       <c r="L30" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34070</t>
+          <t>PDMDEP-34117</t>
         </is>
       </c>
       <c r="M30" s="14" t="inlineStr">
         <is>
-          <t>00170468</t>
+          <t>00170907</t>
         </is>
       </c>
       <c r="N30" s="15" t="n">
-        <v>300</v>
+        <v>707</v>
       </c>
       <c r="O30" s="16" t="n">
         <v>0</v>
@@ -2898,27 +2898,27 @@
     <row r="31">
       <c r="A31" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33985</t>
+          <t>PDMDEP-34081</t>
         </is>
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE QUIMPERLE] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>[COMMUNE DE ERQUY] - Migration GEODP Placier + Pax</t>
         </is>
       </c>
       <c r="C31" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D31" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE QUIMPERLE</t>
+          <t>COMMUNE DE ERQUY</t>
         </is>
       </c>
       <c r="E31" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>Migration GEODP 2 + Pax</t>
         </is>
       </c>
       <c r="F31" s="11" t="inlineStr">
@@ -2938,7 +2938,7 @@
       </c>
       <c r="I31" s="11" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="J31" s="11" t="n">
@@ -2949,19 +2949,19 @@
       </c>
       <c r="L31" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33991</t>
+          <t>PDMDEP-34090</t>
         </is>
       </c>
       <c r="M31" s="11" t="inlineStr">
         <is>
-          <t>00170408</t>
+          <t>00170724</t>
         </is>
       </c>
       <c r="N31" s="12" t="n">
-        <v>510</v>
-      </c>
-      <c r="O31" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O31" s="12" t="n">
+        <v>177.5</v>
       </c>
       <c r="P31" s="12" t="n">
         <v>0</v>
@@ -2970,32 +2970,32 @@
     <row r="32">
       <c r="A32" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33949</t>
+          <t>PDMDEP-34064</t>
         </is>
       </c>
       <c r="B32" s="14" t="inlineStr">
         <is>
-          <t>[Commune de Colmar] - Modélisation Littéralis Expert et Démarrage Prod</t>
+          <t xml:space="preserve">[VILLE DE VANNES] - ORMC pour GEODP PLACIER </t>
         </is>
       </c>
       <c r="C32" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D32" s="14" t="inlineStr">
         <is>
-          <t>Commune de Colmar</t>
+          <t>VILLE DE VANNES</t>
         </is>
       </c>
       <c r="E32" s="14" t="inlineStr">
         <is>
-          <t>Modélisation Littéralis Expert</t>
+          <t xml:space="preserve">ORMC pour GEODP PLACIER </t>
         </is>
       </c>
       <c r="F32" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G32" s="14" t="inlineStr">
@@ -3010,64 +3010,64 @@
       </c>
       <c r="I32" s="14" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="J32" s="14" t="n">
         <v>3</v>
       </c>
       <c r="K32" s="14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L32" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33955</t>
+          <t>PDMDEP-34070</t>
         </is>
       </c>
       <c r="M32" s="14" t="inlineStr">
         <is>
-          <t>00170302</t>
+          <t>00170468</t>
         </is>
       </c>
       <c r="N32" s="15" t="n">
-        <v>242.9</v>
-      </c>
-      <c r="O32" s="15" t="n">
-        <v>1242.9</v>
+        <v>300</v>
+      </c>
+      <c r="O32" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P32" s="15" t="n">
-        <v>621.45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33940</t>
+          <t>PDMDEP-33985</t>
         </is>
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de Thionville] - AME </t>
+          <t>[COMMUNE DE QUIMPERLE] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="C33" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D33" s="11" t="inlineStr">
         <is>
-          <t>Commune de Thionville</t>
+          <t>COMMUNE DE QUIMPERLE</t>
         </is>
       </c>
       <c r="E33" s="11" t="inlineStr">
         <is>
-          <t>AME Littéralis Expert</t>
+          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="F33" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G33" s="11" t="inlineStr">
@@ -3077,12 +3077,12 @@
       </c>
       <c r="H33" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I33" s="11" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="J33" s="11" t="n">
@@ -3093,16 +3093,16 @@
       </c>
       <c r="L33" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33944</t>
+          <t>PDMDEP-33991</t>
         </is>
       </c>
       <c r="M33" s="11" t="inlineStr">
         <is>
-          <t>00170299</t>
+          <t>00170408</t>
         </is>
       </c>
       <c r="N33" s="12" t="n">
-        <v>220</v>
+        <v>510</v>
       </c>
       <c r="O33" s="16" t="n">
         <v>0</v>
@@ -3114,27 +3114,27 @@
     <row r="34">
       <c r="A34" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33813</t>
+          <t>PDMDEP-33949</t>
         </is>
       </c>
       <c r="B34" s="14" t="inlineStr">
         <is>
-          <t>[METROPOLE TOULON-PROVENCE-MEDITERRANEE] - Modélisation Seyne S/ Mer</t>
+          <t>[Commune de Colmar] - Modélisation Littéralis Expert et Démarrage Prod</t>
         </is>
       </c>
       <c r="C34" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D34" s="14" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
+          <t>Commune de Colmar</t>
         </is>
       </c>
       <c r="E34" s="14" t="inlineStr">
         <is>
-          <t>Modélisation Seyne S/ Mer</t>
+          <t>Modélisation Littéralis Expert</t>
         </is>
       </c>
       <c r="F34" s="14" t="inlineStr">
@@ -3154,44 +3154,44 @@
       </c>
       <c r="I34" s="14" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="J34" s="14" t="n">
         <v>3</v>
       </c>
       <c r="K34" s="14" t="n">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="L34" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33817</t>
+          <t>PDMDEP-33955</t>
         </is>
       </c>
       <c r="M34" s="14" t="inlineStr">
         <is>
-          <t>00169865</t>
+          <t>00170302</t>
         </is>
       </c>
       <c r="N34" s="15" t="n">
-        <v>0</v>
+        <v>242.9</v>
       </c>
       <c r="O34" s="15" t="n">
-        <v>65.73</v>
+        <v>1242.9</v>
       </c>
       <c r="P34" s="15" t="n">
-        <v>52.58</v>
+        <v>621.45</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33804</t>
+          <t>PDMDEP-33940</t>
         </is>
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>[CD 73)] - Purge arrêtés temporaires</t>
+          <t xml:space="preserve">[Commune de Thionville] - AME </t>
         </is>
       </c>
       <c r="C35" s="11" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="D35" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE LA SAVOIE (CD 73)</t>
+          <t>Commune de Thionville</t>
         </is>
       </c>
       <c r="E35" s="11" t="inlineStr">
         <is>
-          <t>Purge arrêtés temporaires</t>
+          <t>AME Littéralis Expert</t>
         </is>
       </c>
       <c r="F35" s="11" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="I35" s="11" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="J35" s="11" t="n">
@@ -3237,16 +3237,16 @@
       </c>
       <c r="L35" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33808</t>
+          <t>PDMDEP-33944</t>
         </is>
       </c>
       <c r="M35" s="11" t="inlineStr">
         <is>
-          <t>00169856</t>
+          <t>00170299</t>
         </is>
       </c>
       <c r="N35" s="12" t="n">
-        <v>1890</v>
+        <v>220</v>
       </c>
       <c r="O35" s="16" t="n">
         <v>0</v>
@@ -3258,27 +3258,27 @@
     <row r="36">
       <c r="A36" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33790</t>
+          <t>PDMDEP-33813</t>
         </is>
       </c>
       <c r="B36" s="14" t="inlineStr">
         <is>
-          <t>[CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91)] - Commande modélisation supplémentaire - 6,5j</t>
+          <t>[METROPOLE TOULON-PROVENCE-MEDITERRANEE] - Modélisation Seyne S/ Mer</t>
         </is>
       </c>
       <c r="C36" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D36" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
         </is>
       </c>
       <c r="E36" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Commande modélisation supplémentaire </t>
+          <t>Modélisation Seyne S/ Mer</t>
         </is>
       </c>
       <c r="F36" s="14" t="inlineStr">
@@ -3298,59 +3298,59 @@
       </c>
       <c r="I36" s="14" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="J36" s="14" t="n">
         <v>3</v>
       </c>
       <c r="K36" s="14" t="n">
-        <v>3.75</v>
+        <v>1.25</v>
       </c>
       <c r="L36" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33794</t>
+          <t>PDMDEP-33817</t>
         </is>
       </c>
       <c r="M36" s="14" t="inlineStr">
         <is>
-          <t>00169697</t>
+          <t>00169865</t>
         </is>
       </c>
       <c r="N36" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O36" s="15" t="n">
-        <v>266.2</v>
+        <v>65.73</v>
       </c>
       <c r="P36" s="15" t="n">
-        <v>70.98999999999999</v>
+        <v>52.58</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33739</t>
+          <t>PDMDEP-33804</t>
         </is>
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DU POIRE SUR VIE (MAIRIE)] - UPSELL Pastell + Portail DA DPA</t>
+          <t>[CD 73)] - Purge arrêtés temporaires</t>
         </is>
       </c>
       <c r="C37" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D37" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DU POIRE SUR VIE (MAIRIE)</t>
+          <t>CONSEIL DEPARTEMENTAL DE LA SAVOIE (CD 73)</t>
         </is>
       </c>
       <c r="E37" s="11" t="inlineStr">
         <is>
-          <t>UPSELL PASTELL + DA DPA</t>
+          <t>Purge arrêtés temporaires</t>
         </is>
       </c>
       <c r="F37" s="11" t="inlineStr">
@@ -3370,27 +3370,27 @@
       </c>
       <c r="I37" s="11" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="J37" s="11" t="n">
         <v>3</v>
       </c>
       <c r="K37" s="11" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="L37" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33745</t>
+          <t>PDMDEP-33808</t>
         </is>
       </c>
       <c r="M37" s="11" t="inlineStr">
         <is>
-          <t>00169509</t>
+          <t>00169856</t>
         </is>
       </c>
       <c r="N37" s="12" t="n">
-        <v>920</v>
+        <v>1890</v>
       </c>
       <c r="O37" s="16" t="n">
         <v>0</v>
@@ -3402,27 +3402,27 @@
     <row r="38">
       <c r="A38" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33729</t>
+          <t>PDMDEP-33790</t>
         </is>
       </c>
       <c r="B38" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[VILLE DE NEUILLY SUR SEINE - Direction des systèmes d'information] - MONTEE DE VERSION LITT EXP  test et prod </t>
+          <t>[CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91)] - Commande modélisation supplémentaire - 6,5j</t>
         </is>
       </c>
       <c r="C38" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D38" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE NEUILLY SUR SEINE - Direction des systèmes d'information</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
         </is>
       </c>
       <c r="E38" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">MONTEE DE VERSION LITT EXP  test et prod </t>
+          <t xml:space="preserve">Commande modélisation supplémentaire </t>
         </is>
       </c>
       <c r="F38" s="14" t="inlineStr">
@@ -3442,59 +3442,59 @@
       </c>
       <c r="I38" s="14" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="J38" s="14" t="n">
         <v>3</v>
       </c>
       <c r="K38" s="14" t="n">
-        <v>0.75</v>
+        <v>3.75</v>
       </c>
       <c r="L38" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33733</t>
+          <t>PDMDEP-33794</t>
         </is>
       </c>
       <c r="M38" s="14" t="inlineStr">
         <is>
-          <t>00169480</t>
+          <t>00169697</t>
         </is>
       </c>
       <c r="N38" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O38" s="15" t="n">
-        <v>679.5</v>
+        <v>266.2</v>
       </c>
       <c r="P38" s="15" t="n">
-        <v>906</v>
+        <v>70.98999999999999</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33699</t>
+          <t>PDMDEP-33739</t>
         </is>
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>[CD 35)] - Montée de version Littéralis - 1 journée d'assistance fonctionnelle à distance</t>
+          <t>[COMMUNE DU POIRE SUR VIE (MAIRIE)] - UPSELL Pastell + Portail DA DPA</t>
         </is>
       </c>
       <c r="C39" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D39" s="11" t="inlineStr">
         <is>
-          <t>DEPARTEMENT D'ILLE ET VILAINE (CD 35)</t>
+          <t>COMMUNE DU POIRE SUR VIE (MAIRIE)</t>
         </is>
       </c>
       <c r="E39" s="11" t="inlineStr">
         <is>
-          <t>Montée de version Littéralis - 1 journée d'assistance fonctionnelle à distance</t>
+          <t>UPSELL PASTELL + DA DPA</t>
         </is>
       </c>
       <c r="F39" s="11" t="inlineStr">
@@ -3514,64 +3514,64 @@
       </c>
       <c r="I39" s="11" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="J39" s="11" t="n">
         <v>3</v>
       </c>
       <c r="K39" s="11" t="n">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
       <c r="L39" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33703</t>
+          <t>PDMDEP-33745</t>
         </is>
       </c>
       <c r="M39" s="11" t="inlineStr">
         <is>
-          <t>00169363</t>
+          <t>00169509</t>
         </is>
       </c>
       <c r="N39" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O39" s="12" t="n">
-        <v>540</v>
+        <v>920</v>
+      </c>
+      <c r="O39" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P39" s="12" t="n">
-        <v>720</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33610</t>
+          <t>PDMDEP-33729</t>
         </is>
       </c>
       <c r="B40" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE MORLAIX] - Migration GEODP Placier hors matériel </t>
+          <t xml:space="preserve">[VILLE DE NEUILLY SUR SEINE - Direction des systèmes d'information] - MONTEE DE VERSION LITT EXP  test et prod </t>
         </is>
       </c>
       <c r="C40" s="14" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D40" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE MORLAIX</t>
+          <t>VILLE DE NEUILLY SUR SEINE - Direction des systèmes d'information</t>
         </is>
       </c>
       <c r="E40" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">MIGRATION GEODP PLACIER hors matériel </t>
+          <t xml:space="preserve">MONTEE DE VERSION LITT EXP  test et prod </t>
         </is>
       </c>
       <c r="F40" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G40" s="14" t="inlineStr">
@@ -3581,69 +3581,69 @@
       </c>
       <c r="H40" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I40" s="14" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="J40" s="14" t="n">
         <v>3</v>
       </c>
       <c r="K40" s="14" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="L40" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33616</t>
+          <t>PDMDEP-33733</t>
         </is>
       </c>
       <c r="M40" s="14" t="inlineStr">
         <is>
-          <t>00169015</t>
+          <t>00169480</t>
         </is>
       </c>
       <c r="N40" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O40" s="15" t="n">
-        <v>505</v>
+        <v>679.5</v>
       </c>
       <c r="P40" s="15" t="n">
-        <v>0</v>
+        <v>906</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33597</t>
+          <t>PDMDEP-33699</t>
         </is>
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>[Commune de Trets] - Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
+          <t>[CD 35)] - Montée de version Littéralis - 1 journée d'assistance fonctionnelle à distance</t>
         </is>
       </c>
       <c r="C41" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D41" s="11" t="inlineStr">
         <is>
-          <t>Commune de Trets</t>
+          <t>DEPARTEMENT D'ILLE ET VILAINE (CD 35)</t>
         </is>
       </c>
       <c r="E41" s="11" t="inlineStr">
         <is>
-          <t>Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
+          <t>Montée de version Littéralis - 1 journée d'assistance fonctionnelle à distance</t>
         </is>
       </c>
       <c r="F41" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G41" s="11" t="inlineStr">
@@ -3658,59 +3658,59 @@
       </c>
       <c r="I41" s="11" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="J41" s="11" t="n">
         <v>3</v>
       </c>
       <c r="K41" s="11" t="n">
-        <v>3</v>
+        <v>0.75</v>
       </c>
       <c r="L41" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33605</t>
+          <t>PDMDEP-33703</t>
         </is>
       </c>
       <c r="M41" s="11" t="inlineStr">
         <is>
-          <t>00168993</t>
+          <t>00169363</t>
         </is>
       </c>
       <c r="N41" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O41" s="12" t="n">
-        <v>0</v>
+        <v>540</v>
       </c>
       <c r="P41" s="12" t="n">
-        <v>0</v>
+        <v>720</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33500</t>
+          <t>PDMDEP-33610</t>
         </is>
       </c>
       <c r="B42" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Mairie de Carcès ] - GEODP PLACIER avec PAIEMENT CB </t>
+          <t xml:space="preserve">[COMMUNE DE MORLAIX] - Migration GEODP Placier hors matériel </t>
         </is>
       </c>
       <c r="C42" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D42" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mairie de Carcès </t>
+          <t>COMMUNE DE MORLAIX</t>
         </is>
       </c>
       <c r="E42" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">GEODP PLACIER avec PAIEMENT CB </t>
+          <t xml:space="preserve">MIGRATION GEODP PLACIER hors matériel </t>
         </is>
       </c>
       <c r="F42" s="14" t="inlineStr">
@@ -3725,69 +3725,69 @@
       </c>
       <c r="H42" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I42" s="14" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="J42" s="14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K42" s="14" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="L42" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33509</t>
+          <t>PDMDEP-33616</t>
         </is>
       </c>
       <c r="M42" s="14" t="inlineStr">
         <is>
-          <t>00168117</t>
+          <t>00169015</t>
         </is>
       </c>
       <c r="N42" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O42" s="15" t="n">
-        <v>691.9</v>
+        <v>505</v>
       </c>
       <c r="P42" s="15" t="n">
-        <v>461.27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33471</t>
+          <t>PDMDEP-33597</t>
         </is>
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE D AUCH] - FDS Facture LiS</t>
+          <t>[Commune de Trets] - Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
         </is>
       </c>
       <c r="C43" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D43" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE D AUCH</t>
+          <t>Commune de Trets</t>
         </is>
       </c>
       <c r="E43" s="11" t="inlineStr">
         <is>
-          <t>FDS Facture LiS</t>
+          <t>Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
         </is>
       </c>
       <c r="F43" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G43" s="11" t="inlineStr">
@@ -3802,29 +3802,29 @@
       </c>
       <c r="I43" s="11" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="J43" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K43" s="11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L43" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33475</t>
+          <t>PDMDEP-33605</t>
         </is>
       </c>
       <c r="M43" s="11" t="inlineStr">
         <is>
-          <t>00168025</t>
+          <t>00168993</t>
         </is>
       </c>
       <c r="N43" s="12" t="n">
-        <v>171.4</v>
-      </c>
-      <c r="O43" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P43" s="12" t="n">
@@ -3834,27 +3834,27 @@
     <row r="44">
       <c r="A44" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33431</t>
+          <t>PDMDEP-33500</t>
         </is>
       </c>
       <c r="B44" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE VERSAILLES] - Migration multi-modules (hors taxi) </t>
+          <t xml:space="preserve">[Mairie de Carcès ] - GEODP PLACIER avec PAIEMENT CB </t>
         </is>
       </c>
       <c r="C44" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D44" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">COMMUNE DE VERSAILLES </t>
+          <t xml:space="preserve">Mairie de Carcès </t>
         </is>
       </c>
       <c r="E44" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration multi-modules (hors taxi) </t>
+          <t xml:space="preserve">GEODP PLACIER avec PAIEMENT CB </t>
         </is>
       </c>
       <c r="F44" s="14" t="inlineStr">
@@ -3869,69 +3869,69 @@
       </c>
       <c r="H44" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I44" s="14" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="J44" s="14" t="n">
         <v>4</v>
       </c>
       <c r="K44" s="14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="L44" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33440</t>
+          <t>PDMDEP-33509</t>
         </is>
       </c>
       <c r="M44" s="14" t="inlineStr">
         <is>
-          <t>00166923</t>
+          <t>00168117</t>
         </is>
       </c>
       <c r="N44" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O44" s="15" t="n">
-        <v>3339.2</v>
+        <v>691.9</v>
       </c>
       <c r="P44" s="15" t="n">
-        <v>0</v>
+        <v>461.27</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33395</t>
+          <t>PDMDEP-33471</t>
         </is>
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE MONTBELIARD] - Mise en place paiement CB sur PAX présent sur la commune </t>
+          <t>[COMMUNE D AUCH] - FDS Facture LiS</t>
         </is>
       </c>
       <c r="C45" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D45" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTBELIARD</t>
+          <t>COMMUNE D AUCH</t>
         </is>
       </c>
       <c r="E45" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mise en place paiement CB sur PAX présent sur la commune </t>
+          <t>FDS Facture LiS</t>
         </is>
       </c>
       <c r="F45" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G45" s="11" t="inlineStr">
@@ -3946,7 +3946,7 @@
       </c>
       <c r="I45" s="11" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="J45" s="11" t="n">
@@ -3957,16 +3957,16 @@
       </c>
       <c r="L45" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33401</t>
+          <t>PDMDEP-33475</t>
         </is>
       </c>
       <c r="M45" s="11" t="inlineStr">
         <is>
-          <t>00167624</t>
+          <t>00168025</t>
         </is>
       </c>
       <c r="N45" s="12" t="n">
-        <v>344</v>
+        <v>171.4</v>
       </c>
       <c r="O45" s="16" t="n">
         <v>0</v>
@@ -3978,12 +3978,12 @@
     <row r="46">
       <c r="A46" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33266</t>
+          <t>PDMDEP-33431</t>
         </is>
       </c>
       <c r="B46" s="14" t="inlineStr">
         <is>
-          <t>[MAIRIE DE CAPBRETON] - Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
+          <t xml:space="preserve">[COMMUNE DE VERSAILLES] - Migration multi-modules (hors taxi) </t>
         </is>
       </c>
       <c r="C46" s="14" t="inlineStr">
@@ -3993,12 +3993,12 @@
       </c>
       <c r="D46" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE CAPBRETON</t>
+          <t xml:space="preserve">COMMUNE DE VERSAILLES </t>
         </is>
       </c>
       <c r="E46" s="14" t="inlineStr">
         <is>
-          <t>Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
+          <t xml:space="preserve">Migration multi-modules (hors taxi) </t>
         </is>
       </c>
       <c r="F46" s="14" t="inlineStr">
@@ -4013,12 +4013,12 @@
       </c>
       <c r="H46" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I46" s="14" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="J46" s="14" t="n">
@@ -4029,19 +4029,19 @@
       </c>
       <c r="L46" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33272</t>
+          <t>PDMDEP-33440</t>
         </is>
       </c>
       <c r="M46" s="14" t="inlineStr">
         <is>
-          <t>00166910</t>
+          <t>00166923</t>
         </is>
       </c>
       <c r="N46" s="15" t="n">
-        <v>500</v>
-      </c>
-      <c r="O46" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O46" s="15" t="n">
+        <v>3339.2</v>
       </c>
       <c r="P46" s="15" t="n">
         <v>0</v>
@@ -4050,12 +4050,12 @@
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33239</t>
+          <t>PDMDEP-33395</t>
         </is>
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>[MAIRIE DE LODEVE] - Migracier activité Placier vers Geodp V2</t>
+          <t xml:space="preserve">[COMMUNE DE MONTBELIARD] - Mise en place paiement CB sur PAX présent sur la commune </t>
         </is>
       </c>
       <c r="C47" s="11" t="inlineStr">
@@ -4065,12 +4065,12 @@
       </c>
       <c r="D47" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE LODEVE</t>
+          <t>COMMUNE DE MONTBELIARD</t>
         </is>
       </c>
       <c r="E47" s="11" t="inlineStr">
         <is>
-          <t>Migracier activité Placier vers Geodp V2</t>
+          <t xml:space="preserve">Mise en place paiement CB sur PAX présent sur la commune </t>
         </is>
       </c>
       <c r="F47" s="11" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="H47" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I47" s="11" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="J47" s="11" t="n">
@@ -4101,16 +4101,16 @@
       </c>
       <c r="L47" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33245</t>
+          <t>PDMDEP-33401</t>
         </is>
       </c>
       <c r="M47" s="11" t="inlineStr">
         <is>
-          <t>00166748</t>
+          <t>00167624</t>
         </is>
       </c>
       <c r="N47" s="12" t="n">
-        <v>149</v>
+        <v>344</v>
       </c>
       <c r="O47" s="16" t="n">
         <v>0</v>
@@ -4122,32 +4122,32 @@
     <row r="48">
       <c r="A48" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33227</t>
+          <t>PDMDEP-33266</t>
         </is>
       </c>
       <c r="B48" s="14" t="inlineStr">
         <is>
-          <t>[METROPOLE EUROPEENNE DE LILLE] - MEL Crédits 21 heures (3j)     mai 2026</t>
+          <t>[MAIRIE DE CAPBRETON] - Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
         </is>
       </c>
       <c r="C48" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D48" s="14" t="inlineStr">
         <is>
-          <t>METROPOLE EUROPEENNE DE LILLE</t>
+          <t>MAIRIE DE CAPBRETON</t>
         </is>
       </c>
       <c r="E48" s="14" t="inlineStr">
         <is>
-          <t>21 crédits d'heure</t>
+          <t>Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
         </is>
       </c>
       <c r="F48" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G48" s="14" t="inlineStr">
@@ -4162,64 +4162,64 @@
       </c>
       <c r="I48" s="14" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="J48" s="14" t="n">
         <v>4</v>
       </c>
       <c r="K48" s="14" t="n">
-        <v>0.62</v>
+        <v>0</v>
       </c>
       <c r="L48" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33232</t>
+          <t>PDMDEP-33272</t>
         </is>
       </c>
       <c r="M48" s="14" t="inlineStr">
         <is>
-          <t>00166708</t>
+          <t>00166910</t>
         </is>
       </c>
       <c r="N48" s="15" t="n">
-        <v>625</v>
+        <v>500</v>
       </c>
       <c r="O48" s="16" t="n">
-        <v>337.5</v>
+        <v>0</v>
       </c>
       <c r="P48" s="15" t="n">
-        <v>540</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33227</t>
+          <t>PDMDEP-33239</t>
         </is>
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>[METROPOLE EUROPEENNE DE LILLE] - MEL Crédits 21 heures (3j)     mai 2026</t>
+          <t>[MAIRIE DE LODEVE] - Migracier activité Placier vers Geodp V2</t>
         </is>
       </c>
       <c r="C49" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D49" s="11" t="inlineStr">
         <is>
-          <t>METROPOLE EUROPEENNE DE LILLE</t>
+          <t>MAIRIE DE LODEVE</t>
         </is>
       </c>
       <c r="E49" s="11" t="inlineStr">
         <is>
-          <t>21 crédits d'heure</t>
+          <t>Migracier activité Placier vers Geodp V2</t>
         </is>
       </c>
       <c r="F49" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G49" s="11" t="inlineStr">
@@ -4229,69 +4229,69 @@
       </c>
       <c r="H49" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I49" s="11" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="J49" s="11" t="n">
         <v>4</v>
       </c>
       <c r="K49" s="11" t="n">
-        <v>0.62</v>
+        <v>0</v>
       </c>
       <c r="L49" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33231</t>
+          <t>PDMDEP-33245</t>
         </is>
       </c>
       <c r="M49" s="11" t="inlineStr">
         <is>
-          <t>00166707</t>
+          <t>00166748</t>
         </is>
       </c>
       <c r="N49" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O49" s="12" t="n">
-        <v>16</v>
+        <v>149</v>
+      </c>
+      <c r="O49" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P49" s="12" t="n">
-        <v>25.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33170</t>
+          <t>PDMDEP-33227</t>
         </is>
       </c>
       <c r="B50" s="14" t="inlineStr">
         <is>
-          <t>[Commune de Bonneville] - MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
+          <t>[METROPOLE EUROPEENNE DE LILLE] - MEL Crédits 21 heures (3j)     mai 2026</t>
         </is>
       </c>
       <c r="C50" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D50" s="14" t="inlineStr">
         <is>
-          <t>Commune de Bonneville</t>
+          <t>METROPOLE EUROPEENNE DE LILLE</t>
         </is>
       </c>
       <c r="E50" s="14" t="inlineStr">
         <is>
-          <t>MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
+          <t>21 crédits d'heure</t>
         </is>
       </c>
       <c r="F50" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G50" s="14" t="inlineStr">
@@ -4301,69 +4301,69 @@
       </c>
       <c r="H50" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I50" s="14" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="J50" s="14" t="n">
         <v>4</v>
       </c>
       <c r="K50" s="14" t="n">
-        <v>0</v>
+        <v>0.62</v>
       </c>
       <c r="L50" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33177</t>
+          <t>PDMDEP-33232</t>
         </is>
       </c>
       <c r="M50" s="14" t="inlineStr">
         <is>
-          <t>00166356</t>
+          <t>00166708</t>
         </is>
       </c>
       <c r="N50" s="15" t="n">
-        <v>910</v>
+        <v>625</v>
       </c>
       <c r="O50" s="16" t="n">
-        <v>0</v>
+        <v>337.5</v>
       </c>
       <c r="P50" s="15" t="n">
-        <v>0</v>
+        <v>540</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33064</t>
+          <t>PDMDEP-33227</t>
         </is>
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>[MAIRIE DE LONGWY] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>[METROPOLE EUROPEENNE DE LILLE] - MEL Crédits 21 heures (3j)     mai 2026</t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE LONGWY</t>
+          <t>METROPOLE EUROPEENNE DE LILLE</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>21 crédits d'heure</t>
         </is>
       </c>
       <c r="F51" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G51" s="11" t="inlineStr">
@@ -4373,69 +4373,69 @@
       </c>
       <c r="H51" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I51" s="11" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="J51" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K51" s="11" t="n">
-        <v>2</v>
+        <v>0.62</v>
       </c>
       <c r="L51" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33073</t>
+          <t>PDMDEP-33231</t>
         </is>
       </c>
       <c r="M51" s="11" t="inlineStr">
         <is>
-          <t>00165708</t>
+          <t>00166707</t>
         </is>
       </c>
       <c r="N51" s="12" t="n">
-        <v>1207</v>
-      </c>
-      <c r="O51" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O51" s="12" t="n">
+        <v>16</v>
       </c>
       <c r="P51" s="12" t="n">
-        <v>0</v>
+        <v>25.6</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32984</t>
+          <t>PDMDEP-33170</t>
         </is>
       </c>
       <c r="B52" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTELIMAR] - Interface Civil net finance avec Littéralis</t>
+          <t>[Commune de Bonneville] - MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
         </is>
       </c>
       <c r="C52" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D52" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTELIMAR</t>
+          <t>Commune de Bonneville</t>
         </is>
       </c>
       <c r="E52" s="14" t="inlineStr">
         <is>
-          <t>Interface Civil net finance avec Littéralis</t>
+          <t>MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
         </is>
       </c>
       <c r="F52" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G52" s="14" t="inlineStr">
@@ -4445,32 +4445,32 @@
       </c>
       <c r="H52" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I52" s="14" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="J52" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K52" s="14" t="n">
         <v>0</v>
       </c>
       <c r="L52" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32990</t>
+          <t>PDMDEP-33177</t>
         </is>
       </c>
       <c r="M52" s="14" t="inlineStr">
         <is>
-          <t>00165270</t>
+          <t>00166356</t>
         </is>
       </c>
       <c r="N52" s="15" t="n">
-        <v>500</v>
+        <v>910</v>
       </c>
       <c r="O52" s="16" t="n">
         <v>0</v>
@@ -4482,32 +4482,32 @@
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32768</t>
+          <t>PDMDEP-33064</t>
         </is>
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t>[VILLE DE REIMS] - MV app/ infra + màj carto - ON prem</t>
+          <t>[MAIRIE DE LONGWY] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="C53" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D53" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE REIMS</t>
+          <t>MAIRIE DE LONGWY</t>
         </is>
       </c>
       <c r="E53" s="11" t="inlineStr">
         <is>
-          <t>MV app/ infra + màj carto</t>
+          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="F53" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G53" s="11" t="inlineStr">
@@ -4517,34 +4517,34 @@
       </c>
       <c r="H53" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I53" s="11" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="J53" s="11" t="n">
         <v>5</v>
       </c>
       <c r="K53" s="11" t="n">
-        <v>0.25</v>
+        <v>2</v>
       </c>
       <c r="L53" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32772</t>
+          <t>PDMDEP-33073</t>
         </is>
       </c>
       <c r="M53" s="11" t="inlineStr">
         <is>
-          <t>00163806</t>
+          <t>00165708</t>
         </is>
       </c>
       <c r="N53" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O53" s="12" t="n">
+        <v>1207</v>
+      </c>
+      <c r="O53" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P53" s="12" t="n">
@@ -4554,27 +4554,27 @@
     <row r="54">
       <c r="A54" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32552</t>
+          <t>PDMDEP-32984</t>
         </is>
       </c>
       <c r="B54" s="14" t="inlineStr">
         <is>
-          <t>[CHALON SUR SAONE] - Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
+          <t>[COMMUNE DE MONTELIMAR] - Interface Civil net finance avec Littéralis</t>
         </is>
       </c>
       <c r="C54" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D54" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE CHALON SUR SAONE</t>
+          <t>COMMUNE DE MONTELIMAR</t>
         </is>
       </c>
       <c r="E54" s="14" t="inlineStr">
         <is>
-          <t>Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
+          <t>Interface Civil net finance avec Littéralis</t>
         </is>
       </c>
       <c r="F54" s="14" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="I54" s="14" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="J54" s="14" t="n">
@@ -4605,16 +4605,16 @@
       </c>
       <c r="L54" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32556</t>
+          <t>PDMDEP-32990</t>
         </is>
       </c>
       <c r="M54" s="14" t="inlineStr">
         <is>
-          <t>00162313</t>
+          <t>00165270</t>
         </is>
       </c>
       <c r="N54" s="15" t="n">
-        <v>142.1</v>
+        <v>500</v>
       </c>
       <c r="O54" s="16" t="n">
         <v>0</v>
@@ -4626,32 +4626,32 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32461</t>
+          <t>PDMDEP-32768</t>
         </is>
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
+          <t>[VILLE DE REIMS] - MV app/ infra + màj carto - ON prem</t>
         </is>
       </c>
       <c r="C55" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D55" s="11" t="inlineStr">
         <is>
-          <t>NANTES METROPOLE - VDC</t>
+          <t>VILLE DE REIMS</t>
         </is>
       </c>
       <c r="E55" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2</t>
+          <t>MV app/ infra + màj carto</t>
         </is>
       </c>
       <c r="F55" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G55" s="11" t="inlineStr">
@@ -4661,34 +4661,34 @@
       </c>
       <c r="H55" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I55" s="11" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="J55" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K55" s="11" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L55" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32470</t>
+          <t>PDMDEP-32772</t>
         </is>
       </c>
       <c r="M55" s="11" t="inlineStr">
         <is>
-          <t>00161950</t>
+          <t>00163806</t>
         </is>
       </c>
       <c r="N55" s="12" t="n">
-        <v>2335</v>
-      </c>
-      <c r="O55" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O55" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P55" s="12" t="n">
@@ -4698,27 +4698,27 @@
     <row r="56">
       <c r="A56" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32442</t>
+          <t>PDMDEP-32552</t>
         </is>
       </c>
       <c r="B56" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE CHAMBERY] - Montée de version LiEx Test et prod  (03/26)</t>
+          <t>[CHALON SUR SAONE] - Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
         </is>
       </c>
       <c r="C56" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D56" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHAMBERY</t>
+          <t>VILLE DE CHALON SUR SAONE</t>
         </is>
       </c>
       <c r="E56" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Montée de version LiEx Test et prod </t>
+          <t>Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
         </is>
       </c>
       <c r="F56" s="14" t="inlineStr">
@@ -4738,29 +4738,29 @@
       </c>
       <c r="I56" s="14" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="J56" s="14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K56" s="14" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L56" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32446</t>
+          <t>PDMDEP-32556</t>
         </is>
       </c>
       <c r="M56" s="14" t="inlineStr">
         <is>
-          <t>00161842</t>
+          <t>00162313</t>
         </is>
       </c>
       <c r="N56" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O56" s="15" t="n">
+        <v>142.1</v>
+      </c>
+      <c r="O56" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P56" s="15" t="n">
@@ -4770,27 +4770,27 @@
     <row r="57">
       <c r="A57" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32366</t>
+          <t>PDMDEP-32461</t>
         </is>
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t>[Commune de Pleneuf Val André] - Migration de GEODP-Placier simple</t>
+          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="C57" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D57" s="11" t="inlineStr">
         <is>
-          <t>Commune de Pleneuf Val André</t>
+          <t>NANTES METROPOLE - VDC</t>
         </is>
       </c>
       <c r="E57" s="11" t="inlineStr">
         <is>
-          <t>Migration de GEODP-Placier simple</t>
+          <t>Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="F57" s="11" t="inlineStr">
@@ -4810,29 +4810,29 @@
       </c>
       <c r="I57" s="11" t="inlineStr">
         <is>
-          <t>26/03/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
       <c r="J57" s="11" t="n">
         <v>6</v>
       </c>
       <c r="K57" s="11" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L57" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32372</t>
+          <t>PDMDEP-32470</t>
         </is>
       </c>
       <c r="M57" s="11" t="inlineStr">
         <is>
-          <t>00161594</t>
+          <t>00161950</t>
         </is>
       </c>
       <c r="N57" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O57" s="12" t="n">
+        <v>2335</v>
+      </c>
+      <c r="O57" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P57" s="12" t="n">
@@ -4842,32 +4842,32 @@
     <row r="58">
       <c r="A58" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32331</t>
+          <t>PDMDEP-32442</t>
         </is>
       </c>
       <c r="B58" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
+          <t>[COMMUNE DE CHAMBERY] - Montée de version LiEx Test et prod  (03/26)</t>
         </is>
       </c>
       <c r="C58" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D58" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
+          <t>COMMUNE DE CHAMBERY</t>
         </is>
       </c>
       <c r="E58" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GEODP Placier </t>
+          <t xml:space="preserve">Montée de version LiEx Test et prod </t>
         </is>
       </c>
       <c r="F58" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G58" s="14" t="inlineStr">
@@ -4877,34 +4877,34 @@
       </c>
       <c r="H58" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I58" s="14" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
+          <t>27/03/2026</t>
         </is>
       </c>
       <c r="J58" s="14" t="n">
         <v>6</v>
       </c>
       <c r="K58" s="14" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L58" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32340</t>
+          <t>PDMDEP-32446</t>
         </is>
       </c>
       <c r="M58" s="14" t="inlineStr">
         <is>
-          <t>00161493</t>
+          <t>00161842</t>
         </is>
       </c>
       <c r="N58" s="15" t="n">
-        <v>450</v>
-      </c>
-      <c r="O58" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O58" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P58" s="15" t="n">
@@ -4914,32 +4914,32 @@
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32264</t>
+          <t>PDMDEP-32366</t>
         </is>
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
+          <t>[Commune de Pleneuf Val André] - Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="C59" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D59" s="11" t="inlineStr">
         <is>
-          <t>CA DU NIORTAIS</t>
+          <t>Commune de Pleneuf Val André</t>
         </is>
       </c>
       <c r="E59" s="11" t="inlineStr">
         <is>
-          <t>Modélisation</t>
+          <t>Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="F59" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G59" s="11" t="inlineStr">
@@ -4949,49 +4949,49 @@
       </c>
       <c r="H59" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I59" s="11" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>26/03/2026</t>
         </is>
       </c>
       <c r="J59" s="11" t="n">
         <v>6</v>
       </c>
       <c r="K59" s="11" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="L59" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32268</t>
+          <t>PDMDEP-32372</t>
         </is>
       </c>
       <c r="M59" s="11" t="inlineStr">
         <is>
-          <t>00161073</t>
+          <t>00161594</t>
         </is>
       </c>
       <c r="N59" s="12" t="n">
-        <v>910</v>
-      </c>
-      <c r="O59" s="16" t="n">
-        <v>136.5</v>
+        <v>0</v>
+      </c>
+      <c r="O59" s="12" t="n">
+        <v>0</v>
       </c>
       <c r="P59" s="12" t="n">
-        <v>68.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32086</t>
+          <t>PDMDEP-32331</t>
         </is>
       </c>
       <c r="B60" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE VITRY LE FRANCOIS] - Acquisition Geodp Placier</t>
+          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
         </is>
       </c>
       <c r="C60" s="14" t="inlineStr">
@@ -5001,12 +5001,12 @@
       </c>
       <c r="D60" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY LE FRANCOIS</t>
+          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
         </is>
       </c>
       <c r="E60" s="14" t="inlineStr">
         <is>
-          <t>Acquisition Geodp Placier</t>
+          <t xml:space="preserve">Migration GEODP Placier </t>
         </is>
       </c>
       <c r="F60" s="14" t="inlineStr">
@@ -5021,12 +5021,12 @@
       </c>
       <c r="H60" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I60" s="14" t="inlineStr">
         <is>
-          <t>17/03/2026</t>
+          <t>25/03/2026</t>
         </is>
       </c>
       <c r="J60" s="14" t="n">
@@ -5037,16 +5037,16 @@
       </c>
       <c r="L60" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32095</t>
+          <t>PDMDEP-32340</t>
         </is>
       </c>
       <c r="M60" s="14" t="inlineStr">
         <is>
-          <t>00160474</t>
+          <t>00161493</t>
         </is>
       </c>
       <c r="N60" s="15" t="n">
-        <v>590.15</v>
+        <v>450</v>
       </c>
       <c r="O60" s="16" t="n">
         <v>0</v>
@@ -5058,32 +5058,32 @@
     <row r="61">
       <c r="A61" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32065</t>
+          <t>PDMDEP-32264</t>
         </is>
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTBRISON] - Migration GeODP Placier + Ajout Civil Net Finance</t>
+          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
         </is>
       </c>
       <c r="C61" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D61" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTBRISON</t>
+          <t>CA DU NIORTAIS</t>
         </is>
       </c>
       <c r="E61" s="11" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier + Ajout Civil Net Finance</t>
+          <t>Modélisation</t>
         </is>
       </c>
       <c r="F61" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G61" s="11" t="inlineStr">
@@ -5093,49 +5093,49 @@
       </c>
       <c r="H61" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I61" s="11" t="inlineStr">
         <is>
-          <t>16/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
       <c r="J61" s="11" t="n">
         <v>6</v>
       </c>
       <c r="K61" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L61" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32074</t>
+          <t>PDMDEP-32268</t>
         </is>
       </c>
       <c r="M61" s="11" t="inlineStr">
         <is>
-          <t>00160409</t>
+          <t>00161073</t>
         </is>
       </c>
       <c r="N61" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O61" s="12" t="n">
-        <v>823.65</v>
+        <v>910</v>
+      </c>
+      <c r="O61" s="16" t="n">
+        <v>136.5</v>
       </c>
       <c r="P61" s="12" t="n">
-        <v>0</v>
+        <v>68.25</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31996</t>
+          <t>PDMDEP-32086</t>
         </is>
       </c>
       <c r="B62" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
+          <t>[COMMUNE DE VITRY LE FRANCOIS] - Acquisition Geodp Placier</t>
         </is>
       </c>
       <c r="C62" s="14" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="D62" s="14" t="inlineStr">
         <is>
-          <t>Commune de Cluny</t>
+          <t>COMMUNE DE VITRY LE FRANCOIS</t>
         </is>
       </c>
       <c r="E62" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
+          <t>Acquisition Geodp Placier</t>
         </is>
       </c>
       <c r="F62" s="14" t="inlineStr">
@@ -5165,12 +5165,12 @@
       </c>
       <c r="H62" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I62" s="14" t="inlineStr">
         <is>
-          <t>12/03/2026</t>
+          <t>17/03/2026</t>
         </is>
       </c>
       <c r="J62" s="14" t="n">
@@ -5181,16 +5181,16 @@
       </c>
       <c r="L62" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32002</t>
+          <t>PDMDEP-32095</t>
         </is>
       </c>
       <c r="M62" s="14" t="inlineStr">
         <is>
-          <t>00160078</t>
+          <t>00160474</t>
         </is>
       </c>
       <c r="N62" s="15" t="n">
-        <v>285</v>
+        <v>590.15</v>
       </c>
       <c r="O62" s="16" t="n">
         <v>0</v>
@@ -5202,32 +5202,32 @@
     <row r="63">
       <c r="A63" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31967</t>
+          <t>PDMDEP-32065</t>
         </is>
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU LOT -CD46] - Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
+          <t>[COMMUNE DE MONTBRISON] - Migration GeODP Placier + Ajout Civil Net Finance</t>
         </is>
       </c>
       <c r="C63" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D63" s="11" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU LOT -CD46</t>
+          <t>COMMUNE DE MONTBRISON</t>
         </is>
       </c>
       <c r="E63" s="11" t="inlineStr">
         <is>
-          <t>Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
+          <t>Migration GeODP Placier + Ajout Civil Net Finance</t>
         </is>
       </c>
       <c r="F63" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G63" s="11" t="inlineStr">
@@ -5237,35 +5237,35 @@
       </c>
       <c r="H63" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I63" s="11" t="inlineStr">
         <is>
-          <t>11/03/2026</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="J63" s="11" t="n">
         <v>6</v>
       </c>
       <c r="K63" s="11" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="L63" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31971</t>
+          <t>PDMDEP-32074</t>
         </is>
       </c>
       <c r="M63" s="11" t="inlineStr">
         <is>
-          <t>00159863</t>
+          <t>00160409</t>
         </is>
       </c>
       <c r="N63" s="12" t="n">
-        <v>1325</v>
-      </c>
-      <c r="O63" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O63" s="12" t="n">
+        <v>823.65</v>
       </c>
       <c r="P63" s="12" t="n">
         <v>0</v>
@@ -5274,32 +5274,32 @@
     <row r="64">
       <c r="A64" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31947</t>
+          <t>PDMDEP-31996</t>
         </is>
       </c>
       <c r="B64" s="14" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
+          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="C64" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D64" s="14" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
+          <t>Commune de Cluny</t>
         </is>
       </c>
       <c r="E64" s="14" t="inlineStr">
         <is>
-          <t>SSO/LDAP</t>
+          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="F64" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G64" s="14" t="inlineStr">
@@ -5314,7 +5314,7 @@
       </c>
       <c r="I64" s="14" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>12/03/2026</t>
         </is>
       </c>
       <c r="J64" s="14" t="n">
@@ -5325,16 +5325,16 @@
       </c>
       <c r="L64" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31951</t>
+          <t>PDMDEP-32002</t>
         </is>
       </c>
       <c r="M64" s="14" t="inlineStr">
         <is>
-          <t>00159724</t>
+          <t>00160078</t>
         </is>
       </c>
       <c r="N64" s="15" t="n">
-        <v>120</v>
+        <v>285</v>
       </c>
       <c r="O64" s="16" t="n">
         <v>0</v>
@@ -5346,32 +5346,32 @@
     <row r="65">
       <c r="A65" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31908</t>
+          <t>PDMDEP-31967</t>
         </is>
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t>[Commune de GUINGAMP] - Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
+          <t>[DEPARTEMENT DU LOT -CD46] - Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
         </is>
       </c>
       <c r="C65" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D65" s="11" t="inlineStr">
         <is>
-          <t>Commune de GUINGAMP</t>
+          <t>DEPARTEMENT DU LOT -CD46</t>
         </is>
       </c>
       <c r="E65" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
+          <t>Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
         </is>
       </c>
       <c r="F65" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G65" s="11" t="inlineStr">
@@ -5381,32 +5381,32 @@
       </c>
       <c r="H65" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I65" s="11" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>11/03/2026</t>
         </is>
       </c>
       <c r="J65" s="11" t="n">
         <v>6</v>
       </c>
       <c r="K65" s="11" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="L65" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31917</t>
+          <t>PDMDEP-31971</t>
         </is>
       </c>
       <c r="M65" s="11" t="inlineStr">
         <is>
-          <t>00159608</t>
+          <t>00159863</t>
         </is>
       </c>
       <c r="N65" s="12" t="n">
-        <v>588</v>
+        <v>1325</v>
       </c>
       <c r="O65" s="16" t="n">
         <v>0</v>
@@ -5418,32 +5418,32 @@
     <row r="66">
       <c r="A66" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31812</t>
+          <t>PDMDEP-31947</t>
         </is>
       </c>
       <c r="B66" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE PROVINS] - Migration V2 classique</t>
+          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
         </is>
       </c>
       <c r="C66" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D66" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE PROVINS</t>
+          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
         </is>
       </c>
       <c r="E66" s="14" t="inlineStr">
         <is>
-          <t>Migration V2 classique</t>
+          <t>SSO/LDAP</t>
         </is>
       </c>
       <c r="F66" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G66" s="14" t="inlineStr">
@@ -5453,34 +5453,34 @@
       </c>
       <c r="H66" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I66" s="14" t="inlineStr">
         <is>
-          <t>06/03/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
       <c r="J66" s="14" t="n">
         <v>6</v>
       </c>
       <c r="K66" s="14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L66" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31821</t>
+          <t>PDMDEP-31951</t>
         </is>
       </c>
       <c r="M66" s="14" t="inlineStr">
         <is>
-          <t>00159471</t>
+          <t>00159724</t>
         </is>
       </c>
       <c r="N66" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O66" s="15" t="n">
+        <v>120</v>
+      </c>
+      <c r="O66" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P66" s="15" t="n">
@@ -5490,27 +5490,27 @@
     <row r="67">
       <c r="A67" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31649</t>
+          <t>PDMDEP-31908</t>
         </is>
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
+          <t>[Commune de GUINGAMP] - Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
         </is>
       </c>
       <c r="C67" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D67" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE GUILLESTRE</t>
+          <t>Commune de GUINGAMP</t>
         </is>
       </c>
       <c r="E67" s="11" t="inlineStr">
         <is>
-          <t>GeoDP Placier</t>
+          <t>Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
         </is>
       </c>
       <c r="F67" s="11" t="inlineStr">
@@ -5525,32 +5525,32 @@
       </c>
       <c r="H67" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I67" s="11" t="inlineStr">
         <is>
-          <t>27/02/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
       <c r="J67" s="11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K67" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L67" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31658</t>
+          <t>PDMDEP-31917</t>
         </is>
       </c>
       <c r="M67" s="11" t="inlineStr">
         <is>
-          <t>00158175</t>
+          <t>00159608</t>
         </is>
       </c>
       <c r="N67" s="12" t="n">
-        <v>203.5</v>
+        <v>588</v>
       </c>
       <c r="O67" s="16" t="n">
         <v>0</v>
@@ -5562,27 +5562,27 @@
     <row r="68">
       <c r="A68" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31589</t>
+          <t>PDMDEP-31812</t>
         </is>
       </c>
       <c r="B68" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE LEVALLOIS PERRET] - Migration GEODP - 3 MODULES + mise en service export finance </t>
+          <t>[COMMUNE PROVINS] - Migration V2 classique</t>
         </is>
       </c>
       <c r="C68" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D68" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE LEVALLOIS PERRET</t>
+          <t>COMMUNE PROVINS</t>
         </is>
       </c>
       <c r="E68" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GEODP - 3 MODULES + mise en service export finance </t>
+          <t>Migration V2 classique</t>
         </is>
       </c>
       <c r="F68" s="14" t="inlineStr">
@@ -5602,29 +5602,29 @@
       </c>
       <c r="I68" s="14" t="inlineStr">
         <is>
-          <t>26/02/2026</t>
+          <t>06/03/2026</t>
         </is>
       </c>
       <c r="J68" s="14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K68" s="14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L68" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31596</t>
+          <t>PDMDEP-31821</t>
         </is>
       </c>
       <c r="M68" s="14" t="inlineStr">
         <is>
-          <t>00157967</t>
+          <t>00159471</t>
         </is>
       </c>
       <c r="N68" s="15" t="n">
-        <v>300</v>
-      </c>
-      <c r="O68" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O68" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P68" s="15" t="n">
@@ -5634,32 +5634,32 @@
     <row r="69">
       <c r="A69" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31540</t>
+          <t>PDMDEP-31649</t>
         </is>
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTELIMAR] - Modélisation LiEx et redevances</t>
+          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
         </is>
       </c>
       <c r="C69" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D69" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTELIMAR</t>
+          <t>MAIRIE DE GUILLESTRE</t>
         </is>
       </c>
       <c r="E69" s="11" t="inlineStr">
         <is>
-          <t>Modélisation LiEx</t>
+          <t>GeoDP Placier</t>
         </is>
       </c>
       <c r="F69" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G69" s="11" t="inlineStr">
@@ -5669,12 +5669,12 @@
       </c>
       <c r="H69" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I69" s="11" t="inlineStr">
         <is>
-          <t>24/02/2026</t>
+          <t>27/02/2026</t>
         </is>
       </c>
       <c r="J69" s="11" t="n">
@@ -5685,16 +5685,16 @@
       </c>
       <c r="L69" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31546</t>
+          <t>PDMDEP-31658</t>
         </is>
       </c>
       <c r="M69" s="11" t="inlineStr">
         <is>
-          <t>00157816</t>
+          <t>00158175</t>
         </is>
       </c>
       <c r="N69" s="12" t="n">
-        <v>700</v>
+        <v>203.5</v>
       </c>
       <c r="O69" s="16" t="n">
         <v>0</v>
@@ -5706,27 +5706,27 @@
     <row r="70">
       <c r="A70" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31351</t>
+          <t>PDMDEP-31589</t>
         </is>
       </c>
       <c r="B70" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
+          <t xml:space="preserve">[COMMUNE DE LEVALLOIS PERRET] - Migration GEODP - 3 MODULES + mise en service export finance </t>
         </is>
       </c>
       <c r="C70" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D70" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
+          <t>COMMUNE DE LEVALLOIS PERRET</t>
         </is>
       </c>
       <c r="E70" s="14" t="inlineStr">
         <is>
-          <t>Migration vers GeoDP V2</t>
+          <t xml:space="preserve">Migration GEODP - 3 MODULES + mise en service export finance </t>
         </is>
       </c>
       <c r="F70" s="14" t="inlineStr">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="I70" s="14" t="inlineStr">
         <is>
-          <t>17/02/2026</t>
+          <t>26/02/2026</t>
         </is>
       </c>
       <c r="J70" s="14" t="n">
@@ -5757,16 +5757,16 @@
       </c>
       <c r="L70" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31360</t>
+          <t>PDMDEP-31596</t>
         </is>
       </c>
       <c r="M70" s="14" t="inlineStr">
         <is>
-          <t>00157041</t>
+          <t>00157967</t>
         </is>
       </c>
       <c r="N70" s="15" t="n">
-        <v>210</v>
+        <v>300</v>
       </c>
       <c r="O70" s="16" t="n">
         <v>0</v>
@@ -5778,32 +5778,32 @@
     <row r="71">
       <c r="A71" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31319</t>
+          <t>PDMDEP-31540</t>
         </is>
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LARMOR PLAGE] - Migration de GEODP-Placier simple</t>
+          <t>[COMMUNE DE MONTELIMAR] - Modélisation LiEx et redevances</t>
         </is>
       </c>
       <c r="C71" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D71" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE LARMOR PLAGE</t>
+          <t>COMMUNE DE MONTELIMAR</t>
         </is>
       </c>
       <c r="E71" s="11" t="inlineStr">
         <is>
-          <t>Migration de GEODP-Placier simple</t>
+          <t>Modélisation LiEx</t>
         </is>
       </c>
       <c r="F71" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G71" s="11" t="inlineStr">
@@ -5813,12 +5813,12 @@
       </c>
       <c r="H71" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I71" s="11" t="inlineStr">
         <is>
-          <t>17/02/2026</t>
+          <t>24/02/2026</t>
         </is>
       </c>
       <c r="J71" s="11" t="n">
@@ -5829,19 +5829,19 @@
       </c>
       <c r="L71" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31328</t>
+          <t>PDMDEP-31546</t>
         </is>
       </c>
       <c r="M71" s="11" t="inlineStr">
         <is>
-          <t>00156518</t>
+          <t>00157816</t>
         </is>
       </c>
       <c r="N71" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O71" s="12" t="n">
-        <v>281</v>
+        <v>700</v>
+      </c>
+      <c r="O71" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P71" s="12" t="n">
         <v>0</v>
@@ -5850,32 +5850,32 @@
     <row r="72">
       <c r="A72" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31188</t>
+          <t>PDMDEP-31464</t>
         </is>
       </c>
       <c r="B72" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
+          <t>[CD 17] - Modélisation PV - 2 jours</t>
         </is>
       </c>
       <c r="C72" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D72" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE D HENDAYE</t>
+          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
         </is>
       </c>
       <c r="E72" s="14" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t xml:space="preserve">2 jours de modélisation - nouveau modèle </t>
         </is>
       </c>
       <c r="F72" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G72" s="14" t="inlineStr">
@@ -5885,34 +5885,34 @@
       </c>
       <c r="H72" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I72" s="14" t="inlineStr">
         <is>
-          <t>12/02/2026</t>
+          <t>19/02/2026</t>
         </is>
       </c>
       <c r="J72" s="14" t="n">
         <v>7</v>
       </c>
       <c r="K72" s="14" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L72" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31197</t>
+          <t>PDMDEP-31468</t>
         </is>
       </c>
       <c r="M72" s="14" t="inlineStr">
         <is>
-          <t>00156556</t>
+          <t>00157346</t>
         </is>
       </c>
       <c r="N72" s="15" t="n">
-        <v>130</v>
-      </c>
-      <c r="O72" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O72" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P72" s="15" t="n">
@@ -5922,12 +5922,12 @@
     <row r="73">
       <c r="A73" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31036</t>
+          <t>PDMDEP-31351</t>
         </is>
       </c>
       <c r="B73" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
+          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="C73" s="11" t="inlineStr">
@@ -5937,12 +5937,12 @@
       </c>
       <c r="D73" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE SARLAT LA CANEDA</t>
+          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
         </is>
       </c>
       <c r="E73" s="11" t="inlineStr">
         <is>
-          <t>Migration V2 classique + abo CB</t>
+          <t>Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="F73" s="11" t="inlineStr">
@@ -5962,7 +5962,7 @@
       </c>
       <c r="I73" s="11" t="inlineStr">
         <is>
-          <t>10/02/2026</t>
+          <t>17/02/2026</t>
         </is>
       </c>
       <c r="J73" s="11" t="n">
@@ -5973,16 +5973,16 @@
       </c>
       <c r="L73" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31045</t>
+          <t>PDMDEP-31360</t>
         </is>
       </c>
       <c r="M73" s="11" t="inlineStr">
         <is>
-          <t>00156095</t>
+          <t>00157041</t>
         </is>
       </c>
       <c r="N73" s="12" t="n">
-        <v>255</v>
+        <v>210</v>
       </c>
       <c r="O73" s="16" t="n">
         <v>0</v>
@@ -5994,12 +5994,12 @@
     <row r="74">
       <c r="A74" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-30330</t>
+          <t>PDMDEP-31319</t>
         </is>
       </c>
       <c r="B74" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
+          <t>[COMMUNE DE LARMOR PLAGE] - Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="C74" s="14" t="inlineStr">
@@ -6009,12 +6009,12 @@
       </c>
       <c r="D74" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE ALENCON</t>
+          <t>COMMUNE DE LARMOR PLAGE</t>
         </is>
       </c>
       <c r="E74" s="14" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="F74" s="14" t="inlineStr">
@@ -6034,30 +6034,30 @@
       </c>
       <c r="I74" s="14" t="inlineStr">
         <is>
-          <t>28/01/2026</t>
+          <t>17/02/2026</t>
         </is>
       </c>
       <c r="J74" s="14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K74" s="14" t="n">
         <v>0</v>
       </c>
       <c r="L74" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30335</t>
+          <t>PDMDEP-31328</t>
         </is>
       </c>
       <c r="M74" s="14" t="inlineStr">
         <is>
-          <t>00154411</t>
+          <t>00156518</t>
         </is>
       </c>
       <c r="N74" s="15" t="n">
-        <v>140</v>
-      </c>
-      <c r="O74" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O74" s="15" t="n">
+        <v>281</v>
       </c>
       <c r="P74" s="15" t="n">
         <v>0</v>
@@ -6066,32 +6066,32 @@
     <row r="75">
       <c r="A75" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-30196</t>
+          <t>PDMDEP-31188</t>
         </is>
       </c>
       <c r="B75" s="11" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
+          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C75" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D75" s="11" t="inlineStr">
         <is>
-          <t>CD56</t>
+          <t>COMMUNE D HENDAYE</t>
         </is>
       </c>
       <c r="E75" s="11" t="inlineStr">
         <is>
-          <t>Paramétrage interface Pastell</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F75" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G75" s="11" t="inlineStr">
@@ -6101,32 +6101,32 @@
       </c>
       <c r="H75" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I75" s="11" t="inlineStr">
         <is>
-          <t>21/01/2026</t>
+          <t>12/02/2026</t>
         </is>
       </c>
       <c r="J75" s="11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K75" s="11" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="L75" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30197</t>
+          <t>PDMDEP-31197</t>
         </is>
       </c>
       <c r="M75" s="11" t="inlineStr">
         <is>
-          <t>00153939</t>
+          <t>00156556</t>
         </is>
       </c>
       <c r="N75" s="12" t="n">
-        <v>690</v>
+        <v>130</v>
       </c>
       <c r="O75" s="16" t="n">
         <v>0</v>
@@ -6138,32 +6138,32 @@
     <row r="76">
       <c r="A76" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-29606</t>
+          <t>PDMDEP-31036</t>
         </is>
       </c>
       <c r="B76" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
+          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="C76" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D76" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE BIARRITZ</t>
+          <t>COMMUNE DE SARLAT LA CANEDA</t>
         </is>
       </c>
       <c r="E76" s="14" t="inlineStr">
         <is>
-          <t>Paramétrages complémentaires + Vision</t>
+          <t>Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="F76" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G76" s="14" t="inlineStr">
@@ -6173,34 +6173,34 @@
       </c>
       <c r="H76" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I76" s="14" t="inlineStr">
         <is>
-          <t>09/01/2026</t>
+          <t>10/02/2026</t>
         </is>
       </c>
       <c r="J76" s="14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K76" s="14" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="L76" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30431</t>
+          <t>PDMDEP-31045</t>
         </is>
       </c>
       <c r="M76" s="14" t="inlineStr">
         <is>
-          <t>00154684</t>
+          <t>00156095</t>
         </is>
       </c>
       <c r="N76" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O76" s="15" t="n">
+        <v>255</v>
+      </c>
+      <c r="O76" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P76" s="15" t="n">
@@ -6210,32 +6210,32 @@
     <row r="77">
       <c r="A77" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-29606</t>
+          <t>PDMDEP-30330</t>
         </is>
       </c>
       <c r="B77" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
+          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C77" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D77" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE BIARRITZ</t>
+          <t>COMMUNE DE ALENCON</t>
         </is>
       </c>
       <c r="E77" s="11" t="inlineStr">
         <is>
-          <t>Paramétrages complémentaires + Vision</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F77" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G77" s="11" t="inlineStr">
@@ -6245,32 +6245,32 @@
       </c>
       <c r="H77" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I77" s="11" t="inlineStr">
         <is>
-          <t>09/01/2026</t>
+          <t>28/01/2026</t>
         </is>
       </c>
       <c r="J77" s="11" t="n">
         <v>8</v>
       </c>
       <c r="K77" s="11" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="L77" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-29625</t>
+          <t>PDMDEP-30335</t>
         </is>
       </c>
       <c r="M77" s="11" t="inlineStr">
         <is>
-          <t>00145091</t>
+          <t>00154411</t>
         </is>
       </c>
       <c r="N77" s="12" t="n">
-        <v>187.5</v>
+        <v>140</v>
       </c>
       <c r="O77" s="16" t="n">
         <v>0</v>
@@ -6282,27 +6282,27 @@
     <row r="78">
       <c r="A78" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-29606</t>
+          <t>PDMDEP-30196</t>
         </is>
       </c>
       <c r="B78" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
+          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="C78" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D78" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE BIARRITZ</t>
+          <t>CD56</t>
         </is>
       </c>
       <c r="E78" s="14" t="inlineStr">
         <is>
-          <t>Paramétrages complémentaires + Vision</t>
+          <t>Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="F78" s="14" t="inlineStr">
@@ -6322,27 +6322,27 @@
       </c>
       <c r="I78" s="14" t="inlineStr">
         <is>
-          <t>09/01/2026</t>
+          <t>21/01/2026</t>
         </is>
       </c>
       <c r="J78" s="14" t="n">
         <v>8</v>
       </c>
       <c r="K78" s="14" t="n">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
       <c r="L78" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-29608</t>
+          <t>PDMDEP-30197</t>
         </is>
       </c>
       <c r="M78" s="14" t="inlineStr">
         <is>
-          <t>00152338</t>
+          <t>00153939</t>
         </is>
       </c>
       <c r="N78" s="15" t="n">
-        <v>787.5</v>
+        <v>690</v>
       </c>
       <c r="O78" s="16" t="n">
         <v>0</v>
@@ -6354,32 +6354,32 @@
     <row r="79">
       <c r="A79" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-28306</t>
+          <t>PDMDEP-29606</t>
         </is>
       </c>
       <c r="B79" s="11" t="inlineStr">
         <is>
-          <t>Commune de CLAMART - GEODP2 migration</t>
+          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="C79" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D79" s="11" t="inlineStr">
         <is>
-          <t>Commune de CLAMART</t>
+          <t>COMMUNE DE BIARRITZ</t>
         </is>
       </c>
       <c r="E79" s="11" t="inlineStr">
         <is>
-          <t>Migration V2</t>
+          <t>Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="F79" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G79" s="11" t="inlineStr">
@@ -6389,35 +6389,35 @@
       </c>
       <c r="H79" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I79" s="11" t="inlineStr">
         <is>
-          <t>28/11/2025</t>
+          <t>09/01/2026</t>
         </is>
       </c>
       <c r="J79" s="11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K79" s="11" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="L79" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28310</t>
+          <t>PDMDEP-30431</t>
         </is>
       </c>
       <c r="M79" s="11" t="inlineStr">
         <is>
-          <t>00145374</t>
+          <t>00154684</t>
         </is>
       </c>
       <c r="N79" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O79" s="12" t="n">
-        <v>362.5</v>
+        <v>0</v>
       </c>
       <c r="P79" s="12" t="n">
         <v>0</v>
@@ -6426,26 +6426,28 @@
     <row r="80">
       <c r="A80" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-28174</t>
+          <t>PDMDEP-29606</t>
         </is>
       </c>
       <c r="B80" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOBIGNY - LITTERALIS</t>
+          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="C80" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D80" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOBIGNY</t>
-        </is>
-      </c>
-      <c r="E80" s="14" t="n">
-        <v/>
+          <t>COMMUNE DE BIARRITZ</t>
+        </is>
+      </c>
+      <c r="E80" s="14" t="inlineStr">
+        <is>
+          <t>Paramétrages complémentaires + Vision</t>
+        </is>
       </c>
       <c r="F80" s="14" t="inlineStr">
         <is>
@@ -6459,34 +6461,34 @@
       </c>
       <c r="H80" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I80" s="14" t="inlineStr">
         <is>
-          <t>25/11/2025</t>
+          <t>09/01/2026</t>
         </is>
       </c>
       <c r="J80" s="14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K80" s="14" t="n">
-        <v>2.75</v>
+        <v>0.75</v>
       </c>
       <c r="L80" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28175</t>
+          <t>PDMDEP-29625</t>
         </is>
       </c>
       <c r="M80" s="14" t="inlineStr">
         <is>
-          <t>00145001</t>
+          <t>00145091</t>
         </is>
       </c>
       <c r="N80" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O80" s="15" t="n">
+        <v>187.5</v>
+      </c>
+      <c r="O80" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P80" s="15" t="n">
@@ -6496,27 +6498,27 @@
     <row r="81">
       <c r="A81" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-29606</t>
         </is>
       </c>
       <c r="B81" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="C81" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D81" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+          <t>COMMUNE DE BIARRITZ</t>
         </is>
       </c>
       <c r="E81" s="11" t="inlineStr">
         <is>
-          <t>Déploiement Littéralis Expert</t>
+          <t>Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="F81" s="11" t="inlineStr">
@@ -6531,34 +6533,34 @@
       </c>
       <c r="H81" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I81" s="11" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>09/01/2026</t>
         </is>
       </c>
       <c r="J81" s="11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K81" s="11" t="n">
-        <v>0.95</v>
+        <v>0.75</v>
       </c>
       <c r="L81" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28206</t>
+          <t>PDMDEP-29608</t>
         </is>
       </c>
       <c r="M81" s="11" t="inlineStr">
         <is>
-          <t>00144864</t>
+          <t>00152338</t>
         </is>
       </c>
       <c r="N81" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O81" s="12" t="n">
+        <v>787.5</v>
+      </c>
+      <c r="O81" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P81" s="12" t="n">
@@ -6568,32 +6570,32 @@
     <row r="82">
       <c r="A82" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-28306</t>
         </is>
       </c>
       <c r="B82" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t>Commune de CLAMART - GEODP2 migration</t>
         </is>
       </c>
       <c r="C82" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D82" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+          <t>Commune de CLAMART</t>
         </is>
       </c>
       <c r="E82" s="14" t="inlineStr">
         <is>
-          <t>Déploiement Littéralis Expert</t>
+          <t>Migration V2</t>
         </is>
       </c>
       <c r="F82" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G82" s="14" t="inlineStr">
@@ -6603,35 +6605,35 @@
       </c>
       <c r="H82" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I82" s="14" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>28/11/2025</t>
         </is>
       </c>
       <c r="J82" s="14" t="n">
         <v>10</v>
       </c>
       <c r="K82" s="14" t="n">
-        <v>0.95</v>
+        <v>0</v>
       </c>
       <c r="L82" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28205</t>
+          <t>PDMDEP-28310</t>
         </is>
       </c>
       <c r="M82" s="14" t="inlineStr">
         <is>
-          <t>00144863</t>
+          <t>00145374</t>
         </is>
       </c>
       <c r="N82" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O82" s="15" t="n">
-        <v>0</v>
+        <v>362.5</v>
       </c>
       <c r="P82" s="15" t="n">
         <v>0</v>
@@ -6640,12 +6642,12 @@
     <row r="83">
       <c r="A83" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-28174</t>
         </is>
       </c>
       <c r="B83" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t>COMMUNE DE BOBIGNY - LITTERALIS</t>
         </is>
       </c>
       <c r="C83" s="11" t="inlineStr">
@@ -6655,13 +6657,11 @@
       </c>
       <c r="D83" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
-        </is>
-      </c>
-      <c r="E83" s="11" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
+          <t>COMMUNE DE BOBIGNY</t>
+        </is>
+      </c>
+      <c r="E83" s="11" t="n">
+        <v/>
       </c>
       <c r="F83" s="11" t="inlineStr">
         <is>
@@ -6680,23 +6680,23 @@
       </c>
       <c r="I83" s="11" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>25/11/2025</t>
         </is>
       </c>
       <c r="J83" s="11" t="n">
         <v>10</v>
       </c>
       <c r="K83" s="11" t="n">
-        <v>0.95</v>
+        <v>2.75</v>
       </c>
       <c r="L83" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28204</t>
+          <t>PDMDEP-28175</t>
         </is>
       </c>
       <c r="M83" s="11" t="inlineStr">
         <is>
-          <t>00144862</t>
+          <t>00145001</t>
         </is>
       </c>
       <c r="N83" s="12" t="n">
@@ -6763,12 +6763,12 @@
       </c>
       <c r="L84" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28203</t>
+          <t>PDMDEP-28206</t>
         </is>
       </c>
       <c r="M84" s="14" t="inlineStr">
         <is>
-          <t>00144860</t>
+          <t>00144864</t>
         </is>
       </c>
       <c r="N84" s="15" t="n">
@@ -6835,18 +6835,18 @@
       </c>
       <c r="L85" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28202</t>
+          <t>PDMDEP-28205</t>
         </is>
       </c>
       <c r="M85" s="11" t="inlineStr">
         <is>
-          <t>00144857</t>
+          <t>00144863</t>
         </is>
       </c>
       <c r="N85" s="12" t="n">
-        <v>1320</v>
-      </c>
-      <c r="O85" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O85" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P85" s="12" t="n">
@@ -6856,12 +6856,12 @@
     <row r="86">
       <c r="A86" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-27634</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B86" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes - LITTERALIS</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C86" s="14" t="inlineStr">
@@ -6871,11 +6871,13 @@
       </c>
       <c r="D86" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes</t>
-        </is>
-      </c>
-      <c r="E86" s="14" t="n">
-        <v/>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+        </is>
+      </c>
+      <c r="E86" s="14" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F86" s="14" t="inlineStr">
         <is>
@@ -6889,28 +6891,28 @@
       </c>
       <c r="H86" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I86" s="14" t="inlineStr">
         <is>
-          <t>21/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J86" s="14" t="n">
         <v>10</v>
       </c>
       <c r="K86" s="14" t="n">
-        <v>0.5</v>
+        <v>0.95</v>
       </c>
       <c r="L86" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27642</t>
+          <t>PDMDEP-28204</t>
         </is>
       </c>
       <c r="M86" s="14" t="inlineStr">
         <is>
-          <t>00143935</t>
+          <t>00144862</t>
         </is>
       </c>
       <c r="N86" s="15" t="n">
@@ -6926,12 +6928,12 @@
     <row r="87">
       <c r="A87" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-26831</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B87" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [CD74] - Maj Ref carto dans le cadre de la maintenance</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C87" s="11" t="inlineStr">
@@ -6941,34 +6943,50 @@
       </c>
       <c r="D87" s="11" t="inlineStr">
         <is>
-          <t>CD74</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
         </is>
       </c>
       <c r="E87" s="11" t="inlineStr">
         <is>
-          <t>MAJ carto</t>
-        </is>
-      </c>
-      <c r="F87" s="11" t="inlineStr"/>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
+      </c>
+      <c r="F87" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
       <c r="G87" s="11" t="inlineStr">
         <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="H87" s="11" t="inlineStr"/>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H87" s="11" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I87" s="11" t="inlineStr">
         <is>
-          <t>05/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J87" s="11" t="n">
         <v>10</v>
       </c>
       <c r="K87" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L87" s="11" t="inlineStr"/>
-      <c r="M87" s="11" t="inlineStr"/>
+        <v>0.95</v>
+      </c>
+      <c r="L87" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-28203</t>
+        </is>
+      </c>
+      <c r="M87" s="11" t="inlineStr">
+        <is>
+          <t>00144860</t>
+        </is>
+      </c>
       <c r="N87" s="12" t="n">
         <v>0</v>
       </c>
@@ -6982,12 +7000,12 @@
     <row r="88">
       <c r="A88" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-26813</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B88" s="14" t="inlineStr">
         <is>
-          <t>[VILLEJUIF] - Litteralis Modèle facture + param Civil Net</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C88" s="14" t="inlineStr">
@@ -6997,11 +7015,13 @@
       </c>
       <c r="D88" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE VILLEJUIF</t>
-        </is>
-      </c>
-      <c r="E88" s="14" t="n">
-        <v/>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+        </is>
+      </c>
+      <c r="E88" s="14" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F88" s="14" t="inlineStr">
         <is>
@@ -7015,34 +7035,34 @@
       </c>
       <c r="H88" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I88" s="14" t="inlineStr">
         <is>
-          <t>04/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J88" s="14" t="n">
         <v>10</v>
       </c>
       <c r="K88" s="14" t="n">
-        <v>0.25</v>
+        <v>0.95</v>
       </c>
       <c r="L88" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-26814</t>
+          <t>PDMDEP-28202</t>
         </is>
       </c>
       <c r="M88" s="14" t="inlineStr">
         <is>
-          <t>00142941</t>
+          <t>00144857</t>
         </is>
       </c>
       <c r="N88" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O88" s="15" t="n">
+        <v>1320</v>
+      </c>
+      <c r="O88" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P88" s="15" t="n">
@@ -7052,12 +7072,12 @@
     <row r="89">
       <c r="A89" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-24866</t>
+          <t>PDMDEP-27634</t>
         </is>
       </c>
       <c r="B89" s="11" t="inlineStr">
         <is>
-          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
+          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes - LITTERALIS</t>
         </is>
       </c>
       <c r="C89" s="11" t="inlineStr">
@@ -7067,7 +7087,7 @@
       </c>
       <c r="D89" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
+          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes</t>
         </is>
       </c>
       <c r="E89" s="11" t="n">
@@ -7085,34 +7105,34 @@
       </c>
       <c r="H89" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I89" s="11" t="inlineStr">
         <is>
-          <t>16/10/2025</t>
+          <t>21/11/2025</t>
         </is>
       </c>
       <c r="J89" s="11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K89" s="11" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L89" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27017</t>
+          <t>PDMDEP-27642</t>
         </is>
       </c>
       <c r="M89" s="11" t="inlineStr">
         <is>
-          <t>00141205</t>
+          <t>00143935</t>
         </is>
       </c>
       <c r="N89" s="12" t="n">
-        <v>1212</v>
-      </c>
-      <c r="O89" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O89" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P89" s="12" t="n">
@@ -7122,12 +7142,12 @@
     <row r="90">
       <c r="A90" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-23918</t>
+          <t>PDMDEP-26831</t>
         </is>
       </c>
       <c r="B90" s="14" t="inlineStr">
         <is>
-          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
+          <t xml:space="preserve"> [CD74] - Maj Ref carto dans le cadre de la maintenance</t>
         </is>
       </c>
       <c r="C90" s="14" t="inlineStr">
@@ -7137,67 +7157,53 @@
       </c>
       <c r="D90" s="14" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
-        </is>
-      </c>
-      <c r="E90" s="14" t="n">
-        <v/>
-      </c>
-      <c r="F90" s="14" t="inlineStr">
-        <is>
-          <t>LITTERALIS</t>
-        </is>
-      </c>
+          <t>CD74</t>
+        </is>
+      </c>
+      <c r="E90" s="14" t="inlineStr">
+        <is>
+          <t>MAJ carto</t>
+        </is>
+      </c>
+      <c r="F90" s="14" t="inlineStr"/>
       <c r="G90" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H90" s="14" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="H90" s="14" t="inlineStr"/>
       <c r="I90" s="14" t="inlineStr">
         <is>
-          <t>26/08/2025</t>
+          <t>05/11/2025</t>
         </is>
       </c>
       <c r="J90" s="14" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="K90" s="14" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L90" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-28055</t>
-        </is>
-      </c>
-      <c r="M90" s="14" t="inlineStr">
-        <is>
-          <t>499132</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="L90" s="14" t="inlineStr"/>
+      <c r="M90" s="14" t="inlineStr"/>
       <c r="N90" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O90" s="15" t="n">
-        <v>416.188</v>
+        <v>0</v>
       </c>
       <c r="P90" s="15" t="n">
-        <v>277.46</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-23750</t>
+          <t>PDMDEP-26813</t>
         </is>
       </c>
       <c r="B91" s="11" t="inlineStr">
         <is>
-          <t>MEL - LITTERALIS x AXION</t>
+          <t>[VILLEJUIF] - Litteralis Modèle facture + param Civil Net</t>
         </is>
       </c>
       <c r="C91" s="11" t="inlineStr">
@@ -7207,13 +7213,11 @@
       </c>
       <c r="D91" s="11" t="inlineStr">
         <is>
-          <t>METROPOLE EUROPEENNE DE LILLE</t>
-        </is>
-      </c>
-      <c r="E91" s="11" t="inlineStr">
-        <is>
-          <t>AXION</t>
-        </is>
+          <t>VILLE DE VILLEJUIF</t>
+        </is>
+      </c>
+      <c r="E91" s="11" t="n">
+        <v/>
       </c>
       <c r="F91" s="11" t="inlineStr">
         <is>
@@ -7222,7 +7226,7 @@
       </c>
       <c r="G91" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H91" s="11" t="inlineStr">
@@ -7232,23 +7236,23 @@
       </c>
       <c r="I91" s="11" t="inlineStr">
         <is>
-          <t>08/08/2025</t>
+          <t>04/11/2025</t>
         </is>
       </c>
       <c r="J91" s="11" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="K91" s="11" t="n">
         <v>0.25</v>
       </c>
       <c r="L91" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27033</t>
+          <t>PDMDEP-26814</t>
         </is>
       </c>
       <c r="M91" s="11" t="inlineStr">
         <is>
-          <t>497304</t>
+          <t>00142941</t>
         </is>
       </c>
       <c r="N91" s="12" t="n">
@@ -7264,12 +7268,12 @@
     <row r="92">
       <c r="A92" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-23323</t>
+          <t>PDMDEP-24866</t>
         </is>
       </c>
       <c r="B92" s="14" t="inlineStr">
         <is>
-          <t>[BAGNOLET] - LITTERALIS projet</t>
+          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
         </is>
       </c>
       <c r="C92" s="14" t="inlineStr">
@@ -7279,7 +7283,7 @@
       </c>
       <c r="D92" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE BAGNOLET</t>
+          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
         </is>
       </c>
       <c r="E92" s="14" t="n">
@@ -7302,29 +7306,29 @@
       </c>
       <c r="I92" s="14" t="inlineStr">
         <is>
-          <t>21/07/2025</t>
+          <t>16/10/2025</t>
         </is>
       </c>
       <c r="J92" s="14" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="K92" s="14" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="L92" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27570</t>
+          <t>PDMDEP-27017</t>
         </is>
       </c>
       <c r="M92" s="14" t="inlineStr">
         <is>
-          <t>493613</t>
+          <t>00141205</t>
         </is>
       </c>
       <c r="N92" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O92" s="15" t="n">
+        <v>1212</v>
+      </c>
+      <c r="O92" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P92" s="15" t="n">
@@ -7334,12 +7338,12 @@
     <row r="93">
       <c r="A93" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-22757</t>
+          <t>PDMDEP-23918</t>
         </is>
       </c>
       <c r="B93" s="11" t="inlineStr">
         <is>
-          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
+          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C93" s="11" t="inlineStr">
@@ -7349,7 +7353,7 @@
       </c>
       <c r="D93" s="11" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
         </is>
       </c>
       <c r="E93" s="11" t="n">
@@ -7372,44 +7376,44 @@
       </c>
       <c r="I93" s="11" t="inlineStr">
         <is>
-          <t>01/07/2025</t>
+          <t>26/08/2025</t>
         </is>
       </c>
       <c r="J93" s="11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K93" s="11" t="n">
-        <v>0.06</v>
+        <v>1.5</v>
       </c>
       <c r="L93" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30081</t>
+          <t>PDMDEP-28055</t>
         </is>
       </c>
       <c r="M93" s="11" t="inlineStr">
         <is>
-          <t>00152628</t>
+          <t>499132</t>
         </is>
       </c>
       <c r="N93" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O93" s="12" t="n">
-        <v>0</v>
+        <v>416.188</v>
       </c>
       <c r="P93" s="12" t="n">
-        <v>0</v>
+        <v>277.46</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-22757</t>
+          <t>PDMDEP-23750</t>
         </is>
       </c>
       <c r="B94" s="14" t="inlineStr">
         <is>
-          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
+          <t>MEL - LITTERALIS x AXION</t>
         </is>
       </c>
       <c r="C94" s="14" t="inlineStr">
@@ -7419,11 +7423,13 @@
       </c>
       <c r="D94" s="14" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
-        </is>
-      </c>
-      <c r="E94" s="14" t="n">
-        <v/>
+          <t>METROPOLE EUROPEENNE DE LILLE</t>
+        </is>
+      </c>
+      <c r="E94" s="14" t="inlineStr">
+        <is>
+          <t>AXION</t>
+        </is>
       </c>
       <c r="F94" s="14" t="inlineStr">
         <is>
@@ -7432,33 +7438,33 @@
       </c>
       <c r="G94" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H94" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I94" s="14" t="inlineStr">
         <is>
-          <t>01/07/2025</t>
+          <t>08/08/2025</t>
         </is>
       </c>
       <c r="J94" s="14" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K94" s="14" t="n">
-        <v>0.06</v>
+        <v>0.25</v>
       </c>
       <c r="L94" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30080</t>
+          <t>PDMDEP-27033</t>
         </is>
       </c>
       <c r="M94" s="14" t="inlineStr">
         <is>
-          <t>00152635</t>
+          <t>497304</t>
         </is>
       </c>
       <c r="N94" s="15" t="n">
@@ -7474,12 +7480,12 @@
     <row r="95">
       <c r="A95" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-22757</t>
+          <t>PDMDEP-23323</t>
         </is>
       </c>
       <c r="B95" s="11" t="inlineStr">
         <is>
-          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
+          <t>[BAGNOLET] - LITTERALIS projet</t>
         </is>
       </c>
       <c r="C95" s="11" t="inlineStr">
@@ -7489,7 +7495,7 @@
       </c>
       <c r="D95" s="11" t="inlineStr">
         <is>
-          <t>Brest Métropole</t>
+          <t>VILLE DE BAGNOLET</t>
         </is>
       </c>
       <c r="E95" s="11" t="n">
@@ -7512,23 +7518,23 @@
       </c>
       <c r="I95" s="11" t="inlineStr">
         <is>
-          <t>01/07/2025</t>
+          <t>21/07/2025</t>
         </is>
       </c>
       <c r="J95" s="11" t="n">
         <v>14</v>
       </c>
       <c r="K95" s="11" t="n">
-        <v>0.06</v>
+        <v>1.5</v>
       </c>
       <c r="L95" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30079</t>
+          <t>PDMDEP-27570</t>
         </is>
       </c>
       <c r="M95" s="11" t="inlineStr">
         <is>
-          <t>00152632</t>
+          <t>493613</t>
         </is>
       </c>
       <c r="N95" s="12" t="n">
@@ -7593,12 +7599,12 @@
       </c>
       <c r="L96" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27365</t>
+          <t>PDMDEP-30081</t>
         </is>
       </c>
       <c r="M96" s="14" t="inlineStr">
         <is>
-          <t>491593</t>
+          <t>00152628</t>
         </is>
       </c>
       <c r="N96" s="15" t="n">
@@ -7614,12 +7620,12 @@
     <row r="97">
       <c r="A97" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-22126</t>
+          <t>PDMDEP-22757</t>
         </is>
       </c>
       <c r="B97" s="11" t="inlineStr">
         <is>
-          <t>[MEL Lille] - LITTERALIS - 3 jours de modélisation / param / accomp (21h)</t>
+          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C97" s="11" t="inlineStr">
@@ -7629,7 +7635,7 @@
       </c>
       <c r="D97" s="11" t="inlineStr">
         <is>
-          <t>Métropole Européenne de Lille</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E97" s="11" t="n">
@@ -7647,28 +7653,28 @@
       </c>
       <c r="H97" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I97" s="11" t="inlineStr">
         <is>
-          <t>02/06/2025</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="J97" s="11" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K97" s="11" t="n">
-        <v>0.25</v>
+        <v>0.06</v>
       </c>
       <c r="L97" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27368</t>
+          <t>PDMDEP-30080</t>
         </is>
       </c>
       <c r="M97" s="11" t="inlineStr">
         <is>
-          <t>484163</t>
+          <t>00152635</t>
         </is>
       </c>
       <c r="N97" s="12" t="n">
@@ -7684,22 +7690,22 @@
     <row r="98">
       <c r="A98" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-21661</t>
+          <t>PDMDEP-22757</t>
         </is>
       </c>
       <c r="B98" s="14" t="inlineStr">
         <is>
-          <t>[Grand Dax] - Pastell</t>
+          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C98" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D98" s="14" t="inlineStr">
         <is>
-          <t>GRAND DAX</t>
+          <t>Brest Métropole</t>
         </is>
       </c>
       <c r="E98" s="14" t="n">
@@ -7717,34 +7723,34 @@
       </c>
       <c r="H98" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I98" s="14" t="inlineStr">
         <is>
-          <t>07/05/2025</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="J98" s="14" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K98" s="14" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="L98" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27373</t>
+          <t>PDMDEP-30079</t>
         </is>
       </c>
       <c r="M98" s="14" t="inlineStr">
         <is>
-          <t>466234</t>
+          <t>00152632</t>
         </is>
       </c>
       <c r="N98" s="15" t="n">
-        <v>401</v>
-      </c>
-      <c r="O98" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O98" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P98" s="15" t="n">
@@ -7754,22 +7760,22 @@
     <row r="99">
       <c r="A99" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-21222</t>
+          <t>PDMDEP-22757</t>
         </is>
       </c>
       <c r="B99" s="11" t="inlineStr">
         <is>
-          <t>[Issy les Moulineaux] Litteralis Expert</t>
+          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C99" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D99" s="11" t="inlineStr">
         <is>
-          <t>ISSY LES MOULINEAUX</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E99" s="11" t="n">
@@ -7792,23 +7798,23 @@
       </c>
       <c r="I99" s="11" t="inlineStr">
         <is>
-          <t>23/04/2025</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="J99" s="11" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="K99" s="11" t="n">
-        <v>3.5</v>
+        <v>0.06</v>
       </c>
       <c r="L99" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28036</t>
+          <t>PDMDEP-27365</t>
         </is>
       </c>
       <c r="M99" s="11" t="inlineStr">
         <is>
-          <t>483799</t>
+          <t>491593</t>
         </is>
       </c>
       <c r="N99" s="12" t="n">
@@ -7824,12 +7830,12 @@
     <row r="100">
       <c r="A100" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-21165</t>
+          <t>PDMDEP-22126</t>
         </is>
       </c>
       <c r="B100" s="14" t="inlineStr">
         <is>
-          <t>[Montreuil] Mise à jour carto (SaaS)</t>
+          <t>[MEL Lille] - LITTERALIS - 3 jours de modélisation / param / accomp (21h)</t>
         </is>
       </c>
       <c r="C100" s="14" t="inlineStr">
@@ -7839,7 +7845,7 @@
       </c>
       <c r="D100" s="14" t="inlineStr">
         <is>
-          <t>MONTREUIL</t>
+          <t>Métropole Européenne de Lille</t>
         </is>
       </c>
       <c r="E100" s="14" t="n">
@@ -7862,23 +7868,23 @@
       </c>
       <c r="I100" s="14" t="inlineStr">
         <is>
-          <t>18/04/2025</t>
+          <t>02/06/2025</t>
         </is>
       </c>
       <c r="J100" s="14" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="K100" s="14" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="L100" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28035</t>
+          <t>PDMDEP-27368</t>
         </is>
       </c>
       <c r="M100" s="14" t="inlineStr">
         <is>
-          <t>468660</t>
+          <t>484163</t>
         </is>
       </c>
       <c r="N100" s="15" t="n">
@@ -7894,12 +7900,12 @@
     <row r="101">
       <c r="A101" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-20907</t>
+          <t>PDMDEP-21661</t>
         </is>
       </c>
       <c r="B101" s="11" t="inlineStr">
         <is>
-          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
+          <t>[Grand Dax] - Pastell</t>
         </is>
       </c>
       <c r="C101" s="11" t="inlineStr">
@@ -7909,7 +7915,7 @@
       </c>
       <c r="D101" s="11" t="inlineStr">
         <is>
-          <t>SAINT PIERRE (LA REUNION)</t>
+          <t>GRAND DAX</t>
         </is>
       </c>
       <c r="E101" s="11" t="n">
@@ -7932,27 +7938,27 @@
       </c>
       <c r="I101" s="11" t="inlineStr">
         <is>
-          <t>14/04/2025</t>
+          <t>07/05/2025</t>
         </is>
       </c>
       <c r="J101" s="11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K101" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L101" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28034</t>
+          <t>PDMDEP-27373</t>
         </is>
       </c>
       <c r="M101" s="11" t="inlineStr">
         <is>
-          <t>475575</t>
+          <t>466234</t>
         </is>
       </c>
       <c r="N101" s="12" t="n">
-        <v>230</v>
+        <v>401</v>
       </c>
       <c r="O101" s="16" t="n">
         <v>0</v>
@@ -7964,12 +7970,12 @@
     <row r="102">
       <c r="A102" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-19909</t>
+          <t>PDMDEP-21222</t>
         </is>
       </c>
       <c r="B102" s="14" t="inlineStr">
         <is>
-          <t>[CD 29] Interface Pastell</t>
+          <t>[Issy les Moulineaux] Litteralis Expert</t>
         </is>
       </c>
       <c r="C102" s="14" t="inlineStr">
@@ -7979,7 +7985,7 @@
       </c>
       <c r="D102" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU FINISTERE (CD29)</t>
+          <t>ISSY LES MOULINEAUX</t>
         </is>
       </c>
       <c r="E102" s="14" t="n">
@@ -7997,28 +8003,28 @@
       </c>
       <c r="H102" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I102" s="14" t="inlineStr">
         <is>
-          <t>11/03/2025</t>
+          <t>23/04/2025</t>
         </is>
       </c>
       <c r="J102" s="14" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K102" s="14" t="n">
-        <v>0.5</v>
+        <v>3.5</v>
       </c>
       <c r="L102" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27568</t>
+          <t>PDMDEP-28036</t>
         </is>
       </c>
       <c r="M102" s="14" t="inlineStr">
         <is>
-          <t>471958</t>
+          <t>483799</t>
         </is>
       </c>
       <c r="N102" s="15" t="n">
@@ -8034,12 +8040,12 @@
     <row r="103">
       <c r="A103" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-19558</t>
+          <t>PDMDEP-21165</t>
         </is>
       </c>
       <c r="B103" s="11" t="inlineStr">
         <is>
-          <t>[VILLEFONTAINE] - Litteralis Expert SAAS</t>
+          <t>[Montreuil] Mise à jour carto (SaaS)</t>
         </is>
       </c>
       <c r="C103" s="11" t="inlineStr">
@@ -8049,7 +8055,7 @@
       </c>
       <c r="D103" s="11" t="inlineStr">
         <is>
-          <t>VILLEFONTAINE</t>
+          <t>MONTREUIL</t>
         </is>
       </c>
       <c r="E103" s="11" t="n">
@@ -8067,28 +8073,28 @@
       </c>
       <c r="H103" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I103" s="11" t="inlineStr">
         <is>
-          <t>28/02/2025</t>
+          <t>18/04/2025</t>
         </is>
       </c>
       <c r="J103" s="11" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K103" s="11" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L103" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28215</t>
+          <t>PDMDEP-28035</t>
         </is>
       </c>
       <c r="M103" s="11" t="inlineStr">
         <is>
-          <t>458306</t>
+          <t>468660</t>
         </is>
       </c>
       <c r="N103" s="12" t="n">
@@ -8104,22 +8110,22 @@
     <row r="104">
       <c r="A104" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-19558</t>
+          <t>PDMDEP-20907</t>
         </is>
       </c>
       <c r="B104" s="14" t="inlineStr">
         <is>
-          <t>[VILLEFONTAINE] - Litteralis Expert SAAS</t>
+          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
         </is>
       </c>
       <c r="C104" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D104" s="14" t="inlineStr">
         <is>
-          <t>VILLEFONTAINE</t>
+          <t>SAINT PIERRE (LA REUNION)</t>
         </is>
       </c>
       <c r="E104" s="14" t="n">
@@ -8137,34 +8143,34 @@
       </c>
       <c r="H104" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I104" s="14" t="inlineStr">
         <is>
-          <t>28/02/2025</t>
+          <t>14/04/2025</t>
         </is>
       </c>
       <c r="J104" s="14" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K104" s="14" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L104" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28214</t>
+          <t>PDMDEP-28034</t>
         </is>
       </c>
       <c r="M104" s="14" t="inlineStr">
         <is>
-          <t>458286</t>
+          <t>475575</t>
         </is>
       </c>
       <c r="N104" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O104" s="15" t="n">
+        <v>230</v>
+      </c>
+      <c r="O104" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P104" s="15" t="n">
@@ -8174,22 +8180,22 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18241</t>
+          <t>PDMDEP-19909</t>
         </is>
       </c>
       <c r="B105" s="11" t="inlineStr">
         <is>
-          <t>[CD74 - HAUTE SAVOIE] - Interface LiEx Maj Ref BG</t>
+          <t>[CD 29] Interface Pastell</t>
         </is>
       </c>
       <c r="C105" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D105" s="11" t="inlineStr">
         <is>
-          <t>CD 74 - HAUTE SAVOIE</t>
+          <t>CONSEIL DEPARTEMENTAL DU FINISTERE (CD29)</t>
         </is>
       </c>
       <c r="E105" s="11" t="n">
@@ -8202,7 +8208,7 @@
       </c>
       <c r="G105" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H105" s="11" t="inlineStr">
@@ -8212,17 +8218,25 @@
       </c>
       <c r="I105" s="11" t="inlineStr">
         <is>
-          <t>20/12/2024</t>
+          <t>11/03/2025</t>
         </is>
       </c>
       <c r="J105" s="11" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="K105" s="11" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="L105" s="11" t="inlineStr"/>
-      <c r="M105" s="11" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="L105" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-27568</t>
+        </is>
+      </c>
+      <c r="M105" s="11" t="inlineStr">
+        <is>
+          <t>471958</t>
+        </is>
+      </c>
       <c r="N105" s="12" t="n">
         <v>0</v>
       </c>
@@ -8236,22 +8250,22 @@
     <row r="106">
       <c r="A106" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-18240</t>
+          <t>PDMDEP-19558</t>
         </is>
       </c>
       <c r="B106" s="14" t="inlineStr">
         <is>
-          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
+          <t>[VILLEFONTAINE] - Litteralis Expert SAAS</t>
         </is>
       </c>
       <c r="C106" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D106" s="14" t="inlineStr">
         <is>
-          <t>Biarritz</t>
+          <t>VILLEFONTAINE</t>
         </is>
       </c>
       <c r="E106" s="14" t="n">
@@ -8264,7 +8278,7 @@
       </c>
       <c r="G106" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H106" s="14" t="inlineStr">
@@ -8274,17 +8288,25 @@
       </c>
       <c r="I106" s="14" t="inlineStr">
         <is>
-          <t>20/12/2024</t>
+          <t>28/02/2025</t>
         </is>
       </c>
       <c r="J106" s="14" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="K106" s="14" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="L106" s="14" t="inlineStr"/>
-      <c r="M106" s="14" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="L106" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-28215</t>
+        </is>
+      </c>
+      <c r="M106" s="14" t="inlineStr">
+        <is>
+          <t>458306</t>
+        </is>
+      </c>
       <c r="N106" s="15" t="n">
         <v>0</v>
       </c>
@@ -8298,22 +8320,22 @@
     <row r="107">
       <c r="A107" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18115</t>
+          <t>PDMDEP-19558</t>
         </is>
       </c>
       <c r="B107" s="11" t="inlineStr">
         <is>
-          <t>[Bischwiller] Migration + Pax + M2M</t>
+          <t>[VILLEFONTAINE] - Litteralis Expert SAAS</t>
         </is>
       </c>
       <c r="C107" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D107" s="11" t="inlineStr">
         <is>
-          <t>BISCHWILLER</t>
+          <t>VILLEFONTAINE</t>
         </is>
       </c>
       <c r="E107" s="11" t="n">
@@ -8321,7 +8343,7 @@
       </c>
       <c r="F107" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G107" s="11" t="inlineStr">
@@ -8331,34 +8353,34 @@
       </c>
       <c r="H107" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I107" s="11" t="inlineStr">
         <is>
-          <t>17/12/2024</t>
+          <t>28/02/2025</t>
         </is>
       </c>
       <c r="J107" s="11" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="K107" s="11" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L107" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28019</t>
+          <t>PDMDEP-28214</t>
         </is>
       </c>
       <c r="M107" s="11" t="inlineStr">
         <is>
-          <t>455151</t>
+          <t>458286</t>
         </is>
       </c>
       <c r="N107" s="12" t="n">
-        <v>240</v>
-      </c>
-      <c r="O107" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O107" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P107" s="12" t="n">
@@ -8368,22 +8390,22 @@
     <row r="108">
       <c r="A108" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-18037</t>
+          <t>PDMDEP-18241</t>
         </is>
       </c>
       <c r="B108" s="14" t="inlineStr">
         <is>
-          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
+          <t>[CD74 - HAUTE SAVOIE] - Interface LiEx Maj Ref BG</t>
         </is>
       </c>
       <c r="C108" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D108" s="14" t="inlineStr">
         <is>
-          <t>LE PERREUX SUR MARNE</t>
+          <t>CD 74 - HAUTE SAVOIE</t>
         </is>
       </c>
       <c r="E108" s="14" t="n">
@@ -8396,7 +8418,7 @@
       </c>
       <c r="G108" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H108" s="14" t="inlineStr">
@@ -8406,29 +8428,21 @@
       </c>
       <c r="I108" s="14" t="inlineStr">
         <is>
-          <t>12/12/2024</t>
+          <t>20/12/2024</t>
         </is>
       </c>
       <c r="J108" s="14" t="n">
         <v>21</v>
       </c>
       <c r="K108" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L108" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-28023</t>
-        </is>
-      </c>
-      <c r="M108" s="14" t="inlineStr">
-        <is>
-          <t>454387</t>
-        </is>
-      </c>
+        <v>5.5</v>
+      </c>
+      <c r="L108" s="14" t="inlineStr"/>
+      <c r="M108" s="14" t="inlineStr"/>
       <c r="N108" s="15" t="n">
-        <v>557.145</v>
-      </c>
-      <c r="O108" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O108" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P108" s="15" t="n">
@@ -8438,22 +8452,22 @@
     <row r="109">
       <c r="A109" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-14118</t>
+          <t>PDMDEP-18240</t>
         </is>
       </c>
       <c r="B109" s="11" t="inlineStr">
         <is>
-          <t>[SURESNES] Interface FAST-Parapheur</t>
+          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
         </is>
       </c>
       <c r="C109" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D109" s="11" t="inlineStr">
         <is>
-          <t>Suresnes</t>
+          <t>Biarritz</t>
         </is>
       </c>
       <c r="E109" s="11" t="n">
@@ -8471,19 +8485,19 @@
       </c>
       <c r="H109" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I109" s="11" t="inlineStr">
         <is>
-          <t>01/02/2024</t>
+          <t>20/12/2024</t>
         </is>
       </c>
       <c r="J109" s="11" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="K109" s="11" t="n">
-        <v>0.5</v>
+        <v>3.08</v>
       </c>
       <c r="L109" s="11" t="inlineStr"/>
       <c r="M109" s="11" t="inlineStr"/>
@@ -8500,22 +8514,22 @@
     <row r="110">
       <c r="A110" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-13128</t>
+          <t>PDMDEP-18115</t>
         </is>
       </c>
       <c r="B110" s="14" t="inlineStr">
         <is>
-          <t>[VALENCIENNES] Littéralis Prime - RAF FAST PARAPHEUR - Déjà facturé</t>
+          <t>[Bischwiller] Migration + Pax + M2M</t>
         </is>
       </c>
       <c r="C110" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D110" s="14" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>BISCHWILLER</t>
         </is>
       </c>
       <c r="E110" s="14" t="n">
@@ -8523,36 +8537,44 @@
       </c>
       <c r="F110" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G110" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H110" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I110" s="14" t="inlineStr">
         <is>
-          <t>30/10/2023</t>
+          <t>17/12/2024</t>
         </is>
       </c>
       <c r="J110" s="14" t="n">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="K110" s="14" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="L110" s="14" t="inlineStr"/>
-      <c r="M110" s="14" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L110" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-28019</t>
+        </is>
+      </c>
+      <c r="M110" s="14" t="inlineStr">
+        <is>
+          <t>455151</t>
+        </is>
+      </c>
       <c r="N110" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O110" s="15" t="n">
+        <v>240</v>
+      </c>
+      <c r="O110" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P110" s="15" t="n">
@@ -8562,12 +8584,12 @@
     <row r="111">
       <c r="A111" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-12747</t>
+          <t>PDMDEP-18037</t>
         </is>
       </c>
       <c r="B111" s="11" t="inlineStr">
         <is>
-          <t>[FOUGERES] ARPEGE</t>
+          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
         </is>
       </c>
       <c r="C111" s="11" t="inlineStr">
@@ -8577,7 +8599,7 @@
       </c>
       <c r="D111" s="11" t="inlineStr">
         <is>
-          <t>FOUGERES</t>
+          <t>LE PERREUX SUR MARNE</t>
         </is>
       </c>
       <c r="E111" s="11" t="n">
@@ -8600,29 +8622,29 @@
       </c>
       <c r="I111" s="11" t="inlineStr">
         <is>
-          <t>26/09/2023</t>
+          <t>12/12/2024</t>
         </is>
       </c>
       <c r="J111" s="11" t="n">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="K111" s="11" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="L111" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27990</t>
+          <t>PDMDEP-28023</t>
         </is>
       </c>
       <c r="M111" s="11" t="inlineStr">
         <is>
-          <t>406296</t>
+          <t>454387</t>
         </is>
       </c>
       <c r="N111" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O111" s="12" t="n">
+        <v>557.145</v>
+      </c>
+      <c r="O111" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P111" s="12" t="n">
@@ -8632,12 +8654,12 @@
     <row r="112">
       <c r="A112" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-12708</t>
+          <t>PDMDEP-14118</t>
         </is>
       </c>
       <c r="B112" s="14" t="inlineStr">
         <is>
-          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
+          <t>[SURESNES] Interface FAST-Parapheur</t>
         </is>
       </c>
       <c r="C112" s="14" t="inlineStr">
@@ -8647,7 +8669,7 @@
       </c>
       <c r="D112" s="14" t="inlineStr">
         <is>
-          <t>CD 56 MORBIHAN</t>
+          <t>Suresnes</t>
         </is>
       </c>
       <c r="E112" s="14" t="n">
@@ -8663,17 +8685,21 @@
           <t>Rework</t>
         </is>
       </c>
-      <c r="H112" s="14" t="inlineStr"/>
+      <c r="H112" s="14" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I112" s="14" t="inlineStr">
         <is>
-          <t>22/09/2023</t>
+          <t>01/02/2024</t>
         </is>
       </c>
       <c r="J112" s="14" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="K112" s="14" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="L112" s="14" t="inlineStr"/>
       <c r="M112" s="14" t="inlineStr"/>
@@ -8690,24 +8716,26 @@
     <row r="113">
       <c r="A113" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-11477</t>
+          <t>PDMDEP-13128</t>
         </is>
       </c>
       <c r="B113" s="11" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
-        </is>
-      </c>
-      <c r="C113" s="11" t="inlineStr"/>
+          <t>[VALENCIENNES] Littéralis Prime - RAF FAST PARAPHEUR - Déjà facturé</t>
+        </is>
+      </c>
+      <c r="C113" s="11" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
       <c r="D113" s="11" t="inlineStr">
         <is>
-          <t>MONTPELLIER MMM</t>
-        </is>
-      </c>
-      <c r="E113" s="11" t="inlineStr">
-        <is>
-          <t>Déploiement Module AC</t>
-        </is>
+          <t>Valenciennes</t>
+        </is>
+      </c>
+      <c r="E113" s="11" t="n">
+        <v/>
       </c>
       <c r="F113" s="11" t="inlineStr">
         <is>
@@ -8726,14 +8754,14 @@
       </c>
       <c r="I113" s="11" t="inlineStr">
         <is>
-          <t>03/09/2023</t>
+          <t>30/10/2023</t>
         </is>
       </c>
       <c r="J113" s="11" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K113" s="11" t="n">
-        <v>2.75</v>
+        <v>3.58</v>
       </c>
       <c r="L113" s="11" t="inlineStr"/>
       <c r="M113" s="11" t="inlineStr"/>
@@ -8750,89 +8778,277 @@
     <row r="114">
       <c r="A114" s="13" t="inlineStr">
         <is>
+          <t>PDMDEP-12747</t>
+        </is>
+      </c>
+      <c r="B114" s="14" t="inlineStr">
+        <is>
+          <t>[FOUGERES] ARPEGE</t>
+        </is>
+      </c>
+      <c r="C114" s="14" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
+      <c r="D114" s="14" t="inlineStr">
+        <is>
+          <t>FOUGERES</t>
+        </is>
+      </c>
+      <c r="E114" s="14" t="n">
+        <v/>
+      </c>
+      <c r="F114" s="14" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G114" s="14" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H114" s="14" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="I114" s="14" t="inlineStr">
+        <is>
+          <t>26/09/2023</t>
+        </is>
+      </c>
+      <c r="J114" s="14" t="n">
+        <v>36</v>
+      </c>
+      <c r="K114" s="14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L114" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-27990</t>
+        </is>
+      </c>
+      <c r="M114" s="14" t="inlineStr">
+        <is>
+          <t>406296</t>
+        </is>
+      </c>
+      <c r="N114" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O114" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P114" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="10" t="inlineStr">
+        <is>
+          <t>PDMDEP-12708</t>
+        </is>
+      </c>
+      <c r="B115" s="11" t="inlineStr">
+        <is>
+          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
+        </is>
+      </c>
+      <c r="C115" s="11" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
+      <c r="D115" s="11" t="inlineStr">
+        <is>
+          <t>CD 56 MORBIHAN</t>
+        </is>
+      </c>
+      <c r="E115" s="11" t="n">
+        <v/>
+      </c>
+      <c r="F115" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G115" s="11" t="inlineStr">
+        <is>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H115" s="11" t="inlineStr"/>
+      <c r="I115" s="11" t="inlineStr">
+        <is>
+          <t>22/09/2023</t>
+        </is>
+      </c>
+      <c r="J115" s="11" t="n">
+        <v>36</v>
+      </c>
+      <c r="K115" s="11" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="L115" s="11" t="inlineStr"/>
+      <c r="M115" s="11" t="inlineStr"/>
+      <c r="N115" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O115" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P115" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="13" t="inlineStr">
+        <is>
+          <t>PDMDEP-11477</t>
+        </is>
+      </c>
+      <c r="B116" s="14" t="inlineStr">
+        <is>
+          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
+        </is>
+      </c>
+      <c r="C116" s="14" t="inlineStr"/>
+      <c r="D116" s="14" t="inlineStr">
+        <is>
+          <t>MONTPELLIER MMM</t>
+        </is>
+      </c>
+      <c r="E116" s="14" t="inlineStr">
+        <is>
+          <t>Déploiement Module AC</t>
+        </is>
+      </c>
+      <c r="F116" s="14" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G116" s="14" t="inlineStr">
+        <is>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H116" s="14" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
+      <c r="I116" s="14" t="inlineStr">
+        <is>
+          <t>03/09/2023</t>
+        </is>
+      </c>
+      <c r="J116" s="14" t="n">
+        <v>36</v>
+      </c>
+      <c r="K116" s="14" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="L116" s="14" t="inlineStr"/>
+      <c r="M116" s="14" t="inlineStr"/>
+      <c r="N116" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O116" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P116" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="10" t="inlineStr">
+        <is>
           <t>PSC-1270</t>
         </is>
       </c>
-      <c r="B114" s="14" t="inlineStr">
+      <c r="B117" s="11" t="inlineStr">
         <is>
           <t>COMMUNE DE CASTELNAUDARY</t>
         </is>
       </c>
-      <c r="C114" s="14" t="inlineStr"/>
-      <c r="D114" s="14" t="inlineStr">
+      <c r="C117" s="11" t="inlineStr"/>
+      <c r="D117" s="11" t="inlineStr">
         <is>
           <t>COMMUNE DE CASTELNAUDARY</t>
         </is>
       </c>
-      <c r="E114" s="14" t="inlineStr"/>
-      <c r="F114" s="14" t="inlineStr">
+      <c r="E117" s="11" t="inlineStr"/>
+      <c r="F117" s="11" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
         </is>
       </c>
-      <c r="G114" s="14" t="inlineStr">
+      <c r="G117" s="11" t="inlineStr">
         <is>
           <t>Projet</t>
         </is>
       </c>
-      <c r="H114" s="14" t="inlineStr"/>
-      <c r="I114" s="14" t="inlineStr">
+      <c r="H117" s="11" t="inlineStr"/>
+      <c r="I117" s="11" t="inlineStr">
         <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="J114" s="14" t="n">
+      <c r="J117" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="K114" s="14" t="n">
+      <c r="K117" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="L114" s="14" t="inlineStr">
+      <c r="L117" s="11" t="inlineStr">
         <is>
           <t>PDMDEP-33362</t>
         </is>
       </c>
-      <c r="M114" s="14" t="inlineStr">
+      <c r="M117" s="11" t="inlineStr">
         <is>
           <t>00167140</t>
         </is>
       </c>
-      <c r="N114" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O114" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P114" s="15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="17" t="inlineStr">
+      <c r="N117" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O117" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P117" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="17" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B115" s="17" t="inlineStr"/>
-      <c r="C115" s="17" t="inlineStr"/>
-      <c r="D115" s="17" t="inlineStr"/>
-      <c r="E115" s="17" t="inlineStr"/>
-      <c r="F115" s="17" t="inlineStr"/>
-      <c r="G115" s="17" t="inlineStr"/>
-      <c r="H115" s="17" t="inlineStr"/>
-      <c r="I115" s="17" t="inlineStr"/>
-      <c r="J115" s="17" t="inlineStr"/>
-      <c r="K115" s="17" t="inlineStr"/>
-      <c r="L115" s="17" t="inlineStr"/>
-      <c r="M115" s="17" t="inlineStr"/>
-      <c r="N115" s="18" t="n">
+      <c r="B118" s="17" t="inlineStr"/>
+      <c r="C118" s="17" t="inlineStr"/>
+      <c r="D118" s="17" t="inlineStr"/>
+      <c r="E118" s="17" t="inlineStr"/>
+      <c r="F118" s="17" t="inlineStr"/>
+      <c r="G118" s="17" t="inlineStr"/>
+      <c r="H118" s="17" t="inlineStr"/>
+      <c r="I118" s="17" t="inlineStr"/>
+      <c r="J118" s="17" t="inlineStr"/>
+      <c r="K118" s="17" t="inlineStr"/>
+      <c r="L118" s="17" t="inlineStr"/>
+      <c r="M118" s="17" t="inlineStr"/>
+      <c r="N118" s="18" t="n">
         <v>47526.995</v>
       </c>
-      <c r="O115" s="18" t="n">
-        <v>17396.678</v>
-      </c>
-      <c r="P115" s="18" t="n">
-        <v>185.45</v>
+      <c r="O118" s="18" t="n">
+        <v>17574.178</v>
+      </c>
+      <c r="P118" s="18" t="n">
+        <v>183.91</v>
       </c>
     </row>
   </sheetData>
@@ -8948,6 +9164,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A112" r:id="rId108"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A113" r:id="rId109"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A114" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A115" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A116" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A117" r:id="rId113"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9705,7 +9924,7 @@
         </is>
       </c>
       <c r="B5" s="14" t="n">
-        <v>50.92</v>
+        <v>52.67</v>
       </c>
       <c r="C5" s="14" t="n">
         <v>16.42</v>
@@ -9714,7 +9933,7 @@
         <v>5.75</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>73.08</v>
+        <v>74.83</v>
       </c>
       <c r="F5" s="14" t="n">
         <v>11.17</v>
@@ -9724,7 +9943,7 @@
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>11.5%</t>
         </is>
       </c>
     </row>
@@ -9851,16 +10070,16 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>393570</v>
+        <v>393393</v>
       </c>
       <c r="C5" s="24" t="n">
         <v>167739</v>
       </c>
       <c r="D5" s="24" t="n">
-        <v>225831</v>
+        <v>225654</v>
       </c>
       <c r="E5" s="24" t="n">
-        <v>140842</v>
+        <v>140664</v>
       </c>
       <c r="F5" s="24" t="n">
         <v>18223</v>
@@ -9901,16 +10120,16 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>230305</v>
+        <v>230128</v>
       </c>
       <c r="C7" s="26" t="n">
         <v>106174</v>
       </c>
       <c r="D7" s="26" t="n">
-        <v>124131</v>
+        <v>123954</v>
       </c>
       <c r="E7" s="26" t="n">
-        <v>54027</v>
+        <v>53849</v>
       </c>
       <c r="F7" s="26" t="n">
         <v>9048</v>
@@ -9930,7 +10149,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -9954,7 +10173,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Épics créées ce mois — 10 commande(s)</t>
+          <t>Épics créées ce mois — 11 commande(s)</t>
         </is>
       </c>
     </row>
@@ -10009,22 +10228,22 @@
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35587</t>
+          <t>PDMDEP-35606</t>
         </is>
       </c>
       <c r="B5" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35583</t>
+          <t>PDMDEP-35597</t>
         </is>
       </c>
       <c r="C5" s="14" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="D5" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHAMBERY</t>
+          <t>COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE</t>
         </is>
       </c>
       <c r="E5" s="14" t="inlineStr">
@@ -10034,7 +10253,7 @@
       </c>
       <c r="F5" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="G5" s="14" t="inlineStr">
@@ -10044,7 +10263,7 @@
       </c>
       <c r="H5" s="14" t="inlineStr">
         <is>
-          <t>00180931</t>
+          <t>00181049</t>
         </is>
       </c>
       <c r="I5" s="25" t="n">
@@ -10054,22 +10273,22 @@
     <row r="6">
       <c r="A6" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35532</t>
+          <t>PDMDEP-35587</t>
         </is>
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35518</t>
+          <t>PDMDEP-35583</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE PRIVAS</t>
+          <t>COMMUNE DE CHAMBERY</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">
@@ -10079,34 +10298,42 @@
       </c>
       <c r="F6" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
-        </is>
-      </c>
-      <c r="G6" s="11" t="inlineStr"/>
-      <c r="H6" s="11" t="inlineStr"/>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="G6" s="11" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="H6" s="11" t="inlineStr">
+        <is>
+          <t>00180931</t>
+        </is>
+      </c>
       <c r="I6" s="26" t="n">
-        <v>1450</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35478</t>
+          <t>PDMDEP-35532</t>
         </is>
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35469</t>
+          <t>PDMDEP-35518</t>
         </is>
       </c>
       <c r="C7" s="14" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="D7" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE VENCE</t>
+          <t>COMMUNE DE PRIVAS</t>
         </is>
       </c>
       <c r="E7" s="14" t="inlineStr">
@@ -10119,39 +10346,31 @@
           <t>Migration</t>
         </is>
       </c>
-      <c r="G7" s="14" t="inlineStr">
-        <is>
-          <t>Services</t>
-        </is>
-      </c>
-      <c r="H7" s="14" t="inlineStr">
-        <is>
-          <t>00180643</t>
-        </is>
-      </c>
+      <c r="G7" s="14" t="inlineStr"/>
+      <c r="H7" s="14" t="inlineStr"/>
       <c r="I7" s="25" t="n">
-        <v>6285</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35410</t>
+          <t>PDMDEP-35478</t>
         </is>
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35401</t>
+          <t>PDMDEP-35469</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Commune de Saint Cast le Guildo </t>
+          <t>COMMUNE DE VENCE</t>
         </is>
       </c>
       <c r="E8" s="11" t="inlineStr">
@@ -10171,22 +10390,22 @@
       </c>
       <c r="H8" s="11" t="inlineStr">
         <is>
-          <t>00173074</t>
+          <t>00180643</t>
         </is>
       </c>
       <c r="I8" s="26" t="n">
-        <v>1200</v>
+        <v>6285</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35392</t>
+          <t>PDMDEP-35410</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35385</t>
+          <t>PDMDEP-35401</t>
         </is>
       </c>
       <c r="C9" s="14" t="inlineStr">
@@ -10196,7 +10415,7 @@
       </c>
       <c r="D9" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE ROUEN</t>
+          <t xml:space="preserve">Commune de Saint Cast le Guildo </t>
         </is>
       </c>
       <c r="E9" s="14" t="inlineStr">
@@ -10216,42 +10435,42 @@
       </c>
       <c r="H9" s="14" t="inlineStr">
         <is>
-          <t>00179700</t>
+          <t>00173074</t>
         </is>
       </c>
       <c r="I9" s="25" t="n">
-        <v>28915.01</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35576</t>
+          <t>PDMDEP-35392</t>
         </is>
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35572</t>
+          <t>PDMDEP-35385</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L'ARIEGE (CD 09)</t>
+          <t>COMMUNE DE ROUEN</t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="F10" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="G10" s="11" t="inlineStr">
@@ -10261,22 +10480,22 @@
       </c>
       <c r="H10" s="11" t="inlineStr">
         <is>
-          <t>00180891</t>
+          <t>00179700</t>
         </is>
       </c>
       <c r="I10" s="26" t="n">
-        <v>0</v>
+        <v>28915.01</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35567</t>
+          <t>PDMDEP-35576</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35561</t>
+          <t>PDMDEP-35572</t>
         </is>
       </c>
       <c r="C11" s="14" t="inlineStr">
@@ -10286,7 +10505,7 @@
       </c>
       <c r="D11" s="14" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU MORBIHAN (CD 56)</t>
+          <t>CONSEIL DEPARTEMENTAL DE L'ARIEGE (CD 09)</t>
         </is>
       </c>
       <c r="E11" s="14" t="inlineStr">
@@ -10306,7 +10525,7 @@
       </c>
       <c r="H11" s="14" t="inlineStr">
         <is>
-          <t>00180878</t>
+          <t>00180891</t>
         </is>
       </c>
       <c r="I11" s="25" t="n">
@@ -10316,22 +10535,22 @@
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35511</t>
+          <t>PDMDEP-35567</t>
         </is>
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35504</t>
+          <t>PDMDEP-35561</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>[TEST]</t>
+          <t>DEPARTEMENT DU MORBIHAN (CD 56)</t>
         </is>
       </c>
       <c r="E12" s="11" t="inlineStr">
@@ -10341,7 +10560,7 @@
       </c>
       <c r="F12" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="G12" s="11" t="inlineStr">
@@ -10351,7 +10570,7 @@
       </c>
       <c r="H12" s="11" t="inlineStr">
         <is>
-          <t>0015489263</t>
+          <t>00180878</t>
         </is>
       </c>
       <c r="I12" s="26" t="n">
@@ -10361,22 +10580,22 @@
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35464</t>
+          <t>PDMDEP-35511</t>
         </is>
       </c>
       <c r="B13" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35460</t>
+          <t>PDMDEP-35504</t>
         </is>
       </c>
       <c r="C13" s="14" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="D13" s="14" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DE LA CHARENTE (CD 16)</t>
+          <t>[TEST]</t>
         </is>
       </c>
       <c r="E13" s="14" t="inlineStr">
@@ -10386,7 +10605,7 @@
       </c>
       <c r="F13" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="G13" s="14" t="inlineStr">
@@ -10396,83 +10615,107 @@
       </c>
       <c r="H13" s="14" t="inlineStr">
         <is>
-          <t>00180631</t>
+          <t>0015489263</t>
         </is>
       </c>
       <c r="I13" s="25" t="n">
-        <v>455</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
         <is>
+          <t>PDMDEP-35464</t>
+        </is>
+      </c>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-35460</t>
+        </is>
+      </c>
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="D14" s="11" t="inlineStr">
+        <is>
+          <t>DEPARTEMENT DE LA CHARENTE (CD 16)</t>
+        </is>
+      </c>
+      <c r="E14" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F14" s="11" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="G14" s="11" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="H14" s="11" t="inlineStr">
+        <is>
+          <t>00180631</t>
+        </is>
+      </c>
+      <c r="I14" s="26" t="n">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="14" t="inlineStr">
+        <is>
           <t>PDMDEP-35439</t>
         </is>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B15" s="14" t="inlineStr">
         <is>
           <t>PDMDEP-35435</t>
         </is>
       </c>
-      <c r="C14" s="11" t="inlineStr">
+      <c r="C15" s="14" t="inlineStr">
         <is>
           <t>03/09/2026</t>
         </is>
       </c>
-      <c r="D14" s="11" t="inlineStr">
+      <c r="D15" s="14" t="inlineStr">
         <is>
           <t>DEPARTEMENT DES HAUTS-DE-SEINE</t>
         </is>
       </c>
-      <c r="E14" s="11" t="inlineStr">
+      <c r="E15" s="14" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
         </is>
       </c>
-      <c r="F14" s="11" t="inlineStr">
+      <c r="F15" s="14" t="inlineStr">
         <is>
           <t>Vente additionnelle</t>
         </is>
       </c>
-      <c r="G14" s="11" t="inlineStr">
+      <c r="G15" s="14" t="inlineStr">
         <is>
           <t>Services</t>
         </is>
       </c>
-      <c r="H14" s="11" t="inlineStr">
+      <c r="H15" s="14" t="inlineStr">
         <is>
           <t>00180506</t>
         </is>
       </c>
-      <c r="I14" s="26" t="n">
+      <c r="I15" s="25" t="n">
         <v>3974</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="17" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B15" s="17" t="n"/>
-      <c r="C15" s="17" t="n"/>
-      <c r="D15" s="17" t="n"/>
-      <c r="E15" s="17" t="n"/>
-      <c r="F15" s="17" t="n"/>
-      <c r="G15" s="17" t="n"/>
-      <c r="H15" s="17" t="inlineStr">
-        <is>
-          <t>10 commande(s)</t>
-        </is>
-      </c>
-      <c r="I15" s="24" t="n">
-        <v>42279</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="17" t="inlineStr">
         <is>
-          <t>dont Littéralis</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B16" s="17" t="n"/>
@@ -10483,17 +10726,17 @@
       <c r="G16" s="17" t="n"/>
       <c r="H16" s="17" t="inlineStr">
         <is>
-          <t>5 commande(s)</t>
+          <t>11 commande(s)</t>
         </is>
       </c>
       <c r="I16" s="24" t="n">
-        <v>4429</v>
+        <v>42279</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="17" t="inlineStr">
         <is>
-          <t>dont GEODP</t>
+          <t>dont Littéralis</t>
         </is>
       </c>
       <c r="B17" s="17" t="n"/>
@@ -10508,6 +10751,27 @@
         </is>
       </c>
       <c r="I17" s="24" t="n">
+        <v>4429</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="17" t="inlineStr">
+        <is>
+          <t>dont GEODP</t>
+        </is>
+      </c>
+      <c r="B18" s="17" t="n"/>
+      <c r="C18" s="17" t="n"/>
+      <c r="D18" s="17" t="n"/>
+      <c r="E18" s="17" t="n"/>
+      <c r="F18" s="17" t="n"/>
+      <c r="G18" s="17" t="n"/>
+      <c r="H18" s="17" t="inlineStr">
+        <is>
+          <t>6 commande(s)</t>
+        </is>
+      </c>
+      <c r="I18" s="24" t="n">
         <v>37850</v>
       </c>
     </row>
